--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30602"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3233" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F832B7A0-A963-4D73-9C15-8703A49DA3BE}"/>
+  <xr:revisionPtr revIDLastSave="3264" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B56F1BE5-F1B5-4FDC-9A77-6F61C3D3CFA2}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1081" uniqueCount="378">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="380">
   <si>
     <t>Date</t>
   </si>
@@ -1176,6 +1176,12 @@
   </si>
   <si>
     <t>791 MB</t>
+  </si>
+  <si>
+    <t>qwen2-math:1.5b</t>
+  </si>
+  <si>
+    <t>935MB</t>
   </si>
 </sst>
 </file>
@@ -11347,35 +11353,63 @@
     </row>
     <row r="181" spans="1:22" ht="15.75" customHeight="1">
       <c r="A181" s="33">
-        <v>46304</v>
+        <v>46307</v>
       </c>
       <c r="B181" s="26" t="s">
         <v>367</v>
       </c>
-      <c r="C181" s="10"/>
-      <c r="D181" s="10"/>
-      <c r="E181" s="10"/>
-      <c r="F181" s="10"/>
+      <c r="C181" t="s">
+        <v>378</v>
+      </c>
+      <c r="D181" t="s">
+        <v>34</v>
+      </c>
+      <c r="E181" t="s">
+        <v>379</v>
+      </c>
+      <c r="F181" s="10" t="s">
+        <v>31</v>
+      </c>
       <c r="G181" s="10"/>
       <c r="H181" s="10"/>
       <c r="I181" s="10"/>
       <c r="J181" s="10"/>
       <c r="K181" s="10"/>
       <c r="L181" s="10"/>
-      <c r="M181" s="10"/>
+      <c r="M181" s="30"/>
       <c r="N181" s="10"/>
-      <c r="O181" s="10"/>
-      <c r="P181" s="10"/>
-      <c r="Q181" s="10"/>
-      <c r="R181" s="10"/>
-      <c r="S181" s="10"/>
-      <c r="T181" s="10"/>
-      <c r="U181" s="10"/>
-      <c r="V181" s="10"/>
+      <c r="O181" s="10">
+        <v>0.95</v>
+      </c>
+      <c r="P181" s="10">
+        <v>0.36199999999999999</v>
+      </c>
+      <c r="Q181" s="10">
+        <v>15537.3</v>
+      </c>
+      <c r="R181" s="10">
+        <v>0.48899999999999999</v>
+      </c>
+      <c r="S181" s="10">
+        <v>0.68200000000000005</v>
+      </c>
+      <c r="T181" s="10">
+        <v>1</v>
+      </c>
+      <c r="U181" s="10">
+        <v>0.92400000000000004</v>
+      </c>
+      <c r="V181" s="10">
+        <v>0.58199999999999996</v>
+      </c>
     </row>
     <row r="182" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A182" s="10"/>
-      <c r="B182" s="10"/>
+      <c r="A182" s="13">
+        <v>46307</v>
+      </c>
+      <c r="B182" s="10" t="s">
+        <v>367</v>
+      </c>
       <c r="C182" s="10"/>
       <c r="D182" s="10"/>
       <c r="E182" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3264" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B56F1BE5-F1B5-4FDC-9A77-6F61C3D3CFA2}"/>
+  <xr:revisionPtr revIDLastSave="3265" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D9AA07F-4022-44CD-B57E-28A384B5C41B}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -3264,10 +3264,7 @@
       <c r="I25" s="2"/>
       <c r="J25" s="2"/>
       <c r="K25" s="2"/>
-      <c r="L25" s="2">
-        <f>-P12</f>
-        <v>-0.64400000000000002</v>
-      </c>
+      <c r="L25" s="2"/>
       <c r="M25" s="9"/>
       <c r="N25" s="2"/>
       <c r="O25" s="2">

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3265" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6D9AA07F-4022-44CD-B57E-28A384B5C41B}"/>
+  <xr:revisionPtr revIDLastSave="3287" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25FC002F-DB0F-4765-A2E2-ED2AF36C51EC}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1086" uniqueCount="380">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="383">
   <si>
     <t>Date</t>
   </si>
@@ -1182,6 +1182,15 @@
   </si>
   <si>
     <t>935MB</t>
+  </si>
+  <si>
+    <t>falcon-h1</t>
+  </si>
+  <si>
+    <t>448b</t>
+  </si>
+  <si>
+    <t>Tii</t>
   </si>
 </sst>
 </file>
@@ -11407,26 +11416,50 @@
       <c r="B182" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="C182" s="10"/>
-      <c r="D182" s="10"/>
-      <c r="E182" s="10"/>
-      <c r="F182" s="10"/>
+      <c r="C182" t="s">
+        <v>380</v>
+      </c>
+      <c r="D182" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E182" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="F182" s="10" t="s">
+        <v>382</v>
+      </c>
       <c r="G182" s="10"/>
       <c r="H182" s="10"/>
-      <c r="I182" s="10"/>
+      <c r="I182" s="30"/>
       <c r="J182" s="10"/>
       <c r="K182" s="10"/>
       <c r="L182" s="10"/>
       <c r="M182" s="10"/>
       <c r="N182" s="10"/>
-      <c r="O182" s="10"/>
-      <c r="P182" s="10"/>
-      <c r="Q182" s="10"/>
-      <c r="R182" s="10"/>
-      <c r="S182" s="10"/>
-      <c r="T182" s="10"/>
-      <c r="U182" s="10"/>
-      <c r="V182" s="10"/>
+      <c r="O182" s="10">
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="P182" s="10">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="Q182" s="10">
+        <v>19401.37</v>
+      </c>
+      <c r="R182" s="10">
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="S182" s="10">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="T182" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="U182" s="10">
+        <v>0.89100000000000001</v>
+      </c>
+      <c r="V182" s="10">
+        <v>0.63600000000000001</v>
+      </c>
     </row>
     <row r="183" spans="1:22" ht="15.75" customHeight="1">
       <c r="A183" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3287" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25FC002F-DB0F-4765-A2E2-ED2AF36C51EC}"/>
+  <xr:revisionPtr revIDLastSave="3306" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22EE77E3-CC00-42F2-86C3-07EB60C8EB60}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1090" uniqueCount="383">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="382">
   <si>
     <t>Date</t>
   </si>
@@ -1188,9 +1188,6 @@
   </si>
   <si>
     <t>448b</t>
-  </si>
-  <si>
-    <t>Tii</t>
   </si>
 </sst>
 </file>
@@ -11426,7 +11423,7 @@
         <v>381</v>
       </c>
       <c r="F182" s="10" t="s">
-        <v>382</v>
+        <v>142</v>
       </c>
       <c r="G182" s="10"/>
       <c r="H182" s="10"/>
@@ -11462,32 +11459,64 @@
       </c>
     </row>
     <row r="183" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A183" s="10"/>
-      <c r="B183" s="10"/>
-      <c r="C183" s="10"/>
-      <c r="D183" s="10"/>
-      <c r="E183" s="10"/>
-      <c r="F183" s="10"/>
+      <c r="A183" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B183" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C183" s="10" t="s">
+        <v>380</v>
+      </c>
+      <c r="D183" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E183" s="10" t="s">
+        <v>381</v>
+      </c>
+      <c r="F183" t="s">
+        <v>142</v>
+      </c>
       <c r="G183" s="10"/>
       <c r="H183" s="10"/>
       <c r="I183" s="10"/>
       <c r="J183" s="10"/>
-      <c r="K183" s="10"/>
+      <c r="K183" s="30"/>
       <c r="L183" s="10"/>
       <c r="M183" s="10"/>
       <c r="N183" s="10"/>
-      <c r="O183" s="10"/>
-      <c r="P183" s="10"/>
-      <c r="Q183" s="10"/>
-      <c r="R183" s="10"/>
-      <c r="S183" s="10"/>
-      <c r="T183" s="10"/>
-      <c r="U183" s="10"/>
-      <c r="V183" s="10"/>
+      <c r="O183" s="10">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="P183" s="10">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="Q183" s="10">
+        <v>15751.2</v>
+      </c>
+      <c r="R183" s="10">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="S183" s="10">
+        <v>0.60699999999999998</v>
+      </c>
+      <c r="T183" s="10">
+        <v>1</v>
+      </c>
+      <c r="U183" s="10">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="V183" s="10">
+        <v>0.55500000000000005</v>
+      </c>
     </row>
     <row r="184" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A184" s="10"/>
-      <c r="B184" s="10"/>
+      <c r="A184" s="13">
+        <v>46308</v>
+      </c>
+      <c r="B184" s="10" t="s">
+        <v>367</v>
+      </c>
       <c r="C184" s="10"/>
       <c r="D184" s="10"/>
       <c r="E184" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3306" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22EE77E3-CC00-42F2-86C3-07EB60C8EB60}"/>
+  <xr:revisionPtr revIDLastSave="3321" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B7AAC42-5D8C-4184-9371-35C436C2E53D}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="385">
   <si>
     <t>Date</t>
   </si>
@@ -1188,6 +1188,15 @@
   </si>
   <si>
     <t>448b</t>
+  </si>
+  <si>
+    <t>exaone-4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812 MB </t>
+  </si>
+  <si>
+    <t>LG AI Research</t>
   </si>
 </sst>
 </file>
@@ -11517,26 +11526,50 @@
       <c r="B184" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="C184" s="10"/>
-      <c r="D184" s="10"/>
-      <c r="E184" s="10"/>
-      <c r="F184" s="10"/>
+      <c r="C184" t="s">
+        <v>382</v>
+      </c>
+      <c r="D184" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E184" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="F184" t="s">
+        <v>384</v>
+      </c>
       <c r="G184" s="10"/>
       <c r="H184" s="10"/>
       <c r="I184" s="10"/>
       <c r="J184" s="10"/>
-      <c r="K184" s="10"/>
+      <c r="K184" s="30"/>
       <c r="L184" s="10"/>
       <c r="M184" s="10"/>
       <c r="N184" s="10"/>
-      <c r="O184" s="10"/>
-      <c r="P184" s="10"/>
-      <c r="Q184" s="10"/>
-      <c r="R184" s="10"/>
-      <c r="S184" s="10"/>
-      <c r="T184" s="10"/>
-      <c r="U184" s="10"/>
-      <c r="V184" s="10"/>
+      <c r="O184" s="10">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="P184" s="10">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="Q184" s="10">
+        <v>48734.2</v>
+      </c>
+      <c r="R184" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="S184" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="T184" s="10">
+        <v>1</v>
+      </c>
+      <c r="U184" s="10">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="V184" s="10">
+        <v>0.57699999999999996</v>
+      </c>
     </row>
     <row r="185" spans="1:22" ht="15.75" customHeight="1">
       <c r="A185" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3321" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4B7AAC42-5D8C-4184-9371-35C436C2E53D}"/>
+  <xr:revisionPtr revIDLastSave="3338" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{63FA85DA-DDA6-4946-A46C-0E2EA3933463}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1100" uniqueCount="385">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1105" uniqueCount="388">
   <si>
     <t>Date</t>
   </si>
@@ -1197,6 +1197,15 @@
   </si>
   <si>
     <t>LG AI Research</t>
+  </si>
+  <si>
+    <t>ernie-4.5</t>
+  </si>
+  <si>
+    <t>220mb</t>
+  </si>
+  <si>
+    <t>Baidu</t>
   </si>
 </sst>
 </file>
@@ -11572,28 +11581,56 @@
       </c>
     </row>
     <row r="185" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A185" s="10"/>
-      <c r="B185" s="10"/>
-      <c r="C185" s="10"/>
-      <c r="D185" s="10"/>
-      <c r="E185" s="10"/>
-      <c r="F185" s="10"/>
+      <c r="A185" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C185" t="s">
+        <v>385</v>
+      </c>
+      <c r="D185" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E185" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="F185" s="10" t="s">
+        <v>387</v>
+      </c>
       <c r="G185" s="10"/>
       <c r="H185" s="10"/>
       <c r="I185" s="10"/>
       <c r="J185" s="10"/>
-      <c r="K185" s="10"/>
+      <c r="K185" s="30"/>
       <c r="L185" s="10"/>
       <c r="M185" s="10"/>
       <c r="N185" s="10"/>
-      <c r="O185" s="10"/>
-      <c r="P185" s="10"/>
-      <c r="Q185" s="10"/>
-      <c r="R185" s="10"/>
-      <c r="S185" s="10"/>
-      <c r="T185" s="10"/>
-      <c r="U185" s="10"/>
-      <c r="V185" s="10"/>
+      <c r="O185" s="10">
+        <v>0.82</v>
+      </c>
+      <c r="P185" s="10">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="Q185" s="10">
+        <v>3049.23</v>
+      </c>
+      <c r="R185" s="10">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="S185" s="10">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="T185" s="10">
+        <v>1</v>
+      </c>
+      <c r="U185" s="10">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="V185" s="10">
+        <v>0.32700000000000001</v>
+      </c>
     </row>
     <row r="186" spans="1:22" ht="15.75" customHeight="1">
       <c r="A186" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3306" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22EE77E3-CC00-42F2-86C3-07EB60C8EB60}"/>
+  <xr:revisionPtr revIDLastSave="3344" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7B1043B-F1B2-425C-BC6B-F1495A41E143}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1096" uniqueCount="382">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="390">
   <si>
     <t>Date</t>
   </si>
@@ -1188,6 +1188,30 @@
   </si>
   <si>
     <t>448b</t>
+  </si>
+  <si>
+    <t>exaone-4.0</t>
+  </si>
+  <si>
+    <t xml:space="preserve">812 MB </t>
+  </si>
+  <si>
+    <t>LG AI Research</t>
+  </si>
+  <si>
+    <t>ernie-4.5</t>
+  </si>
+  <si>
+    <t>220mb</t>
+  </si>
+  <si>
+    <t>Baidu</t>
+  </si>
+  <si>
+    <t>lfm2-1.2b</t>
+  </si>
+  <si>
+    <t>730mb</t>
   </si>
 </sst>
 </file>
@@ -11517,58 +11541,122 @@
       <c r="B184" s="10" t="s">
         <v>367</v>
       </c>
-      <c r="C184" s="10"/>
-      <c r="D184" s="10"/>
-      <c r="E184" s="10"/>
-      <c r="F184" s="10"/>
+      <c r="C184" t="s">
+        <v>382</v>
+      </c>
+      <c r="D184" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E184" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="F184" t="s">
+        <v>384</v>
+      </c>
       <c r="G184" s="10"/>
       <c r="H184" s="10"/>
       <c r="I184" s="10"/>
       <c r="J184" s="10"/>
-      <c r="K184" s="10"/>
+      <c r="K184" s="30"/>
       <c r="L184" s="10"/>
       <c r="M184" s="10"/>
       <c r="N184" s="10"/>
-      <c r="O184" s="10"/>
-      <c r="P184" s="10"/>
-      <c r="Q184" s="10"/>
-      <c r="R184" s="10"/>
-      <c r="S184" s="10"/>
-      <c r="T184" s="10"/>
-      <c r="U184" s="10"/>
-      <c r="V184" s="10"/>
+      <c r="O184" s="10">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="P184" s="10">
+        <v>0.41199999999999998</v>
+      </c>
+      <c r="Q184" s="10">
+        <v>48734.2</v>
+      </c>
+      <c r="R184" s="10">
+        <v>0.53</v>
+      </c>
+      <c r="S184" s="10">
+        <v>0.63</v>
+      </c>
+      <c r="T184" s="10">
+        <v>1</v>
+      </c>
+      <c r="U184" s="10">
+        <v>0.86799999999999999</v>
+      </c>
+      <c r="V184" s="10">
+        <v>0.57699999999999996</v>
+      </c>
     </row>
     <row r="185" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A185" s="10"/>
-      <c r="B185" s="10"/>
-      <c r="C185" s="10"/>
-      <c r="D185" s="10"/>
-      <c r="E185" s="10"/>
-      <c r="F185" s="10"/>
+      <c r="A185" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B185" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C185" t="s">
+        <v>385</v>
+      </c>
+      <c r="D185" s="10" t="s">
+        <v>161</v>
+      </c>
+      <c r="E185" s="10" t="s">
+        <v>386</v>
+      </c>
+      <c r="F185" s="10" t="s">
+        <v>387</v>
+      </c>
       <c r="G185" s="10"/>
       <c r="H185" s="10"/>
       <c r="I185" s="10"/>
       <c r="J185" s="10"/>
-      <c r="K185" s="10"/>
+      <c r="K185" s="30"/>
       <c r="L185" s="10"/>
       <c r="M185" s="10"/>
       <c r="N185" s="10"/>
-      <c r="O185" s="10"/>
-      <c r="P185" s="10"/>
-      <c r="Q185" s="10"/>
-      <c r="R185" s="10"/>
-      <c r="S185" s="10"/>
-      <c r="T185" s="10"/>
-      <c r="U185" s="10"/>
-      <c r="V185" s="10"/>
+      <c r="O185" s="10">
+        <v>0.82</v>
+      </c>
+      <c r="P185" s="10">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="Q185" s="10">
+        <v>3049.23</v>
+      </c>
+      <c r="R185" s="10">
+        <v>0.36599999999999999</v>
+      </c>
+      <c r="S185" s="10">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="T185" s="10">
+        <v>1</v>
+      </c>
+      <c r="U185" s="10">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="V185" s="10">
+        <v>0.32700000000000001</v>
+      </c>
     </row>
     <row r="186" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A186" s="10"/>
-      <c r="B186" s="10"/>
-      <c r="C186" s="10"/>
-      <c r="D186" s="10"/>
-      <c r="E186" s="10"/>
-      <c r="F186" s="10"/>
+      <c r="A186" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B186" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C186" t="s">
+        <v>388</v>
+      </c>
+      <c r="D186" s="10" t="s">
+        <v>77</v>
+      </c>
+      <c r="E186" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="F186" s="10" t="s">
+        <v>79</v>
+      </c>
       <c r="G186" s="10"/>
       <c r="H186" s="10"/>
       <c r="I186" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3344" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A7B1043B-F1B2-425C-BC6B-F1495A41E143}"/>
+  <xr:revisionPtr revIDLastSave="3373" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B386C62F-F459-41AA-ADB4-E6252FD04AD4}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1110" uniqueCount="390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="393">
   <si>
     <t>Date</t>
   </si>
@@ -1212,6 +1212,15 @@
   </si>
   <si>
     <t>730mb</t>
+  </si>
+  <si>
+    <t>amd-olmo-1b-sft</t>
+  </si>
+  <si>
+    <t>479mb</t>
+  </si>
+  <si>
+    <t>AMD</t>
   </si>
 </sst>
 </file>
@@ -11661,42 +11670,86 @@
       <c r="H186" s="10"/>
       <c r="I186" s="10"/>
       <c r="J186" s="10"/>
-      <c r="K186" s="10"/>
+      <c r="K186" s="30"/>
       <c r="L186" s="10"/>
       <c r="M186" s="10"/>
       <c r="N186" s="10"/>
-      <c r="O186" s="10"/>
-      <c r="P186" s="10"/>
-      <c r="Q186" s="10"/>
-      <c r="R186" s="10"/>
-      <c r="S186" s="10"/>
-      <c r="T186" s="10"/>
-      <c r="U186" s="10"/>
-      <c r="V186" s="10"/>
+      <c r="O186" s="10">
+        <v>0.745</v>
+      </c>
+      <c r="P186" s="10">
+        <v>0.47399999999999998</v>
+      </c>
+      <c r="Q186" s="10">
+        <v>15360.2</v>
+      </c>
+      <c r="R186" s="10">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="S186" s="10">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="T186" s="10">
+        <v>0.9</v>
+      </c>
+      <c r="U186" s="10">
+        <v>0.90400000000000003</v>
+      </c>
+      <c r="V186" s="10">
+        <v>0.55500000000000005</v>
+      </c>
     </row>
     <row r="187" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A187" s="10"/>
-      <c r="B187" s="10"/>
-      <c r="C187" s="10"/>
-      <c r="D187" s="10"/>
-      <c r="E187" s="10"/>
-      <c r="F187" s="10"/>
+      <c r="A187" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B187" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C187" t="s">
+        <v>390</v>
+      </c>
+      <c r="D187" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="E187" s="10" t="s">
+        <v>391</v>
+      </c>
+      <c r="F187" s="10" t="s">
+        <v>392</v>
+      </c>
       <c r="G187" s="10"/>
       <c r="H187" s="10"/>
       <c r="I187" s="10"/>
       <c r="J187" s="10"/>
-      <c r="K187" s="10"/>
+      <c r="K187" s="30"/>
       <c r="L187" s="10"/>
       <c r="M187" s="10"/>
       <c r="N187" s="10"/>
-      <c r="O187" s="10"/>
-      <c r="P187" s="10"/>
-      <c r="Q187" s="10"/>
-      <c r="R187" s="10"/>
-      <c r="S187" s="10"/>
-      <c r="T187" s="10"/>
-      <c r="U187" s="10"/>
-      <c r="V187" s="10"/>
+      <c r="O187" s="10">
+        <v>0.33400000000000002</v>
+      </c>
+      <c r="P187" s="10">
+        <v>0.27500000000000002</v>
+      </c>
+      <c r="Q187" s="10">
+        <v>62537.2</v>
+      </c>
+      <c r="R187" s="10">
+        <v>0.42</v>
+      </c>
+      <c r="S187" s="10">
+        <v>0.67400000000000004</v>
+      </c>
+      <c r="T187" s="10">
+        <v>1</v>
+      </c>
+      <c r="U187" s="10">
+        <v>0.58399999999999996</v>
+      </c>
+      <c r="V187" s="10">
+        <v>0.38200000000000001</v>
+      </c>
     </row>
     <row r="188" spans="1:22" ht="15.75" customHeight="1">
       <c r="A188" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3373" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B386C62F-F459-41AA-ADB4-E6252FD04AD4}"/>
+  <xr:revisionPtr revIDLastSave="3443" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{050E558B-6D54-4ED9-BB3B-359CC22D3728}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="408">
   <si>
     <t>Date</t>
   </si>
@@ -1221,6 +1221,51 @@
   </si>
   <si>
     <t>AMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soumya </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> functiongemma</t>
+  </si>
+  <si>
+    <t>270M (0.27B)</t>
+  </si>
+  <si>
+    <t>300 MB</t>
+  </si>
+  <si>
+    <t>2,724.71 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ananya </t>
+  </si>
+  <si>
+    <t>stablelm2:1</t>
+  </si>
+  <si>
+    <t>1.6 Billion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8 GB </t>
+  </si>
+  <si>
+    <t>15,399.90 ms</t>
+  </si>
+  <si>
+    <t>qwen2:0.5b-instruct</t>
+  </si>
+  <si>
+    <t>0.494B</t>
+  </si>
+  <si>
+    <t>440 MB</t>
+  </si>
+  <si>
+    <t>Alibaba Cloud</t>
+  </si>
+  <si>
+    <t>4,230.32 ms</t>
   </si>
 </sst>
 </file>
@@ -11752,12 +11797,24 @@
       </c>
     </row>
     <row r="188" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A188" s="10"/>
-      <c r="B188" s="10"/>
-      <c r="C188" s="10"/>
-      <c r="D188" s="10"/>
-      <c r="E188" s="10"/>
-      <c r="F188" s="10"/>
+      <c r="A188" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D188" t="s">
+        <v>395</v>
+      </c>
+      <c r="E188" t="s">
+        <v>396</v>
+      </c>
+      <c r="F188" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="G188" s="10"/>
       <c r="H188" s="10"/>
       <c r="I188" s="10"/>
@@ -11765,63 +11822,135 @@
       <c r="K188" s="10"/>
       <c r="L188" s="10"/>
       <c r="M188" s="10"/>
-      <c r="N188" s="10"/>
-      <c r="O188" s="10"/>
-      <c r="P188" s="10"/>
-      <c r="Q188" s="10"/>
-      <c r="R188" s="10"/>
-      <c r="S188" s="10"/>
-      <c r="T188" s="10"/>
-      <c r="U188" s="10"/>
-      <c r="V188" s="10"/>
+      <c r="N188" s="30"/>
+      <c r="O188">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="P188">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>397</v>
+      </c>
+      <c r="R188">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="S188">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="T188">
+        <v>1</v>
+      </c>
+      <c r="U188">
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="V188">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="189" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A189" s="10"/>
-      <c r="B189" s="10"/>
-      <c r="C189" s="10"/>
-      <c r="D189" s="10"/>
-      <c r="E189" s="10"/>
-      <c r="F189" s="10"/>
+      <c r="A189" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C189" t="s">
+        <v>399</v>
+      </c>
+      <c r="D189" t="s">
+        <v>400</v>
+      </c>
+      <c r="E189" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="F189" t="s">
+        <v>88</v>
+      </c>
       <c r="G189" s="10"/>
       <c r="H189" s="10"/>
       <c r="I189" s="10"/>
       <c r="J189" s="10"/>
-      <c r="K189" s="10"/>
+      <c r="K189" s="30"/>
       <c r="L189" s="10"/>
       <c r="M189" s="10"/>
       <c r="N189" s="10"/>
-      <c r="O189" s="10"/>
-      <c r="P189" s="10"/>
-      <c r="Q189" s="10"/>
-      <c r="R189" s="10"/>
-      <c r="S189" s="10"/>
-      <c r="T189" s="10"/>
-      <c r="U189" s="10"/>
-      <c r="V189" s="10"/>
+      <c r="O189">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="P189">
+        <v>0.5</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>402</v>
+      </c>
+      <c r="R189">
+        <v>0.6</v>
+      </c>
+      <c r="S189">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="T189">
+        <v>1</v>
+      </c>
+      <c r="U189">
+        <v>0.85</v>
+      </c>
+      <c r="V189">
+        <v>0.56100000000000005</v>
+      </c>
     </row>
     <row r="190" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A190" s="10"/>
-      <c r="B190" s="10"/>
-      <c r="C190" s="10"/>
-      <c r="D190" s="10"/>
-      <c r="E190" s="10"/>
-      <c r="F190" s="10"/>
+      <c r="A190" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C190" t="s">
+        <v>403</v>
+      </c>
+      <c r="D190" t="s">
+        <v>404</v>
+      </c>
+      <c r="E190" t="s">
+        <v>405</v>
+      </c>
+      <c r="F190" t="s">
+        <v>406</v>
+      </c>
       <c r="G190" s="10"/>
       <c r="H190" s="10"/>
       <c r="I190" s="10"/>
       <c r="J190" s="10"/>
-      <c r="K190" s="10"/>
+      <c r="K190" s="30"/>
       <c r="L190" s="10"/>
       <c r="M190" s="10"/>
       <c r="N190" s="10"/>
-      <c r="O190" s="10"/>
-      <c r="P190" s="10"/>
-      <c r="Q190" s="10"/>
-      <c r="R190" s="10"/>
-      <c r="S190" s="10"/>
-      <c r="T190" s="10"/>
-      <c r="U190" s="10"/>
-      <c r="V190" s="10"/>
+      <c r="O190">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="P190">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>407</v>
+      </c>
+      <c r="R190">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="S190">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="T190">
+        <v>1</v>
+      </c>
+      <c r="U190">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="V190">
+        <v>0.54900000000000004</v>
+      </c>
     </row>
     <row r="191" spans="1:22" ht="15.75" customHeight="1">
       <c r="A191" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3443" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{050E558B-6D54-4ED9-BB3B-359CC22D3728}"/>
+  <xr:revisionPtr revIDLastSave="3468" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{931C1623-46F7-4D57-A494-2980F62ED4A7}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1133" uniqueCount="408">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="413">
   <si>
     <t>Date</t>
   </si>
@@ -1266,6 +1266,21 @@
   </si>
   <si>
     <t>4,230.32 ms</t>
+  </si>
+  <si>
+    <t>gemma3:1b</t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 883 MB </t>
+  </si>
+  <si>
+    <t>hunyuan-0.5b-instruct</t>
+  </si>
+  <si>
+    <t>320mb</t>
   </si>
 </sst>
 </file>
@@ -11953,12 +11968,24 @@
       </c>
     </row>
     <row r="191" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A191" s="10"/>
-      <c r="B191" s="10"/>
-      <c r="C191" s="10"/>
-      <c r="D191" s="10"/>
-      <c r="E191" s="10"/>
-      <c r="F191" s="10"/>
+      <c r="A191" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C191" t="s">
+        <v>408</v>
+      </c>
+      <c r="D191" t="s">
+        <v>409</v>
+      </c>
+      <c r="E191" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="F191" t="s">
+        <v>74</v>
+      </c>
       <c r="G191" s="10"/>
       <c r="H191" s="10"/>
       <c r="I191" s="10"/>
@@ -11977,28 +12004,56 @@
       <c r="V191" s="10"/>
     </row>
     <row r="192" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A192" s="10"/>
-      <c r="B192" s="10"/>
-      <c r="C192" s="10"/>
-      <c r="D192" s="10"/>
-      <c r="E192" s="10"/>
-      <c r="F192" s="10"/>
+      <c r="A192" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C192" t="s">
+        <v>411</v>
+      </c>
+      <c r="D192" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>208</v>
+      </c>
       <c r="G192" s="10"/>
       <c r="H192" s="10"/>
       <c r="I192" s="10"/>
       <c r="J192" s="10"/>
-      <c r="K192" s="10"/>
+      <c r="K192" s="30"/>
       <c r="L192" s="10"/>
       <c r="M192" s="10"/>
       <c r="N192" s="10"/>
-      <c r="O192" s="10"/>
-      <c r="P192" s="10"/>
-      <c r="Q192" s="10"/>
-      <c r="R192" s="10"/>
-      <c r="S192" s="10"/>
-      <c r="T192" s="10"/>
-      <c r="U192" s="10"/>
-      <c r="V192" s="10"/>
+      <c r="O192" s="10">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="P192" s="10">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="Q192" s="10">
+        <v>29509.200000000001</v>
+      </c>
+      <c r="R192" s="10">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="S192" s="10">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="T192" s="10">
+        <v>1</v>
+      </c>
+      <c r="U192" s="10">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="V192" s="10">
+        <v>0.54300000000000004</v>
+      </c>
     </row>
     <row r="193" spans="1:22" ht="15.75" customHeight="1">
       <c r="A193" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3373" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B386C62F-F459-41AA-ADB4-E6252FD04AD4}"/>
+  <xr:revisionPtr revIDLastSave="3468" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{931C1623-46F7-4D57-A494-2980F62ED4A7}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="413">
   <si>
     <t>Date</t>
   </si>
@@ -1221,6 +1221,66 @@
   </si>
   <si>
     <t>AMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soumya </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> functiongemma</t>
+  </si>
+  <si>
+    <t>270M (0.27B)</t>
+  </si>
+  <si>
+    <t>300 MB</t>
+  </si>
+  <si>
+    <t>2,724.71 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ananya </t>
+  </si>
+  <si>
+    <t>stablelm2:1</t>
+  </si>
+  <si>
+    <t>1.6 Billion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8 GB </t>
+  </si>
+  <si>
+    <t>15,399.90 ms</t>
+  </si>
+  <si>
+    <t>qwen2:0.5b-instruct</t>
+  </si>
+  <si>
+    <t>0.494B</t>
+  </si>
+  <si>
+    <t>440 MB</t>
+  </si>
+  <si>
+    <t>Alibaba Cloud</t>
+  </si>
+  <si>
+    <t>4,230.32 ms</t>
+  </si>
+  <si>
+    <t>gemma3:1b</t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 883 MB </t>
+  </si>
+  <si>
+    <t>hunyuan-0.5b-instruct</t>
+  </si>
+  <si>
+    <t>320mb</t>
   </si>
 </sst>
 </file>
@@ -11752,12 +11812,24 @@
       </c>
     </row>
     <row r="188" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A188" s="10"/>
-      <c r="B188" s="10"/>
-      <c r="C188" s="10"/>
-      <c r="D188" s="10"/>
-      <c r="E188" s="10"/>
-      <c r="F188" s="10"/>
+      <c r="A188" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D188" t="s">
+        <v>395</v>
+      </c>
+      <c r="E188" t="s">
+        <v>396</v>
+      </c>
+      <c r="F188" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="G188" s="10"/>
       <c r="H188" s="10"/>
       <c r="I188" s="10"/>
@@ -11765,71 +11837,155 @@
       <c r="K188" s="10"/>
       <c r="L188" s="10"/>
       <c r="M188" s="10"/>
-      <c r="N188" s="10"/>
-      <c r="O188" s="10"/>
-      <c r="P188" s="10"/>
-      <c r="Q188" s="10"/>
-      <c r="R188" s="10"/>
-      <c r="S188" s="10"/>
-      <c r="T188" s="10"/>
-      <c r="U188" s="10"/>
-      <c r="V188" s="10"/>
+      <c r="N188" s="30"/>
+      <c r="O188">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="P188">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>397</v>
+      </c>
+      <c r="R188">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="S188">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="T188">
+        <v>1</v>
+      </c>
+      <c r="U188">
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="V188">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="189" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A189" s="10"/>
-      <c r="B189" s="10"/>
-      <c r="C189" s="10"/>
-      <c r="D189" s="10"/>
-      <c r="E189" s="10"/>
-      <c r="F189" s="10"/>
+      <c r="A189" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C189" t="s">
+        <v>399</v>
+      </c>
+      <c r="D189" t="s">
+        <v>400</v>
+      </c>
+      <c r="E189" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="F189" t="s">
+        <v>88</v>
+      </c>
       <c r="G189" s="10"/>
       <c r="H189" s="10"/>
       <c r="I189" s="10"/>
       <c r="J189" s="10"/>
-      <c r="K189" s="10"/>
+      <c r="K189" s="30"/>
       <c r="L189" s="10"/>
       <c r="M189" s="10"/>
       <c r="N189" s="10"/>
-      <c r="O189" s="10"/>
-      <c r="P189" s="10"/>
-      <c r="Q189" s="10"/>
-      <c r="R189" s="10"/>
-      <c r="S189" s="10"/>
-      <c r="T189" s="10"/>
-      <c r="U189" s="10"/>
-      <c r="V189" s="10"/>
+      <c r="O189">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="P189">
+        <v>0.5</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>402</v>
+      </c>
+      <c r="R189">
+        <v>0.6</v>
+      </c>
+      <c r="S189">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="T189">
+        <v>1</v>
+      </c>
+      <c r="U189">
+        <v>0.85</v>
+      </c>
+      <c r="V189">
+        <v>0.56100000000000005</v>
+      </c>
     </row>
     <row r="190" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A190" s="10"/>
-      <c r="B190" s="10"/>
-      <c r="C190" s="10"/>
-      <c r="D190" s="10"/>
-      <c r="E190" s="10"/>
-      <c r="F190" s="10"/>
+      <c r="A190" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C190" t="s">
+        <v>403</v>
+      </c>
+      <c r="D190" t="s">
+        <v>404</v>
+      </c>
+      <c r="E190" t="s">
+        <v>405</v>
+      </c>
+      <c r="F190" t="s">
+        <v>406</v>
+      </c>
       <c r="G190" s="10"/>
       <c r="H190" s="10"/>
       <c r="I190" s="10"/>
       <c r="J190" s="10"/>
-      <c r="K190" s="10"/>
+      <c r="K190" s="30"/>
       <c r="L190" s="10"/>
       <c r="M190" s="10"/>
       <c r="N190" s="10"/>
-      <c r="O190" s="10"/>
-      <c r="P190" s="10"/>
-      <c r="Q190" s="10"/>
-      <c r="R190" s="10"/>
-      <c r="S190" s="10"/>
-      <c r="T190" s="10"/>
-      <c r="U190" s="10"/>
-      <c r="V190" s="10"/>
+      <c r="O190">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="P190">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>407</v>
+      </c>
+      <c r="R190">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="S190">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="T190">
+        <v>1</v>
+      </c>
+      <c r="U190">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="V190">
+        <v>0.54900000000000004</v>
+      </c>
     </row>
     <row r="191" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A191" s="10"/>
-      <c r="B191" s="10"/>
-      <c r="C191" s="10"/>
-      <c r="D191" s="10"/>
-      <c r="E191" s="10"/>
-      <c r="F191" s="10"/>
+      <c r="A191" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C191" t="s">
+        <v>408</v>
+      </c>
+      <c r="D191" t="s">
+        <v>409</v>
+      </c>
+      <c r="E191" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="F191" t="s">
+        <v>74</v>
+      </c>
       <c r="G191" s="10"/>
       <c r="H191" s="10"/>
       <c r="I191" s="10"/>
@@ -11848,28 +12004,56 @@
       <c r="V191" s="10"/>
     </row>
     <row r="192" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A192" s="10"/>
-      <c r="B192" s="10"/>
-      <c r="C192" s="10"/>
-      <c r="D192" s="10"/>
-      <c r="E192" s="10"/>
-      <c r="F192" s="10"/>
+      <c r="A192" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C192" t="s">
+        <v>411</v>
+      </c>
+      <c r="D192" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>208</v>
+      </c>
       <c r="G192" s="10"/>
       <c r="H192" s="10"/>
       <c r="I192" s="10"/>
       <c r="J192" s="10"/>
-      <c r="K192" s="10"/>
+      <c r="K192" s="30"/>
       <c r="L192" s="10"/>
       <c r="M192" s="10"/>
       <c r="N192" s="10"/>
-      <c r="O192" s="10"/>
-      <c r="P192" s="10"/>
-      <c r="Q192" s="10"/>
-      <c r="R192" s="10"/>
-      <c r="S192" s="10"/>
-      <c r="T192" s="10"/>
-      <c r="U192" s="10"/>
-      <c r="V192" s="10"/>
+      <c r="O192" s="10">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="P192" s="10">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="Q192" s="10">
+        <v>29509.200000000001</v>
+      </c>
+      <c r="R192" s="10">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="S192" s="10">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="T192" s="10">
+        <v>1</v>
+      </c>
+      <c r="U192" s="10">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="V192" s="10">
+        <v>0.54300000000000004</v>
+      </c>
     </row>
     <row r="193" spans="1:22" ht="15.75" customHeight="1">
       <c r="A193" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30606"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3373" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{B386C62F-F459-41AA-ADB4-E6252FD04AD4}"/>
+  <xr:revisionPtr revIDLastSave="3470" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{361B1619-D51C-4D88-AE4C-082256B67C2B}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1115" uniqueCount="393">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="414">
   <si>
     <t>Date</t>
   </si>
@@ -1221,6 +1221,69 @@
   </si>
   <si>
     <t>AMD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Soumya </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> functiongemma</t>
+  </si>
+  <si>
+    <t>270M (0.27B)</t>
+  </si>
+  <si>
+    <t>300 MB</t>
+  </si>
+  <si>
+    <t>2,724.71 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ananya </t>
+  </si>
+  <si>
+    <t>stablelm2:1</t>
+  </si>
+  <si>
+    <t>1.6 Billion</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.8 GB </t>
+  </si>
+  <si>
+    <t>15,399.90 ms</t>
+  </si>
+  <si>
+    <t>qwen2:0.5b-instruct</t>
+  </si>
+  <si>
+    <t>0.494B</t>
+  </si>
+  <si>
+    <t>440 MB</t>
+  </si>
+  <si>
+    <t>Alibaba Cloud</t>
+  </si>
+  <si>
+    <t>4,230.32 ms</t>
+  </si>
+  <si>
+    <t>gemma3:1b</t>
+  </si>
+  <si>
+    <t>1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 883 MB </t>
+  </si>
+  <si>
+    <t>27,340.11 ms</t>
+  </si>
+  <si>
+    <t>hunyuan-0.5b-instruct</t>
+  </si>
+  <si>
+    <t>320mb</t>
   </si>
 </sst>
 </file>
@@ -11752,12 +11815,24 @@
       </c>
     </row>
     <row r="188" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A188" s="10"/>
-      <c r="B188" s="10"/>
-      <c r="C188" s="10"/>
-      <c r="D188" s="10"/>
-      <c r="E188" s="10"/>
-      <c r="F188" s="10"/>
+      <c r="A188" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B188" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C188" s="10" t="s">
+        <v>394</v>
+      </c>
+      <c r="D188" t="s">
+        <v>395</v>
+      </c>
+      <c r="E188" t="s">
+        <v>396</v>
+      </c>
+      <c r="F188" s="10" t="s">
+        <v>74</v>
+      </c>
       <c r="G188" s="10"/>
       <c r="H188" s="10"/>
       <c r="I188" s="10"/>
@@ -11765,111 +11840,239 @@
       <c r="K188" s="10"/>
       <c r="L188" s="10"/>
       <c r="M188" s="10"/>
-      <c r="N188" s="10"/>
-      <c r="O188" s="10"/>
-      <c r="P188" s="10"/>
-      <c r="Q188" s="10"/>
-      <c r="R188" s="10"/>
-      <c r="S188" s="10"/>
-      <c r="T188" s="10"/>
-      <c r="U188" s="10"/>
-      <c r="V188" s="10"/>
+      <c r="N188" s="30"/>
+      <c r="O188">
+        <v>0.17100000000000001</v>
+      </c>
+      <c r="P188">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="Q188" t="s">
+        <v>397</v>
+      </c>
+      <c r="R188">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="S188">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="T188">
+        <v>1</v>
+      </c>
+      <c r="U188">
+        <v>0.77600000000000002</v>
+      </c>
+      <c r="V188">
+        <v>0.44</v>
+      </c>
     </row>
     <row r="189" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A189" s="10"/>
-      <c r="B189" s="10"/>
-      <c r="C189" s="10"/>
-      <c r="D189" s="10"/>
-      <c r="E189" s="10"/>
-      <c r="F189" s="10"/>
+      <c r="A189" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B189" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C189" t="s">
+        <v>399</v>
+      </c>
+      <c r="D189" t="s">
+        <v>400</v>
+      </c>
+      <c r="E189" s="10" t="s">
+        <v>401</v>
+      </c>
+      <c r="F189" t="s">
+        <v>88</v>
+      </c>
       <c r="G189" s="10"/>
       <c r="H189" s="10"/>
       <c r="I189" s="10"/>
       <c r="J189" s="10"/>
-      <c r="K189" s="10"/>
+      <c r="K189" s="30"/>
       <c r="L189" s="10"/>
       <c r="M189" s="10"/>
       <c r="N189" s="10"/>
-      <c r="O189" s="10"/>
-      <c r="P189" s="10"/>
-      <c r="Q189" s="10"/>
-      <c r="R189" s="10"/>
-      <c r="S189" s="10"/>
-      <c r="T189" s="10"/>
-      <c r="U189" s="10"/>
-      <c r="V189" s="10"/>
+      <c r="O189">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="P189">
+        <v>0.5</v>
+      </c>
+      <c r="Q189" t="s">
+        <v>402</v>
+      </c>
+      <c r="R189">
+        <v>0.6</v>
+      </c>
+      <c r="S189">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="T189">
+        <v>1</v>
+      </c>
+      <c r="U189">
+        <v>0.85</v>
+      </c>
+      <c r="V189">
+        <v>0.56100000000000005</v>
+      </c>
     </row>
     <row r="190" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A190" s="10"/>
-      <c r="B190" s="10"/>
-      <c r="C190" s="10"/>
-      <c r="D190" s="10"/>
-      <c r="E190" s="10"/>
-      <c r="F190" s="10"/>
+      <c r="A190" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B190" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C190" t="s">
+        <v>403</v>
+      </c>
+      <c r="D190" t="s">
+        <v>404</v>
+      </c>
+      <c r="E190" t="s">
+        <v>405</v>
+      </c>
+      <c r="F190" t="s">
+        <v>406</v>
+      </c>
       <c r="G190" s="10"/>
       <c r="H190" s="10"/>
       <c r="I190" s="10"/>
       <c r="J190" s="10"/>
-      <c r="K190" s="10"/>
+      <c r="K190" s="30"/>
       <c r="L190" s="10"/>
       <c r="M190" s="10"/>
       <c r="N190" s="10"/>
-      <c r="O190" s="10"/>
-      <c r="P190" s="10"/>
-      <c r="Q190" s="10"/>
-      <c r="R190" s="10"/>
-      <c r="S190" s="10"/>
-      <c r="T190" s="10"/>
-      <c r="U190" s="10"/>
-      <c r="V190" s="10"/>
+      <c r="O190">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="P190">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="Q190" t="s">
+        <v>407</v>
+      </c>
+      <c r="R190">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="S190">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="T190">
+        <v>1</v>
+      </c>
+      <c r="U190">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="V190">
+        <v>0.54900000000000004</v>
+      </c>
     </row>
     <row r="191" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A191" s="10"/>
-      <c r="B191" s="10"/>
-      <c r="C191" s="10"/>
-      <c r="D191" s="10"/>
-      <c r="E191" s="10"/>
-      <c r="F191" s="10"/>
+      <c r="A191" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B191" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C191" t="s">
+        <v>408</v>
+      </c>
+      <c r="D191" t="s">
+        <v>409</v>
+      </c>
+      <c r="E191" s="10" t="s">
+        <v>410</v>
+      </c>
+      <c r="F191" t="s">
+        <v>74</v>
+      </c>
       <c r="G191" s="10"/>
       <c r="H191" s="10"/>
       <c r="I191" s="10"/>
       <c r="J191" s="10"/>
-      <c r="K191" s="10"/>
+      <c r="K191" s="30"/>
       <c r="L191" s="10"/>
       <c r="M191" s="10"/>
       <c r="N191" s="10"/>
-      <c r="O191" s="10"/>
-      <c r="P191" s="10"/>
-      <c r="Q191" s="10"/>
-      <c r="R191" s="10"/>
-      <c r="S191" s="10"/>
-      <c r="T191" s="10"/>
-      <c r="U191" s="10"/>
-      <c r="V191" s="10"/>
+      <c r="O191">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="P191">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>411</v>
+      </c>
+      <c r="R191">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="S191">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="T191">
+        <v>0.97</v>
+      </c>
+      <c r="U191">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="V191">
+        <v>0.57799999999999996</v>
+      </c>
     </row>
     <row r="192" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A192" s="10"/>
-      <c r="B192" s="10"/>
-      <c r="C192" s="10"/>
-      <c r="D192" s="10"/>
-      <c r="E192" s="10"/>
-      <c r="F192" s="10"/>
+      <c r="A192" s="13">
+        <v>46309</v>
+      </c>
+      <c r="B192" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C192" t="s">
+        <v>412</v>
+      </c>
+      <c r="D192" s="10" t="s">
+        <v>53</v>
+      </c>
+      <c r="E192" s="10" t="s">
+        <v>413</v>
+      </c>
+      <c r="F192" s="10" t="s">
+        <v>208</v>
+      </c>
       <c r="G192" s="10"/>
       <c r="H192" s="10"/>
       <c r="I192" s="10"/>
       <c r="J192" s="10"/>
-      <c r="K192" s="10"/>
+      <c r="K192" s="30"/>
       <c r="L192" s="10"/>
       <c r="M192" s="10"/>
       <c r="N192" s="10"/>
-      <c r="O192" s="10"/>
-      <c r="P192" s="10"/>
-      <c r="Q192" s="10"/>
-      <c r="R192" s="10"/>
-      <c r="S192" s="10"/>
-      <c r="T192" s="10"/>
-      <c r="U192" s="10"/>
-      <c r="V192" s="10"/>
+      <c r="O192" s="10">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="P192" s="10">
+        <v>0.38300000000000001</v>
+      </c>
+      <c r="Q192" s="10">
+        <v>29509.200000000001</v>
+      </c>
+      <c r="R192" s="10">
+        <v>0.50600000000000001</v>
+      </c>
+      <c r="S192" s="10">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="T192" s="10">
+        <v>1</v>
+      </c>
+      <c r="U192" s="10">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="V192" s="10">
+        <v>0.54300000000000004</v>
+      </c>
     </row>
     <row r="193" spans="1:22" ht="15.75" customHeight="1">
       <c r="A193" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3470" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{361B1619-D51C-4D88-AE4C-082256B67C2B}"/>
+  <xr:revisionPtr revIDLastSave="3485" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01BFD835-7A02-4109-AE4E-9FCAB74BD136}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1144" uniqueCount="414">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="416">
   <si>
     <t>Date</t>
   </si>
@@ -1284,6 +1284,12 @@
   </si>
   <si>
     <t>320mb</t>
+  </si>
+  <si>
+    <t>llama3.2:1b-instruct-q5_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800MB </t>
   </si>
 </sst>
 </file>
@@ -2166,7 +2172,7 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="26.75" customWidth="1"/>
     <col min="6" max="6" width="13.25" customWidth="1"/>
     <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.625" bestFit="1" customWidth="1"/>
@@ -12075,12 +12081,22 @@
       </c>
     </row>
     <row r="193" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A193" s="10"/>
-      <c r="B193" s="10"/>
-      <c r="C193" s="10"/>
+      <c r="A193" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B193" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C193" t="s">
+        <v>414</v>
+      </c>
       <c r="D193" s="10"/>
-      <c r="E193" s="10"/>
-      <c r="F193" s="10"/>
+      <c r="E193" s="10" t="s">
+        <v>415</v>
+      </c>
+      <c r="F193" t="s">
+        <v>43</v>
+      </c>
       <c r="G193" s="10"/>
       <c r="H193" s="10"/>
       <c r="I193" s="10"/>
@@ -12088,20 +12104,35 @@
       <c r="K193" s="10"/>
       <c r="L193" s="10"/>
       <c r="M193" s="10"/>
-      <c r="N193" s="10"/>
-      <c r="O193" s="10"/>
-      <c r="P193" s="10"/>
-      <c r="Q193" s="10"/>
-      <c r="R193" s="10"/>
-      <c r="S193" s="10"/>
-      <c r="T193" s="10"/>
-      <c r="U193" s="10"/>
-      <c r="V193" s="10"/>
+      <c r="N193" s="30"/>
+      <c r="O193">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="P193">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>411</v>
+      </c>
+      <c r="R193">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="S193">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="T193">
+        <v>0.97</v>
+      </c>
+      <c r="U193">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="V193">
+        <v>0.57799999999999996</v>
+      </c>
     </row>
     <row r="194" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A194" s="10"/>
+      <c r="A194" s="13"/>
       <c r="B194" s="10"/>
-      <c r="C194" s="10"/>
       <c r="D194" s="10"/>
       <c r="E194" s="10"/>
       <c r="F194" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3468" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{931C1623-46F7-4D57-A494-2980F62ED4A7}"/>
+  <xr:revisionPtr revIDLastSave="3534" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6CD8006-C572-4464-975F-7E2E8CE82CD8}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1143" uniqueCount="413">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="427">
   <si>
     <t>Date</t>
   </si>
@@ -1277,17 +1277,59 @@
     <t xml:space="preserve"> 883 MB </t>
   </si>
   <si>
+    <t>27,340.11 ms</t>
+  </si>
+  <si>
     <t>hunyuan-0.5b-instruct</t>
   </si>
   <si>
     <t>320mb</t>
+  </si>
+  <si>
+    <t>llama3.2:1b-instruct-q5_K_M</t>
+  </si>
+  <si>
+    <t>1.24B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">800MB </t>
+  </si>
+  <si>
+    <t>qwen:0.5b</t>
+  </si>
+  <si>
+    <t>0.5B</t>
+  </si>
+  <si>
+    <t>500M</t>
+  </si>
+  <si>
+    <t>3,421.81 ms</t>
+  </si>
+  <si>
+    <t>486 MB</t>
+  </si>
+  <si>
+    <t>7,614.12 ms</t>
+  </si>
+  <si>
+    <t>babar_jamali/gemma3-abliterated-</t>
+  </si>
+  <si>
+    <t>806 MB</t>
+  </si>
+  <si>
+    <t>Community fine-tune based on Google Gemma 3</t>
+  </si>
+  <si>
+    <t>22,438.57 ms</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1321,6 +1363,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1367,7 +1415,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1733,11 +1781,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1774,6 +1848,9 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2163,7 +2240,7 @@
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
-    <col min="3" max="3" width="16" customWidth="1"/>
+    <col min="3" max="3" width="26.75" customWidth="1"/>
     <col min="6" max="6" width="13.25" customWidth="1"/>
     <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.625" bestFit="1" customWidth="1"/>
@@ -2174,70 +2251,70 @@
   <sheetData>
     <row r="1" spans="1:22"/>
     <row r="2" spans="1:22" ht="21">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="45" t="s">
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="39" t="s">
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="40"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="43"/>
     </row>
     <row r="3" spans="1:22" ht="18.75">
-      <c r="A3" s="35"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="37" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37" t="s">
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="37"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="38"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="41"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="11" t="s">
         <v>7</v>
       </c>
@@ -11818,7 +11895,7 @@
       <c r="B188" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C188" s="10" t="s">
+      <c r="C188" s="26" t="s">
         <v>394</v>
       </c>
       <c r="D188" t="s">
@@ -11867,10 +11944,10 @@
       <c r="A189" s="13">
         <v>46309</v>
       </c>
-      <c r="B189" s="10" t="s">
+      <c r="B189" s="34" t="s">
         <v>398</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="10" t="s">
         <v>399</v>
       </c>
       <c r="D189" t="s">
@@ -11919,10 +11996,10 @@
       <c r="A190" s="13">
         <v>46309</v>
       </c>
-      <c r="B190" s="10" t="s">
+      <c r="B190" s="34" t="s">
         <v>398</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C190" s="10" t="s">
         <v>403</v>
       </c>
       <c r="D190" t="s">
@@ -11971,10 +12048,10 @@
       <c r="A191" s="13">
         <v>46309</v>
       </c>
-      <c r="B191" s="10" t="s">
+      <c r="B191" s="34" t="s">
         <v>393</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C191" s="10" t="s">
         <v>408</v>
       </c>
       <c r="D191" t="s">
@@ -11990,34 +12067,50 @@
       <c r="H191" s="10"/>
       <c r="I191" s="10"/>
       <c r="J191" s="10"/>
-      <c r="K191" s="10"/>
+      <c r="K191" s="30"/>
       <c r="L191" s="10"/>
       <c r="M191" s="10"/>
       <c r="N191" s="10"/>
-      <c r="O191" s="10"/>
-      <c r="P191" s="10"/>
-      <c r="Q191" s="10"/>
-      <c r="R191" s="10"/>
-      <c r="S191" s="10"/>
-      <c r="T191" s="10"/>
-      <c r="U191" s="10"/>
-      <c r="V191" s="10"/>
+      <c r="O191">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="P191">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="Q191" t="s">
+        <v>411</v>
+      </c>
+      <c r="R191">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="S191">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="T191">
+        <v>0.97</v>
+      </c>
+      <c r="U191">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="V191">
+        <v>0.57799999999999996</v>
+      </c>
     </row>
     <row r="192" spans="1:22" ht="15.75" customHeight="1">
       <c r="A192" s="13">
         <v>46309</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="B192" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="C192" t="s">
-        <v>411</v>
-      </c>
-      <c r="D192" s="10" t="s">
+      <c r="C192" s="10" t="s">
+        <v>412</v>
+      </c>
+      <c r="D192" s="35" t="s">
         <v>53</v>
       </c>
       <c r="E192" s="10" t="s">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="F192" s="10" t="s">
         <v>208</v>
@@ -12056,12 +12149,24 @@
       </c>
     </row>
     <row r="193" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A193" s="10"/>
-      <c r="B193" s="10"/>
-      <c r="C193" s="10"/>
-      <c r="D193" s="10"/>
-      <c r="E193" s="10"/>
-      <c r="F193" s="10"/>
+      <c r="A193" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B193" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="C193" s="10" t="s">
+        <v>414</v>
+      </c>
+      <c r="D193" t="s">
+        <v>415</v>
+      </c>
+      <c r="E193" s="10" t="s">
+        <v>416</v>
+      </c>
+      <c r="F193" t="s">
+        <v>43</v>
+      </c>
       <c r="G193" s="10"/>
       <c r="H193" s="10"/>
       <c r="I193" s="10"/>
@@ -12069,23 +12174,51 @@
       <c r="K193" s="10"/>
       <c r="L193" s="10"/>
       <c r="M193" s="10"/>
-      <c r="N193" s="10"/>
-      <c r="O193" s="10"/>
-      <c r="P193" s="10"/>
-      <c r="Q193" s="10"/>
-      <c r="R193" s="10"/>
-      <c r="S193" s="10"/>
-      <c r="T193" s="10"/>
-      <c r="U193" s="10"/>
-      <c r="V193" s="10"/>
+      <c r="N193" s="30"/>
+      <c r="O193">
+        <v>0.66100000000000003</v>
+      </c>
+      <c r="P193">
+        <v>0.63100000000000001</v>
+      </c>
+      <c r="Q193" t="s">
+        <v>411</v>
+      </c>
+      <c r="R193">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="S193">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="T193">
+        <v>0.97</v>
+      </c>
+      <c r="U193">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="V193">
+        <v>0.57799999999999996</v>
+      </c>
     </row>
     <row r="194" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A194" s="10"/>
-      <c r="B194" s="10"/>
-      <c r="C194" s="10"/>
-      <c r="D194" s="10"/>
-      <c r="E194" s="10"/>
-      <c r="F194" s="10"/>
+      <c r="A194" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B194" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="C194" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="D194" t="s">
+        <v>418</v>
+      </c>
+      <c r="E194" t="s">
+        <v>419</v>
+      </c>
+      <c r="F194" t="s">
+        <v>406</v>
+      </c>
       <c r="G194" s="10"/>
       <c r="H194" s="10"/>
       <c r="I194" s="10"/>
@@ -12093,23 +12226,51 @@
       <c r="K194" s="10"/>
       <c r="L194" s="10"/>
       <c r="M194" s="10"/>
-      <c r="N194" s="10"/>
-      <c r="O194" s="10"/>
-      <c r="P194" s="10"/>
-      <c r="Q194" s="10"/>
-      <c r="R194" s="10"/>
-      <c r="S194" s="10"/>
-      <c r="T194" s="10"/>
-      <c r="U194" s="10"/>
-      <c r="V194" s="10"/>
+      <c r="N194" s="30"/>
+      <c r="O194">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="P194">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>420</v>
+      </c>
+      <c r="R194">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="S194">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="T194">
+        <v>1</v>
+      </c>
+      <c r="U194">
+        <v>0.83499999999999996</v>
+      </c>
+      <c r="V194">
+        <v>0.56100000000000005</v>
+      </c>
     </row>
     <row r="195" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A195" s="10"/>
-      <c r="B195" s="10"/>
-      <c r="C195" s="10"/>
-      <c r="D195" s="10"/>
-      <c r="E195" s="10"/>
-      <c r="F195" s="10"/>
+      <c r="A195" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D195" t="s">
+        <v>418</v>
+      </c>
+      <c r="E195" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="F195" t="s">
+        <v>406</v>
+      </c>
       <c r="G195" s="10"/>
       <c r="H195" s="10"/>
       <c r="I195" s="10"/>
@@ -12117,23 +12278,51 @@
       <c r="K195" s="10"/>
       <c r="L195" s="10"/>
       <c r="M195" s="10"/>
-      <c r="N195" s="10"/>
-      <c r="O195" s="10"/>
-      <c r="P195" s="10"/>
-      <c r="Q195" s="10"/>
-      <c r="R195" s="10"/>
-      <c r="S195" s="10"/>
-      <c r="T195" s="10"/>
-      <c r="U195" s="10"/>
-      <c r="V195" s="10"/>
+      <c r="N195" s="30"/>
+      <c r="O195">
+        <v>0.62</v>
+      </c>
+      <c r="P195">
+        <v>0.622</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>422</v>
+      </c>
+      <c r="R195">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="S195">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="T195">
+        <v>1</v>
+      </c>
+      <c r="U195">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="V195">
+        <v>0.57599999999999996</v>
+      </c>
     </row>
     <row r="196" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A196" s="10"/>
-      <c r="B196" s="10"/>
-      <c r="C196" s="10"/>
-      <c r="D196" s="10"/>
-      <c r="E196" s="10"/>
-      <c r="F196" s="10"/>
+      <c r="A196" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B196" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="C196" t="s">
+        <v>423</v>
+      </c>
+      <c r="D196" t="s">
+        <v>409</v>
+      </c>
+      <c r="E196" t="s">
+        <v>424</v>
+      </c>
+      <c r="F196" t="s">
+        <v>425</v>
+      </c>
       <c r="G196" s="10"/>
       <c r="H196" s="10"/>
       <c r="I196" s="10"/>
@@ -12141,23 +12330,35 @@
       <c r="K196" s="10"/>
       <c r="L196" s="10"/>
       <c r="M196" s="10"/>
-      <c r="N196" s="10"/>
-      <c r="O196" s="10"/>
-      <c r="P196" s="10"/>
-      <c r="Q196" s="10"/>
-      <c r="R196" s="10"/>
-      <c r="S196" s="10"/>
-      <c r="T196" s="10"/>
-      <c r="U196" s="10"/>
-      <c r="V196" s="10"/>
+      <c r="N196" s="30"/>
+      <c r="O196">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="P196">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>426</v>
+      </c>
+      <c r="R196">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="S196">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="T196">
+        <v>0.97</v>
+      </c>
+      <c r="U196">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="V196">
+        <v>0.54100000000000004</v>
+      </c>
     </row>
     <row r="197" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A197" s="10"/>
-      <c r="B197" s="10"/>
-      <c r="C197" s="10"/>
-      <c r="D197" s="10"/>
-      <c r="E197" s="10"/>
-      <c r="F197" s="10"/>
+      <c r="A197" s="13"/>
+      <c r="B197" s="34"/>
       <c r="G197" s="10"/>
       <c r="H197" s="10"/>
       <c r="I197" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3485" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{01BFD835-7A02-4109-AE4E-9FCAB74BD136}"/>
+  <xr:revisionPtr revIDLastSave="3534" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6CD8006-C572-4464-975F-7E2E8CE82CD8}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1149" uniqueCount="416">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="427">
   <si>
     <t>Date</t>
   </si>
@@ -1289,14 +1289,47 @@
     <t>llama3.2:1b-instruct-q5_K_M</t>
   </si>
   <si>
+    <t>1.24B</t>
+  </si>
+  <si>
     <t xml:space="preserve">800MB </t>
+  </si>
+  <si>
+    <t>qwen:0.5b</t>
+  </si>
+  <si>
+    <t>0.5B</t>
+  </si>
+  <si>
+    <t>500M</t>
+  </si>
+  <si>
+    <t>3,421.81 ms</t>
+  </si>
+  <si>
+    <t>486 MB</t>
+  </si>
+  <si>
+    <t>7,614.12 ms</t>
+  </si>
+  <si>
+    <t>babar_jamali/gemma3-abliterated-</t>
+  </si>
+  <si>
+    <t>806 MB</t>
+  </si>
+  <si>
+    <t>Community fine-tune based on Google Gemma 3</t>
+  </si>
+  <si>
+    <t>22,438.57 ms</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5">
+  <fonts count="6">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1330,6 +1363,12 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="8">
@@ -1376,7 +1415,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1742,11 +1781,37 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -1783,6 +1848,9 @@
     <xf numFmtId="14" fontId="0" fillId="7" borderId="17" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="5" borderId="28" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2183,70 +2251,70 @@
   <sheetData>
     <row r="1" spans="1:22"/>
     <row r="2" spans="1:22" ht="21">
-      <c r="A2" s="34" t="s">
+      <c r="A2" s="37" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="34" t="s">
+      <c r="B2" s="37" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="44" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="42"/>
-      <c r="E2" s="42"/>
-      <c r="F2" s="42"/>
-      <c r="G2" s="45" t="s">
+      <c r="D2" s="45"/>
+      <c r="E2" s="45"/>
+      <c r="F2" s="45"/>
+      <c r="G2" s="48" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="46"/>
-      <c r="I2" s="46"/>
-      <c r="J2" s="46"/>
-      <c r="K2" s="46"/>
-      <c r="L2" s="46"/>
-      <c r="M2" s="46"/>
-      <c r="N2" s="47"/>
-      <c r="O2" s="39" t="s">
+      <c r="H2" s="49"/>
+      <c r="I2" s="49"/>
+      <c r="J2" s="49"/>
+      <c r="K2" s="49"/>
+      <c r="L2" s="49"/>
+      <c r="M2" s="49"/>
+      <c r="N2" s="50"/>
+      <c r="O2" s="42" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="39"/>
-      <c r="Q2" s="39"/>
-      <c r="R2" s="39"/>
-      <c r="S2" s="39"/>
-      <c r="T2" s="39"/>
-      <c r="U2" s="39"/>
-      <c r="V2" s="40"/>
+      <c r="P2" s="42"/>
+      <c r="Q2" s="42"/>
+      <c r="R2" s="42"/>
+      <c r="S2" s="42"/>
+      <c r="T2" s="42"/>
+      <c r="U2" s="42"/>
+      <c r="V2" s="43"/>
     </row>
     <row r="3" spans="1:22" ht="18.75">
-      <c r="A3" s="35"/>
-      <c r="B3" s="35"/>
-      <c r="C3" s="43"/>
-      <c r="D3" s="44"/>
-      <c r="E3" s="44"/>
-      <c r="F3" s="44"/>
-      <c r="G3" s="48"/>
-      <c r="H3" s="49"/>
-      <c r="I3" s="49"/>
-      <c r="J3" s="49"/>
-      <c r="K3" s="49"/>
-      <c r="L3" s="49"/>
-      <c r="M3" s="49"/>
-      <c r="N3" s="50"/>
-      <c r="O3" s="37" t="s">
+      <c r="A3" s="38"/>
+      <c r="B3" s="38"/>
+      <c r="C3" s="46"/>
+      <c r="D3" s="47"/>
+      <c r="E3" s="47"/>
+      <c r="F3" s="47"/>
+      <c r="G3" s="51"/>
+      <c r="H3" s="52"/>
+      <c r="I3" s="52"/>
+      <c r="J3" s="52"/>
+      <c r="K3" s="52"/>
+      <c r="L3" s="52"/>
+      <c r="M3" s="52"/>
+      <c r="N3" s="53"/>
+      <c r="O3" s="40" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="37"/>
-      <c r="Q3" s="37"/>
-      <c r="R3" s="37" t="s">
+      <c r="P3" s="40"/>
+      <c r="Q3" s="40"/>
+      <c r="R3" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="37"/>
-      <c r="T3" s="37"/>
-      <c r="U3" s="37"/>
-      <c r="V3" s="38"/>
+      <c r="S3" s="40"/>
+      <c r="T3" s="40"/>
+      <c r="U3" s="40"/>
+      <c r="V3" s="41"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="36"/>
-      <c r="B4" s="36"/>
+      <c r="A4" s="39"/>
+      <c r="B4" s="39"/>
       <c r="C4" s="11" t="s">
         <v>7</v>
       </c>
@@ -11827,7 +11895,7 @@
       <c r="B188" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C188" s="10" t="s">
+      <c r="C188" s="26" t="s">
         <v>394</v>
       </c>
       <c r="D188" t="s">
@@ -11876,10 +11944,10 @@
       <c r="A189" s="13">
         <v>46309</v>
       </c>
-      <c r="B189" s="10" t="s">
+      <c r="B189" s="34" t="s">
         <v>398</v>
       </c>
-      <c r="C189" t="s">
+      <c r="C189" s="10" t="s">
         <v>399</v>
       </c>
       <c r="D189" t="s">
@@ -11928,10 +11996,10 @@
       <c r="A190" s="13">
         <v>46309</v>
       </c>
-      <c r="B190" s="10" t="s">
+      <c r="B190" s="34" t="s">
         <v>398</v>
       </c>
-      <c r="C190" t="s">
+      <c r="C190" s="10" t="s">
         <v>403</v>
       </c>
       <c r="D190" t="s">
@@ -11980,10 +12048,10 @@
       <c r="A191" s="13">
         <v>46309</v>
       </c>
-      <c r="B191" s="10" t="s">
+      <c r="B191" s="34" t="s">
         <v>393</v>
       </c>
-      <c r="C191" t="s">
+      <c r="C191" s="10" t="s">
         <v>408</v>
       </c>
       <c r="D191" t="s">
@@ -12032,13 +12100,13 @@
       <c r="A192" s="13">
         <v>46309</v>
       </c>
-      <c r="B192" s="10" t="s">
+      <c r="B192" s="34" t="s">
         <v>367</v>
       </c>
-      <c r="C192" t="s">
+      <c r="C192" s="10" t="s">
         <v>412</v>
       </c>
-      <c r="D192" s="10" t="s">
+      <c r="D192" s="35" t="s">
         <v>53</v>
       </c>
       <c r="E192" s="10" t="s">
@@ -12084,15 +12152,17 @@
       <c r="A193" s="13">
         <v>46310</v>
       </c>
-      <c r="B193" s="10" t="s">
+      <c r="B193" s="34" t="s">
         <v>393</v>
       </c>
-      <c r="C193" t="s">
+      <c r="C193" s="10" t="s">
         <v>414</v>
       </c>
-      <c r="D193" s="10"/>
+      <c r="D193" t="s">
+        <v>415</v>
+      </c>
       <c r="E193" s="10" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="F193" t="s">
         <v>43</v>
@@ -12131,11 +12201,24 @@
       </c>
     </row>
     <row r="194" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A194" s="13"/>
-      <c r="B194" s="10"/>
-      <c r="D194" s="10"/>
-      <c r="E194" s="10"/>
-      <c r="F194" s="10"/>
+      <c r="A194" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B194" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="C194" s="36" t="s">
+        <v>417</v>
+      </c>
+      <c r="D194" t="s">
+        <v>418</v>
+      </c>
+      <c r="E194" t="s">
+        <v>419</v>
+      </c>
+      <c r="F194" t="s">
+        <v>406</v>
+      </c>
       <c r="G194" s="10"/>
       <c r="H194" s="10"/>
       <c r="I194" s="10"/>
@@ -12143,23 +12226,51 @@
       <c r="K194" s="10"/>
       <c r="L194" s="10"/>
       <c r="M194" s="10"/>
-      <c r="N194" s="10"/>
-      <c r="O194" s="10"/>
-      <c r="P194" s="10"/>
-      <c r="Q194" s="10"/>
-      <c r="R194" s="10"/>
-      <c r="S194" s="10"/>
-      <c r="T194" s="10"/>
-      <c r="U194" s="10"/>
-      <c r="V194" s="10"/>
+      <c r="N194" s="30"/>
+      <c r="O194">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="P194">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="Q194" t="s">
+        <v>420</v>
+      </c>
+      <c r="R194">
+        <v>0.73699999999999999</v>
+      </c>
+      <c r="S194">
+        <v>0.53200000000000003</v>
+      </c>
+      <c r="T194">
+        <v>1</v>
+      </c>
+      <c r="U194">
+        <v>0.83499999999999996</v>
+      </c>
+      <c r="V194">
+        <v>0.56100000000000005</v>
+      </c>
     </row>
     <row r="195" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A195" s="10"/>
-      <c r="B195" s="10"/>
-      <c r="C195" s="10"/>
-      <c r="D195" s="10"/>
-      <c r="E195" s="10"/>
-      <c r="F195" s="10"/>
+      <c r="A195" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B195" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="D195" t="s">
+        <v>418</v>
+      </c>
+      <c r="E195" s="10" t="s">
+        <v>421</v>
+      </c>
+      <c r="F195" t="s">
+        <v>406</v>
+      </c>
       <c r="G195" s="10"/>
       <c r="H195" s="10"/>
       <c r="I195" s="10"/>
@@ -12167,23 +12278,51 @@
       <c r="K195" s="10"/>
       <c r="L195" s="10"/>
       <c r="M195" s="10"/>
-      <c r="N195" s="10"/>
-      <c r="O195" s="10"/>
-      <c r="P195" s="10"/>
-      <c r="Q195" s="10"/>
-      <c r="R195" s="10"/>
-      <c r="S195" s="10"/>
-      <c r="T195" s="10"/>
-      <c r="U195" s="10"/>
-      <c r="V195" s="10"/>
+      <c r="N195" s="30"/>
+      <c r="O195">
+        <v>0.62</v>
+      </c>
+      <c r="P195">
+        <v>0.622</v>
+      </c>
+      <c r="Q195" t="s">
+        <v>422</v>
+      </c>
+      <c r="R195">
+        <v>0.69799999999999995</v>
+      </c>
+      <c r="S195">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="T195">
+        <v>1</v>
+      </c>
+      <c r="U195">
+        <v>0.82499999999999996</v>
+      </c>
+      <c r="V195">
+        <v>0.57599999999999996</v>
+      </c>
     </row>
     <row r="196" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A196" s="10"/>
-      <c r="B196" s="10"/>
-      <c r="C196" s="10"/>
-      <c r="D196" s="10"/>
-      <c r="E196" s="10"/>
-      <c r="F196" s="10"/>
+      <c r="A196" s="13">
+        <v>46310</v>
+      </c>
+      <c r="B196" s="34" t="s">
+        <v>398</v>
+      </c>
+      <c r="C196" t="s">
+        <v>423</v>
+      </c>
+      <c r="D196" t="s">
+        <v>409</v>
+      </c>
+      <c r="E196" t="s">
+        <v>424</v>
+      </c>
+      <c r="F196" t="s">
+        <v>425</v>
+      </c>
       <c r="G196" s="10"/>
       <c r="H196" s="10"/>
       <c r="I196" s="10"/>
@@ -12191,23 +12330,35 @@
       <c r="K196" s="10"/>
       <c r="L196" s="10"/>
       <c r="M196" s="10"/>
-      <c r="N196" s="10"/>
-      <c r="O196" s="10"/>
-      <c r="P196" s="10"/>
-      <c r="Q196" s="10"/>
-      <c r="R196" s="10"/>
-      <c r="S196" s="10"/>
-      <c r="T196" s="10"/>
-      <c r="U196" s="10"/>
-      <c r="V196" s="10"/>
+      <c r="N196" s="30"/>
+      <c r="O196">
+        <v>0.51300000000000001</v>
+      </c>
+      <c r="P196">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="Q196" t="s">
+        <v>426</v>
+      </c>
+      <c r="R196">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="S196">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="T196">
+        <v>0.97</v>
+      </c>
+      <c r="U196">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="V196">
+        <v>0.54100000000000004</v>
+      </c>
     </row>
     <row r="197" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A197" s="10"/>
-      <c r="B197" s="10"/>
-      <c r="C197" s="10"/>
-      <c r="D197" s="10"/>
-      <c r="E197" s="10"/>
-      <c r="F197" s="10"/>
+      <c r="A197" s="13"/>
+      <c r="B197" s="34"/>
       <c r="G197" s="10"/>
       <c r="H197" s="10"/>
       <c r="I197" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3534" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A6CD8006-C572-4464-975F-7E2E8CE82CD8}"/>
+  <xr:revisionPtr revIDLastSave="3553" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{402D52E0-A56C-48C7-A2CA-04DCCE06DFD8}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1168" uniqueCount="427">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="429">
   <si>
     <t>Date</t>
   </si>
@@ -1307,6 +1307,9 @@
     <t>3,421.81 ms</t>
   </si>
   <si>
+    <t>qwen2.5:0.5b-instruct</t>
+  </si>
+  <si>
     <t>486 MB</t>
   </si>
   <si>
@@ -1323,6 +1326,9 @@
   </si>
   <si>
     <t>22,438.57 ms</t>
+  </si>
+  <si>
+    <t>StarCoder</t>
   </si>
 </sst>
 </file>
@@ -2241,7 +2247,7 @@
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
     <col min="3" max="3" width="26.75" customWidth="1"/>
-    <col min="6" max="6" width="13.25" customWidth="1"/>
+    <col min="6" max="6" width="33.875" customWidth="1"/>
     <col min="8" max="8" width="14.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="10.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="14.875" bestFit="1" customWidth="1"/>
@@ -12259,14 +12265,14 @@
       <c r="B195" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C195" s="10" t="s">
-        <v>393</v>
+      <c r="C195" t="s">
+        <v>421</v>
       </c>
       <c r="D195" t="s">
         <v>418</v>
       </c>
       <c r="E195" s="10" t="s">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="F195" t="s">
         <v>406</v>
@@ -12286,7 +12292,7 @@
         <v>0.622</v>
       </c>
       <c r="Q195" t="s">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="R195">
         <v>0.69799999999999995</v>
@@ -12312,16 +12318,16 @@
         <v>398</v>
       </c>
       <c r="C196" t="s">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="D196" t="s">
         <v>409</v>
       </c>
       <c r="E196" t="s">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="F196" t="s">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="G196" s="10"/>
       <c r="H196" s="10"/>
@@ -12338,7 +12344,7 @@
         <v>0.60099999999999998</v>
       </c>
       <c r="Q196" t="s">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="R196">
         <v>0.68100000000000005</v>
@@ -12357,8 +12363,15 @@
       </c>
     </row>
     <row r="197" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A197" s="13"/>
-      <c r="B197" s="34"/>
+      <c r="A197" s="13">
+        <v>46311</v>
+      </c>
+      <c r="B197" s="34" t="s">
+        <v>393</v>
+      </c>
+      <c r="C197" t="s">
+        <v>428</v>
+      </c>
       <c r="G197" s="10"/>
       <c r="H197" s="10"/>
       <c r="I197" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3553" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{402D52E0-A56C-48C7-A2CA-04DCCE06DFD8}"/>
+  <xr:revisionPtr revIDLastSave="3588" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E37EE749-A618-4E1E-AFF9-591BEE3BC393}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1170" uniqueCount="429">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="435">
   <si>
     <t>Date</t>
   </si>
@@ -1328,7 +1328,25 @@
     <t>22,438.57 ms</t>
   </si>
   <si>
-    <t>StarCoder</t>
+    <t>LiquidAI/lfm2.5-350m:q4_k_m</t>
+  </si>
+  <si>
+    <t>350M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 320 MB</t>
+  </si>
+  <si>
+    <t>2770.80 ms</t>
+  </si>
+  <si>
+    <t>jewelzufo/VertaLily-1.2</t>
+  </si>
+  <si>
+    <t>724 MB</t>
+  </si>
+  <si>
+    <t>7631.99 ms</t>
   </si>
 </sst>
 </file>
@@ -12364,13 +12382,22 @@
     </row>
     <row r="197" spans="1:22" ht="15.75" customHeight="1">
       <c r="A197" s="13">
-        <v>46311</v>
+        <v>46314</v>
       </c>
       <c r="B197" s="34" t="s">
         <v>393</v>
       </c>
       <c r="C197" t="s">
         <v>428</v>
+      </c>
+      <c r="D197" t="s">
+        <v>429</v>
+      </c>
+      <c r="E197" t="s">
+        <v>430</v>
+      </c>
+      <c r="F197" t="s">
+        <v>79</v>
       </c>
       <c r="G197" s="10"/>
       <c r="H197" s="10"/>
@@ -12379,23 +12406,51 @@
       <c r="K197" s="10"/>
       <c r="L197" s="10"/>
       <c r="M197" s="10"/>
-      <c r="N197" s="10"/>
-      <c r="O197" s="10"/>
-      <c r="P197" s="10"/>
-      <c r="Q197" s="10"/>
-      <c r="R197" s="10"/>
-      <c r="S197" s="10"/>
-      <c r="T197" s="10"/>
-      <c r="U197" s="10"/>
-      <c r="V197" s="10"/>
+      <c r="N197" s="30"/>
+      <c r="O197">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="P197">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="Q197">
+        <v>0.72399999999999998</v>
+      </c>
+      <c r="R197" t="s">
+        <v>431</v>
+      </c>
+      <c r="S197">
+        <v>0.77900000000000003</v>
+      </c>
+      <c r="T197">
+        <v>0.49199999999999999</v>
+      </c>
+      <c r="U197">
+        <v>1</v>
+      </c>
+      <c r="V197">
+        <v>0.93600000000000005</v>
+      </c>
     </row>
     <row r="198" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A198" s="10"/>
-      <c r="B198" s="10"/>
-      <c r="C198" s="10"/>
-      <c r="D198" s="10"/>
-      <c r="E198" s="10"/>
-      <c r="F198" s="10"/>
+      <c r="A198" s="13">
+        <v>46314</v>
+      </c>
+      <c r="B198" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C198" t="s">
+        <v>432</v>
+      </c>
+      <c r="D198" s="10" t="s">
+        <v>376</v>
+      </c>
+      <c r="E198" s="10" t="s">
+        <v>433</v>
+      </c>
+      <c r="F198" t="s">
+        <v>194</v>
+      </c>
       <c r="G198" s="10"/>
       <c r="H198" s="10"/>
       <c r="I198" s="10"/>
@@ -12403,23 +12458,36 @@
       <c r="K198" s="10"/>
       <c r="L198" s="10"/>
       <c r="M198" s="10"/>
-      <c r="N198" s="10"/>
-      <c r="O198" s="10"/>
-      <c r="P198" s="10"/>
-      <c r="Q198" s="10"/>
-      <c r="R198" s="10"/>
-      <c r="S198" s="10"/>
-      <c r="T198" s="10"/>
-      <c r="U198" s="10"/>
-      <c r="V198" s="10"/>
+      <c r="N198" s="30"/>
+      <c r="O198">
+        <v>0.67500000000000004</v>
+      </c>
+      <c r="P198">
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="Q198" t="s">
+        <v>434</v>
+      </c>
+      <c r="R198">
+        <v>0.72099999999999997</v>
+      </c>
+      <c r="S198">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="T198">
+        <v>1</v>
+      </c>
+      <c r="U198">
+        <v>0.83599999999999997</v>
+      </c>
+      <c r="V198">
+        <v>0.59699999999999998</v>
+      </c>
     </row>
     <row r="199" spans="1:22" ht="15.75" customHeight="1">
       <c r="A199" s="10"/>
       <c r="B199" s="10"/>
-      <c r="C199" s="10"/>
       <c r="D199" s="10"/>
-      <c r="E199" s="10"/>
-      <c r="F199" s="10"/>
       <c r="G199" s="10"/>
       <c r="H199" s="10"/>
       <c r="I199" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3588" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E37EE749-A618-4E1E-AFF9-591BEE3BC393}"/>
+  <xr:revisionPtr revIDLastSave="3656" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCEFC5D2-C67C-419D-831D-B4CA7DEF02A4}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="460">
   <si>
     <t>Date</t>
   </si>
@@ -1347,6 +1347,81 @@
   </si>
   <si>
     <t>7631.99 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> granite3.2</t>
+  </si>
+  <si>
+    <t>1707.52 ms</t>
+  </si>
+  <si>
+    <t>h2oai</t>
+  </si>
+  <si>
+    <t>350 MB</t>
+  </si>
+  <si>
+    <t>H2O.ai</t>
+  </si>
+  <si>
+    <t>1161.33 ms</t>
+  </si>
+  <si>
+    <t>aya-expanse</t>
+  </si>
+  <si>
+    <t>8B</t>
+  </si>
+  <si>
+    <t>5.0 GB</t>
+  </si>
+  <si>
+    <t>Cohere</t>
+  </si>
+  <si>
+    <t>4022.08 ms</t>
+  </si>
+  <si>
+    <t>command-r7b:latest</t>
+  </si>
+  <si>
+    <t>7B</t>
+  </si>
+  <si>
+    <t>5.1GB</t>
+  </si>
+  <si>
+    <t>4854.99 ms</t>
+  </si>
+  <si>
+    <t>mistral-nemo:12b</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>7.1 GB</t>
+  </si>
+  <si>
+    <t>3382.15 ms</t>
+  </si>
+  <si>
+    <t>Ling-3.0-tiny-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>7.9B total (1.3B active)</t>
+  </si>
+  <si>
+    <t>6.4GB</t>
+  </si>
+  <si>
+    <t>inclusionAI</t>
+  </si>
+  <si>
+    <t>3023.63 ms</t>
+  </si>
+  <si>
+    <t>0.604 (HPI)*</t>
   </si>
 </sst>
 </file>
@@ -12485,9 +12560,24 @@
       </c>
     </row>
     <row r="199" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A199" s="10"/>
-      <c r="B199" s="10"/>
-      <c r="D199" s="10"/>
+      <c r="A199" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C199" t="s">
+        <v>435</v>
+      </c>
+      <c r="D199" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E199" t="s">
+        <v>95</v>
+      </c>
+      <c r="F199" t="s">
+        <v>83</v>
+      </c>
       <c r="G199" s="10"/>
       <c r="H199" s="10"/>
       <c r="I199" s="10"/>
@@ -12495,23 +12585,51 @@
       <c r="K199" s="10"/>
       <c r="L199" s="10"/>
       <c r="M199" s="10"/>
-      <c r="N199" s="10"/>
-      <c r="O199" s="10"/>
-      <c r="P199" s="10"/>
-      <c r="Q199" s="10"/>
-      <c r="R199" s="10"/>
-      <c r="S199" s="10"/>
-      <c r="T199" s="10"/>
-      <c r="U199" s="10"/>
-      <c r="V199" s="10"/>
+      <c r="N199" s="30"/>
+      <c r="O199">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="P199">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>436</v>
+      </c>
+      <c r="R199">
+        <v>0.71</v>
+      </c>
+      <c r="S199">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="T199">
+        <v>1</v>
+      </c>
+      <c r="U199">
+        <v>0.873</v>
+      </c>
+      <c r="V199">
+        <v>0.623</v>
+      </c>
     </row>
     <row r="200" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A200" s="10"/>
-      <c r="B200" s="10"/>
-      <c r="C200" s="10"/>
-      <c r="D200" s="10"/>
-      <c r="E200" s="10"/>
-      <c r="F200" s="10"/>
+      <c r="A200" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C200" t="s">
+        <v>437</v>
+      </c>
+      <c r="D200" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="E200" t="s">
+        <v>438</v>
+      </c>
+      <c r="F200" t="s">
+        <v>439</v>
+      </c>
       <c r="G200" s="10"/>
       <c r="H200" s="10"/>
       <c r="I200" s="10"/>
@@ -12519,111 +12637,236 @@
       <c r="K200" s="10"/>
       <c r="L200" s="10"/>
       <c r="M200" s="10"/>
-      <c r="N200" s="10"/>
-      <c r="O200" s="10"/>
-      <c r="P200" s="10"/>
-      <c r="Q200" s="10"/>
-      <c r="R200" s="10"/>
-      <c r="S200" s="10"/>
-      <c r="T200" s="10"/>
-      <c r="U200" s="10"/>
-      <c r="V200" s="10"/>
+      <c r="N200" s="30"/>
+      <c r="O200">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="P200">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>440</v>
+      </c>
+      <c r="R200">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="T200">
+        <v>1</v>
+      </c>
+      <c r="U200">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="V200">
+        <v>0.57499999999999996</v>
+      </c>
     </row>
     <row r="201" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A201" s="10"/>
-      <c r="B201" s="10"/>
-      <c r="C201" s="10"/>
-      <c r="D201" s="10"/>
-      <c r="E201" s="10"/>
-      <c r="F201" s="10"/>
+      <c r="A201" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C201" t="s">
+        <v>441</v>
+      </c>
+      <c r="D201" t="s">
+        <v>442</v>
+      </c>
+      <c r="E201" t="s">
+        <v>443</v>
+      </c>
+      <c r="F201" t="s">
+        <v>444</v>
+      </c>
       <c r="G201" s="10"/>
       <c r="H201" s="10"/>
       <c r="I201" s="10"/>
       <c r="J201" s="10"/>
-      <c r="K201" s="10"/>
+      <c r="K201" s="30"/>
       <c r="L201" s="10"/>
       <c r="M201" s="10"/>
       <c r="N201" s="10"/>
-      <c r="O201" s="10"/>
-      <c r="P201" s="10"/>
-      <c r="Q201" s="10"/>
-      <c r="R201" s="10"/>
-      <c r="S201" s="10"/>
-      <c r="T201" s="10"/>
-      <c r="U201" s="10"/>
-      <c r="V201" s="10"/>
+      <c r="O201">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="P201">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>445</v>
+      </c>
+      <c r="R201">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="S201">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="T201">
+        <v>1</v>
+      </c>
+      <c r="U201">
+        <v>0.92</v>
+      </c>
+      <c r="V201">
+        <v>0.59399999999999997</v>
+      </c>
     </row>
     <row r="202" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A202" s="10"/>
-      <c r="B202" s="10"/>
-      <c r="C202" s="10"/>
-      <c r="D202" s="10"/>
-      <c r="E202" s="10"/>
-      <c r="F202" s="10"/>
+      <c r="A202" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C202" t="s">
+        <v>446</v>
+      </c>
+      <c r="D202" t="s">
+        <v>447</v>
+      </c>
+      <c r="E202" t="s">
+        <v>448</v>
+      </c>
+      <c r="F202" t="s">
+        <v>444</v>
+      </c>
       <c r="G202" s="10"/>
       <c r="H202" s="10"/>
       <c r="I202" s="10"/>
       <c r="J202" s="10"/>
-      <c r="K202" s="10"/>
+      <c r="K202" s="30"/>
       <c r="L202" s="10"/>
       <c r="M202" s="10"/>
       <c r="N202" s="10"/>
-      <c r="O202" s="10"/>
-      <c r="P202" s="10"/>
-      <c r="Q202" s="10"/>
-      <c r="R202" s="10"/>
-      <c r="S202" s="10"/>
-      <c r="T202" s="10"/>
-      <c r="U202" s="10"/>
-      <c r="V202" s="10"/>
+      <c r="O202">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="P202">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>449</v>
+      </c>
+      <c r="R202">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="S202">
+        <v>0.61</v>
+      </c>
+      <c r="T202">
+        <v>1</v>
+      </c>
+      <c r="U202">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="V202">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="203" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A203" s="10"/>
-      <c r="B203" s="10"/>
-      <c r="C203" s="10"/>
-      <c r="D203" s="10"/>
-      <c r="E203" s="10"/>
-      <c r="F203" s="10"/>
+      <c r="A203" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C203" t="s">
+        <v>450</v>
+      </c>
+      <c r="D203" t="s">
+        <v>451</v>
+      </c>
+      <c r="E203" t="s">
+        <v>452</v>
+      </c>
+      <c r="F203" s="10" t="s">
+        <v>104</v>
+      </c>
       <c r="G203" s="10"/>
       <c r="H203" s="10"/>
       <c r="I203" s="10"/>
       <c r="J203" s="10"/>
-      <c r="K203" s="10"/>
+      <c r="K203" s="30"/>
       <c r="L203" s="10"/>
       <c r="M203" s="10"/>
       <c r="N203" s="10"/>
-      <c r="O203" s="10"/>
-      <c r="P203" s="10"/>
-      <c r="Q203" s="10"/>
-      <c r="R203" s="10"/>
-      <c r="S203" s="10"/>
-      <c r="T203" s="10"/>
-      <c r="U203" s="10"/>
-      <c r="V203" s="10"/>
+      <c r="O203">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="P203">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>453</v>
+      </c>
+      <c r="R203">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="S203">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="T203">
+        <v>0.83</v>
+      </c>
+      <c r="U203">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="V203">
+        <v>0.56599999999999995</v>
+      </c>
     </row>
     <row r="204" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A204" s="10"/>
-      <c r="B204" s="10"/>
-      <c r="C204" s="10"/>
-      <c r="D204" s="10"/>
-      <c r="E204" s="10"/>
-      <c r="F204" s="10"/>
+      <c r="A204" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C204" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D204" t="s">
+        <v>455</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="F204" t="s">
+        <v>457</v>
+      </c>
       <c r="G204" s="10"/>
       <c r="H204" s="10"/>
       <c r="I204" s="10"/>
       <c r="J204" s="10"/>
-      <c r="K204" s="10"/>
+      <c r="K204" s="30"/>
       <c r="L204" s="10"/>
       <c r="M204" s="10"/>
       <c r="N204" s="10"/>
-      <c r="O204" s="10"/>
-      <c r="P204" s="10"/>
-      <c r="Q204" s="10"/>
-      <c r="R204" s="10"/>
-      <c r="S204" s="10"/>
-      <c r="T204" s="10"/>
-      <c r="U204" s="10"/>
-      <c r="V204" s="10"/>
+      <c r="O204">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="P204">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>458</v>
+      </c>
+      <c r="R204">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="S204" t="s">
+        <v>459</v>
+      </c>
+      <c r="T204">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U204">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="V204">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="205" spans="1:22" ht="15.75" customHeight="1">
       <c r="A205" s="10"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3656" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{CCEFC5D2-C67C-419D-831D-B4CA7DEF02A4}"/>
+  <xr:revisionPtr revIDLastSave="3697" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27518C61-5283-4F14-ACDC-9826A2D50C43}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$204</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1217" uniqueCount="460">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="476">
   <si>
     <t>Date</t>
   </si>
@@ -1421,7 +1421,55 @@
     <t>3023.63 ms</t>
   </si>
   <si>
-    <t>0.604 (HPI)*</t>
+    <t>EXAONE Deep 2.4B</t>
+  </si>
+  <si>
+    <t>2.4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.2 GB </t>
+  </si>
+  <si>
+    <t>6742.69 ms</t>
+  </si>
+  <si>
+    <t>Phi-4-mini-instruct</t>
+  </si>
+  <si>
+    <t>3.8B</t>
+  </si>
+  <si>
+    <t>2.49 GB</t>
+  </si>
+  <si>
+    <t>2222.52 ms</t>
+  </si>
+  <si>
+    <t>Stable Code Instruct 3B Q4_K_M</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>Stability A</t>
+  </si>
+  <si>
+    <t>429.65 ms</t>
+  </si>
+  <si>
+    <t>Nemotron Mini 4B Instruct Q4_K_M</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>2.7GB</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>678.99 ms</t>
   </si>
 </sst>
 </file>
@@ -12855,8 +12903,8 @@
       <c r="R204">
         <v>0.58899999999999997</v>
       </c>
-      <c r="S204" t="s">
-        <v>459</v>
+      <c r="S204">
+        <v>0.60399999999999998</v>
       </c>
       <c r="T204">
         <v>0.90500000000000003</v>
@@ -12869,103 +12917,214 @@
       </c>
     </row>
     <row r="205" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A205" s="10"/>
-      <c r="B205" s="10"/>
-      <c r="C205" s="10"/>
-      <c r="D205" s="10"/>
-      <c r="E205" s="10"/>
-      <c r="F205" s="10"/>
+      <c r="A205" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C205" t="s">
+        <v>459</v>
+      </c>
+      <c r="D205" t="s">
+        <v>460</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="F205" t="s">
+        <v>384</v>
+      </c>
       <c r="G205" s="10"/>
       <c r="H205" s="10"/>
       <c r="I205" s="10"/>
       <c r="J205" s="10"/>
-      <c r="K205" s="10"/>
+      <c r="K205" s="30"/>
       <c r="L205" s="10"/>
       <c r="M205" s="10"/>
       <c r="N205" s="10"/>
-      <c r="O205" s="10"/>
-      <c r="P205" s="10"/>
-      <c r="Q205" s="10"/>
-      <c r="R205" s="10"/>
-      <c r="S205" s="10"/>
-      <c r="T205" s="10"/>
-      <c r="U205" s="10"/>
-      <c r="V205" s="10"/>
+      <c r="O205">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="P205">
+        <v>0.443</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>462</v>
+      </c>
+      <c r="R205">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="S205">
+        <v>0.627</v>
+      </c>
+      <c r="T205">
+        <v>1</v>
+      </c>
+      <c r="U205">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="V205">
+        <v>0.59799999999999998</v>
+      </c>
     </row>
     <row r="206" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A206" s="10"/>
-      <c r="B206" s="10"/>
-      <c r="C206" s="10"/>
-      <c r="D206" s="10"/>
-      <c r="E206" s="10"/>
-      <c r="F206" s="10"/>
+      <c r="A206" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C206" t="s">
+        <v>463</v>
+      </c>
+      <c r="D206" t="s">
+        <v>464</v>
+      </c>
+      <c r="E206" t="s">
+        <v>465</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="G206" s="10"/>
       <c r="H206" s="10"/>
       <c r="I206" s="10"/>
       <c r="J206" s="10"/>
-      <c r="K206" s="10"/>
+      <c r="K206" s="30"/>
       <c r="L206" s="10"/>
       <c r="M206" s="10"/>
       <c r="N206" s="10"/>
-      <c r="O206" s="10"/>
-      <c r="P206" s="10"/>
-      <c r="Q206" s="10"/>
-      <c r="R206" s="10"/>
-      <c r="S206" s="10"/>
-      <c r="T206" s="10"/>
-      <c r="U206" s="10"/>
-      <c r="V206" s="10"/>
+      <c r="O206">
+        <v>0.78</v>
+      </c>
+      <c r="P206">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>466</v>
+      </c>
+      <c r="R206">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="S206">
+        <v>0.59</v>
+      </c>
+      <c r="T206">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U206">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="V206">
+        <v>0.57599999999999996</v>
+      </c>
     </row>
     <row r="207" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A207" s="10"/>
-      <c r="B207" s="10"/>
-      <c r="C207" s="10"/>
-      <c r="D207" s="10"/>
-      <c r="E207" s="10"/>
-      <c r="F207" s="10"/>
+      <c r="A207" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C207" t="s">
+        <v>467</v>
+      </c>
+      <c r="D207" t="s">
+        <v>468</v>
+      </c>
+      <c r="E207" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F207" t="s">
+        <v>469</v>
+      </c>
       <c r="G207" s="10"/>
       <c r="H207" s="10"/>
       <c r="I207" s="10"/>
       <c r="J207" s="10"/>
-      <c r="K207" s="10"/>
+      <c r="K207" s="30"/>
       <c r="L207" s="10"/>
       <c r="M207" s="10"/>
       <c r="N207" s="10"/>
-      <c r="O207" s="10"/>
-      <c r="P207" s="10"/>
-      <c r="Q207" s="10"/>
-      <c r="R207" s="10"/>
-      <c r="S207" s="10"/>
-      <c r="T207" s="10"/>
-      <c r="U207" s="10"/>
-      <c r="V207" s="10"/>
+      <c r="O207">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="P207">
+        <v>0.498</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>470</v>
+      </c>
+      <c r="R207">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="S207">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="T207">
+        <v>1</v>
+      </c>
+      <c r="U207">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="V207">
+        <v>0.55200000000000005</v>
+      </c>
     </row>
     <row r="208" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A208" s="10"/>
-      <c r="B208" s="10"/>
-      <c r="C208" s="10"/>
-      <c r="D208" s="10"/>
-      <c r="E208" s="10"/>
-      <c r="F208" s="10"/>
+      <c r="A208" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C208" t="s">
+        <v>471</v>
+      </c>
+      <c r="D208" t="s">
+        <v>472</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="F208" t="s">
+        <v>474</v>
+      </c>
       <c r="G208" s="10"/>
       <c r="H208" s="10"/>
       <c r="I208" s="10"/>
       <c r="J208" s="10"/>
-      <c r="K208" s="10"/>
+      <c r="K208" s="30"/>
       <c r="L208" s="10"/>
       <c r="M208" s="10"/>
       <c r="N208" s="10"/>
-      <c r="O208" s="10"/>
-      <c r="P208" s="10"/>
-      <c r="Q208" s="10"/>
-      <c r="R208" s="10"/>
-      <c r="S208" s="10"/>
-      <c r="T208" s="10"/>
-      <c r="U208" s="10"/>
-      <c r="V208" s="10"/>
+      <c r="O208">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="P208">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>475</v>
+      </c>
+      <c r="R208">
+        <v>0.629</v>
+      </c>
+      <c r="S208">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="T208">
+        <v>1</v>
+      </c>
+      <c r="U208">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="V208">
+        <v>0.57299999999999995</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V177" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}"/>
   <mergeCells count="7">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3588" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E37EE749-A618-4E1E-AFF9-591BEE3BC393}"/>
+  <xr:revisionPtr revIDLastSave="3697" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27518C61-5283-4F14-ACDC-9826A2D50C43}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$204</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="476">
   <si>
     <t>Date</t>
   </si>
@@ -1347,6 +1347,129 @@
   </si>
   <si>
     <t>7631.99 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> granite3.2</t>
+  </si>
+  <si>
+    <t>1707.52 ms</t>
+  </si>
+  <si>
+    <t>h2oai</t>
+  </si>
+  <si>
+    <t>350 MB</t>
+  </si>
+  <si>
+    <t>H2O.ai</t>
+  </si>
+  <si>
+    <t>1161.33 ms</t>
+  </si>
+  <si>
+    <t>aya-expanse</t>
+  </si>
+  <si>
+    <t>8B</t>
+  </si>
+  <si>
+    <t>5.0 GB</t>
+  </si>
+  <si>
+    <t>Cohere</t>
+  </si>
+  <si>
+    <t>4022.08 ms</t>
+  </si>
+  <si>
+    <t>command-r7b:latest</t>
+  </si>
+  <si>
+    <t>7B</t>
+  </si>
+  <si>
+    <t>5.1GB</t>
+  </si>
+  <si>
+    <t>4854.99 ms</t>
+  </si>
+  <si>
+    <t>mistral-nemo:12b</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>7.1 GB</t>
+  </si>
+  <si>
+    <t>3382.15 ms</t>
+  </si>
+  <si>
+    <t>Ling-3.0-tiny-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>7.9B total (1.3B active)</t>
+  </si>
+  <si>
+    <t>6.4GB</t>
+  </si>
+  <si>
+    <t>inclusionAI</t>
+  </si>
+  <si>
+    <t>3023.63 ms</t>
+  </si>
+  <si>
+    <t>EXAONE Deep 2.4B</t>
+  </si>
+  <si>
+    <t>2.4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.2 GB </t>
+  </si>
+  <si>
+    <t>6742.69 ms</t>
+  </si>
+  <si>
+    <t>Phi-4-mini-instruct</t>
+  </si>
+  <si>
+    <t>3.8B</t>
+  </si>
+  <si>
+    <t>2.49 GB</t>
+  </si>
+  <si>
+    <t>2222.52 ms</t>
+  </si>
+  <si>
+    <t>Stable Code Instruct 3B Q4_K_M</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>Stability A</t>
+  </si>
+  <si>
+    <t>429.65 ms</t>
+  </si>
+  <si>
+    <t>Nemotron Mini 4B Instruct Q4_K_M</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>2.7GB</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>678.99 ms</t>
   </si>
 </sst>
 </file>
@@ -12485,9 +12608,24 @@
       </c>
     </row>
     <row r="199" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A199" s="10"/>
-      <c r="B199" s="10"/>
-      <c r="D199" s="10"/>
+      <c r="A199" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C199" t="s">
+        <v>435</v>
+      </c>
+      <c r="D199" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E199" t="s">
+        <v>95</v>
+      </c>
+      <c r="F199" t="s">
+        <v>83</v>
+      </c>
       <c r="G199" s="10"/>
       <c r="H199" s="10"/>
       <c r="I199" s="10"/>
@@ -12495,23 +12633,51 @@
       <c r="K199" s="10"/>
       <c r="L199" s="10"/>
       <c r="M199" s="10"/>
-      <c r="N199" s="10"/>
-      <c r="O199" s="10"/>
-      <c r="P199" s="10"/>
-      <c r="Q199" s="10"/>
-      <c r="R199" s="10"/>
-      <c r="S199" s="10"/>
-      <c r="T199" s="10"/>
-      <c r="U199" s="10"/>
-      <c r="V199" s="10"/>
+      <c r="N199" s="30"/>
+      <c r="O199">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="P199">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>436</v>
+      </c>
+      <c r="R199">
+        <v>0.71</v>
+      </c>
+      <c r="S199">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="T199">
+        <v>1</v>
+      </c>
+      <c r="U199">
+        <v>0.873</v>
+      </c>
+      <c r="V199">
+        <v>0.623</v>
+      </c>
     </row>
     <row r="200" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A200" s="10"/>
-      <c r="B200" s="10"/>
-      <c r="C200" s="10"/>
-      <c r="D200" s="10"/>
-      <c r="E200" s="10"/>
-      <c r="F200" s="10"/>
+      <c r="A200" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C200" t="s">
+        <v>437</v>
+      </c>
+      <c r="D200" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="E200" t="s">
+        <v>438</v>
+      </c>
+      <c r="F200" t="s">
+        <v>439</v>
+      </c>
       <c r="G200" s="10"/>
       <c r="H200" s="10"/>
       <c r="I200" s="10"/>
@@ -12519,210 +12685,446 @@
       <c r="K200" s="10"/>
       <c r="L200" s="10"/>
       <c r="M200" s="10"/>
-      <c r="N200" s="10"/>
-      <c r="O200" s="10"/>
-      <c r="P200" s="10"/>
-      <c r="Q200" s="10"/>
-      <c r="R200" s="10"/>
-      <c r="S200" s="10"/>
-      <c r="T200" s="10"/>
-      <c r="U200" s="10"/>
-      <c r="V200" s="10"/>
+      <c r="N200" s="30"/>
+      <c r="O200">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="P200">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>440</v>
+      </c>
+      <c r="R200">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="T200">
+        <v>1</v>
+      </c>
+      <c r="U200">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="V200">
+        <v>0.57499999999999996</v>
+      </c>
     </row>
     <row r="201" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A201" s="10"/>
-      <c r="B201" s="10"/>
-      <c r="C201" s="10"/>
-      <c r="D201" s="10"/>
-      <c r="E201" s="10"/>
-      <c r="F201" s="10"/>
+      <c r="A201" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C201" t="s">
+        <v>441</v>
+      </c>
+      <c r="D201" t="s">
+        <v>442</v>
+      </c>
+      <c r="E201" t="s">
+        <v>443</v>
+      </c>
+      <c r="F201" t="s">
+        <v>444</v>
+      </c>
       <c r="G201" s="10"/>
       <c r="H201" s="10"/>
       <c r="I201" s="10"/>
       <c r="J201" s="10"/>
-      <c r="K201" s="10"/>
+      <c r="K201" s="30"/>
       <c r="L201" s="10"/>
       <c r="M201" s="10"/>
       <c r="N201" s="10"/>
-      <c r="O201" s="10"/>
-      <c r="P201" s="10"/>
-      <c r="Q201" s="10"/>
-      <c r="R201" s="10"/>
-      <c r="S201" s="10"/>
-      <c r="T201" s="10"/>
-      <c r="U201" s="10"/>
-      <c r="V201" s="10"/>
+      <c r="O201">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="P201">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>445</v>
+      </c>
+      <c r="R201">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="S201">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="T201">
+        <v>1</v>
+      </c>
+      <c r="U201">
+        <v>0.92</v>
+      </c>
+      <c r="V201">
+        <v>0.59399999999999997</v>
+      </c>
     </row>
     <row r="202" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A202" s="10"/>
-      <c r="B202" s="10"/>
-      <c r="C202" s="10"/>
-      <c r="D202" s="10"/>
-      <c r="E202" s="10"/>
-      <c r="F202" s="10"/>
+      <c r="A202" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C202" t="s">
+        <v>446</v>
+      </c>
+      <c r="D202" t="s">
+        <v>447</v>
+      </c>
+      <c r="E202" t="s">
+        <v>448</v>
+      </c>
+      <c r="F202" t="s">
+        <v>444</v>
+      </c>
       <c r="G202" s="10"/>
       <c r="H202" s="10"/>
       <c r="I202" s="10"/>
       <c r="J202" s="10"/>
-      <c r="K202" s="10"/>
+      <c r="K202" s="30"/>
       <c r="L202" s="10"/>
       <c r="M202" s="10"/>
       <c r="N202" s="10"/>
-      <c r="O202" s="10"/>
-      <c r="P202" s="10"/>
-      <c r="Q202" s="10"/>
-      <c r="R202" s="10"/>
-      <c r="S202" s="10"/>
-      <c r="T202" s="10"/>
-      <c r="U202" s="10"/>
-      <c r="V202" s="10"/>
+      <c r="O202">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="P202">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>449</v>
+      </c>
+      <c r="R202">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="S202">
+        <v>0.61</v>
+      </c>
+      <c r="T202">
+        <v>1</v>
+      </c>
+      <c r="U202">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="V202">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="203" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A203" s="10"/>
-      <c r="B203" s="10"/>
-      <c r="C203" s="10"/>
-      <c r="D203" s="10"/>
-      <c r="E203" s="10"/>
-      <c r="F203" s="10"/>
+      <c r="A203" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C203" t="s">
+        <v>450</v>
+      </c>
+      <c r="D203" t="s">
+        <v>451</v>
+      </c>
+      <c r="E203" t="s">
+        <v>452</v>
+      </c>
+      <c r="F203" s="10" t="s">
+        <v>104</v>
+      </c>
       <c r="G203" s="10"/>
       <c r="H203" s="10"/>
       <c r="I203" s="10"/>
       <c r="J203" s="10"/>
-      <c r="K203" s="10"/>
+      <c r="K203" s="30"/>
       <c r="L203" s="10"/>
       <c r="M203" s="10"/>
       <c r="N203" s="10"/>
-      <c r="O203" s="10"/>
-      <c r="P203" s="10"/>
-      <c r="Q203" s="10"/>
-      <c r="R203" s="10"/>
-      <c r="S203" s="10"/>
-      <c r="T203" s="10"/>
-      <c r="U203" s="10"/>
-      <c r="V203" s="10"/>
+      <c r="O203">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="P203">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>453</v>
+      </c>
+      <c r="R203">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="S203">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="T203">
+        <v>0.83</v>
+      </c>
+      <c r="U203">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="V203">
+        <v>0.56599999999999995</v>
+      </c>
     </row>
     <row r="204" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A204" s="10"/>
-      <c r="B204" s="10"/>
-      <c r="C204" s="10"/>
-      <c r="D204" s="10"/>
-      <c r="E204" s="10"/>
-      <c r="F204" s="10"/>
+      <c r="A204" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C204" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D204" t="s">
+        <v>455</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="F204" t="s">
+        <v>457</v>
+      </c>
       <c r="G204" s="10"/>
       <c r="H204" s="10"/>
       <c r="I204" s="10"/>
       <c r="J204" s="10"/>
-      <c r="K204" s="10"/>
+      <c r="K204" s="30"/>
       <c r="L204" s="10"/>
       <c r="M204" s="10"/>
       <c r="N204" s="10"/>
-      <c r="O204" s="10"/>
-      <c r="P204" s="10"/>
-      <c r="Q204" s="10"/>
-      <c r="R204" s="10"/>
-      <c r="S204" s="10"/>
-      <c r="T204" s="10"/>
-      <c r="U204" s="10"/>
-      <c r="V204" s="10"/>
+      <c r="O204">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="P204">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>458</v>
+      </c>
+      <c r="R204">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="S204">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="T204">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U204">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="V204">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="205" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A205" s="10"/>
-      <c r="B205" s="10"/>
-      <c r="C205" s="10"/>
-      <c r="D205" s="10"/>
-      <c r="E205" s="10"/>
-      <c r="F205" s="10"/>
+      <c r="A205" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C205" t="s">
+        <v>459</v>
+      </c>
+      <c r="D205" t="s">
+        <v>460</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="F205" t="s">
+        <v>384</v>
+      </c>
       <c r="G205" s="10"/>
       <c r="H205" s="10"/>
       <c r="I205" s="10"/>
       <c r="J205" s="10"/>
-      <c r="K205" s="10"/>
+      <c r="K205" s="30"/>
       <c r="L205" s="10"/>
       <c r="M205" s="10"/>
       <c r="N205" s="10"/>
-      <c r="O205" s="10"/>
-      <c r="P205" s="10"/>
-      <c r="Q205" s="10"/>
-      <c r="R205" s="10"/>
-      <c r="S205" s="10"/>
-      <c r="T205" s="10"/>
-      <c r="U205" s="10"/>
-      <c r="V205" s="10"/>
+      <c r="O205">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="P205">
+        <v>0.443</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>462</v>
+      </c>
+      <c r="R205">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="S205">
+        <v>0.627</v>
+      </c>
+      <c r="T205">
+        <v>1</v>
+      </c>
+      <c r="U205">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="V205">
+        <v>0.59799999999999998</v>
+      </c>
     </row>
     <row r="206" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A206" s="10"/>
-      <c r="B206" s="10"/>
-      <c r="C206" s="10"/>
-      <c r="D206" s="10"/>
-      <c r="E206" s="10"/>
-      <c r="F206" s="10"/>
+      <c r="A206" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C206" t="s">
+        <v>463</v>
+      </c>
+      <c r="D206" t="s">
+        <v>464</v>
+      </c>
+      <c r="E206" t="s">
+        <v>465</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="G206" s="10"/>
       <c r="H206" s="10"/>
       <c r="I206" s="10"/>
       <c r="J206" s="10"/>
-      <c r="K206" s="10"/>
+      <c r="K206" s="30"/>
       <c r="L206" s="10"/>
       <c r="M206" s="10"/>
       <c r="N206" s="10"/>
-      <c r="O206" s="10"/>
-      <c r="P206" s="10"/>
-      <c r="Q206" s="10"/>
-      <c r="R206" s="10"/>
-      <c r="S206" s="10"/>
-      <c r="T206" s="10"/>
-      <c r="U206" s="10"/>
-      <c r="V206" s="10"/>
+      <c r="O206">
+        <v>0.78</v>
+      </c>
+      <c r="P206">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>466</v>
+      </c>
+      <c r="R206">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="S206">
+        <v>0.59</v>
+      </c>
+      <c r="T206">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U206">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="V206">
+        <v>0.57599999999999996</v>
+      </c>
     </row>
     <row r="207" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A207" s="10"/>
-      <c r="B207" s="10"/>
-      <c r="C207" s="10"/>
-      <c r="D207" s="10"/>
-      <c r="E207" s="10"/>
-      <c r="F207" s="10"/>
+      <c r="A207" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C207" t="s">
+        <v>467</v>
+      </c>
+      <c r="D207" t="s">
+        <v>468</v>
+      </c>
+      <c r="E207" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F207" t="s">
+        <v>469</v>
+      </c>
       <c r="G207" s="10"/>
       <c r="H207" s="10"/>
       <c r="I207" s="10"/>
       <c r="J207" s="10"/>
-      <c r="K207" s="10"/>
+      <c r="K207" s="30"/>
       <c r="L207" s="10"/>
       <c r="M207" s="10"/>
       <c r="N207" s="10"/>
-      <c r="O207" s="10"/>
-      <c r="P207" s="10"/>
-      <c r="Q207" s="10"/>
-      <c r="R207" s="10"/>
-      <c r="S207" s="10"/>
-      <c r="T207" s="10"/>
-      <c r="U207" s="10"/>
-      <c r="V207" s="10"/>
+      <c r="O207">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="P207">
+        <v>0.498</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>470</v>
+      </c>
+      <c r="R207">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="S207">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="T207">
+        <v>1</v>
+      </c>
+      <c r="U207">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="V207">
+        <v>0.55200000000000005</v>
+      </c>
     </row>
     <row r="208" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A208" s="10"/>
-      <c r="B208" s="10"/>
-      <c r="C208" s="10"/>
-      <c r="D208" s="10"/>
-      <c r="E208" s="10"/>
-      <c r="F208" s="10"/>
+      <c r="A208" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C208" t="s">
+        <v>471</v>
+      </c>
+      <c r="D208" t="s">
+        <v>472</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="F208" t="s">
+        <v>474</v>
+      </c>
       <c r="G208" s="10"/>
       <c r="H208" s="10"/>
       <c r="I208" s="10"/>
       <c r="J208" s="10"/>
-      <c r="K208" s="10"/>
+      <c r="K208" s="30"/>
       <c r="L208" s="10"/>
       <c r="M208" s="10"/>
       <c r="N208" s="10"/>
-      <c r="O208" s="10"/>
-      <c r="P208" s="10"/>
-      <c r="Q208" s="10"/>
-      <c r="R208" s="10"/>
-      <c r="S208" s="10"/>
-      <c r="T208" s="10"/>
-      <c r="U208" s="10"/>
-      <c r="V208" s="10"/>
+      <c r="O208">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="P208">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>475</v>
+      </c>
+      <c r="R208">
+        <v>0.629</v>
+      </c>
+      <c r="S208">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="T208">
+        <v>1</v>
+      </c>
+      <c r="U208">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="V208">
+        <v>0.57299999999999995</v>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V177" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}"/>
   <mergeCells count="7">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3697" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27518C61-5283-4F14-ACDC-9826A2D50C43}"/>
+  <xr:revisionPtr revIDLastSave="3849" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BAD1469-1582-4F0E-8A9A-6B2FDB9D4045}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="500">
   <si>
     <t>Date</t>
   </si>
@@ -1470,6 +1470,78 @@
   </si>
   <si>
     <t>678.99 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> gemma4:e2b</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>~4.6 GB</t>
+  </si>
+  <si>
+    <t>5721.52 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deepcoder:1.5b</t>
+  </si>
+  <si>
+    <t>1.5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 GB </t>
+  </si>
+  <si>
+    <t>smollm:1.7b-instruct-v0.2-q4_K_M</t>
+  </si>
+  <si>
+    <t>1.7B</t>
+  </si>
+  <si>
+    <t>Qwen2 1.5B</t>
+  </si>
+  <si>
+    <t>934 MB</t>
+  </si>
+  <si>
+    <t>Medllama-1B-Instruct-v3-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 807 MB</t>
+  </si>
+  <si>
+    <t>Llama SmolTalk 3.2 1B Instruct Q4_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 672 MB</t>
+  </si>
+  <si>
+    <t>KittyLM MiniCPM5 1B</t>
+  </si>
+  <si>
+    <t>377.33 ms</t>
+  </si>
+  <si>
+    <t>atlas-coder</t>
+  </si>
+  <si>
+    <t>531 Mb</t>
+  </si>
+  <si>
+    <t>Pluto AI Labs</t>
+  </si>
+  <si>
+    <t>157380.2MS</t>
+  </si>
+  <si>
+    <t>qwen3.5-0.8b</t>
+  </si>
+  <si>
+    <t>8b</t>
+  </si>
+  <si>
+    <t>5GB</t>
   </si>
 </sst>
 </file>
@@ -2383,7 +2455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V208"/>
+  <dimension ref="A1:V222"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -13124,6 +13196,574 @@
         <v>0.57299999999999995</v>
       </c>
     </row>
+    <row r="209" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A209" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C209" t="s">
+        <v>476</v>
+      </c>
+      <c r="D209" t="s">
+        <v>477</v>
+      </c>
+      <c r="E209" t="s">
+        <v>478</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G209" s="2"/>
+      <c r="H209" s="2"/>
+      <c r="I209" s="2"/>
+      <c r="J209" s="2"/>
+      <c r="K209" s="30"/>
+      <c r="L209" s="2"/>
+      <c r="M209" s="2"/>
+      <c r="N209" s="2"/>
+      <c r="O209">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="P209">
+        <v>0.501</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>479</v>
+      </c>
+      <c r="R209">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="S209">
+        <v>1</v>
+      </c>
+      <c r="T209">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="U209">
+        <v>1</v>
+      </c>
+      <c r="V209">
+        <v>0.53400000000000003</v>
+      </c>
+    </row>
+    <row r="210" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A210" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C210" t="s">
+        <v>480</v>
+      </c>
+      <c r="D210" t="s">
+        <v>481</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G210" s="2"/>
+      <c r="H210" s="2"/>
+      <c r="I210" s="2"/>
+      <c r="J210" s="2"/>
+      <c r="K210" s="30"/>
+      <c r="L210" s="2"/>
+      <c r="M210" s="2"/>
+      <c r="N210" s="2"/>
+      <c r="O210">
+        <v>0.307</v>
+      </c>
+      <c r="P210">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="Q210">
+        <v>227.69</v>
+      </c>
+      <c r="R210">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="S210">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="T210">
+        <v>1</v>
+      </c>
+      <c r="U210">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="V210">
+        <v>0.39600000000000002</v>
+      </c>
+    </row>
+    <row r="211" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A211" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C211" t="s">
+        <v>483</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2"/>
+      <c r="I211" s="2"/>
+      <c r="J211" s="2"/>
+      <c r="K211" s="30"/>
+      <c r="L211" s="2"/>
+      <c r="M211" s="2"/>
+      <c r="N211" s="2"/>
+      <c r="O211">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="P211">
+        <v>0.439</v>
+      </c>
+      <c r="Q211">
+        <v>1771.27</v>
+      </c>
+      <c r="R211">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="S211">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="T211">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U211">
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="V211">
+        <v>0.55200000000000005</v>
+      </c>
+    </row>
+    <row r="212" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A212" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C212" t="s">
+        <v>485</v>
+      </c>
+      <c r="D212" t="s">
+        <v>481</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+      <c r="I212" s="2"/>
+      <c r="J212" s="2"/>
+      <c r="K212" s="30"/>
+      <c r="L212" s="2"/>
+      <c r="M212" s="2"/>
+      <c r="N212" s="2"/>
+      <c r="O212">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="P212">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="Q212">
+        <v>795.2</v>
+      </c>
+      <c r="R212">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="S212">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="T212">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U212">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="V212">
+        <v>0.59099999999999997</v>
+      </c>
+    </row>
+    <row r="213" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A213" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
+      <c r="I213" s="2"/>
+      <c r="J213" s="2"/>
+      <c r="K213" s="30"/>
+      <c r="L213" s="2"/>
+      <c r="M213" s="2"/>
+      <c r="N213" s="2"/>
+      <c r="O213">
+        <v>0.754</v>
+      </c>
+      <c r="P213">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="Q213">
+        <v>1069.24</v>
+      </c>
+      <c r="R213">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="S213">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="T213">
+        <v>1</v>
+      </c>
+      <c r="U213">
+        <v>0.88800000000000001</v>
+      </c>
+      <c r="V213">
+        <v>0.57599999999999996</v>
+      </c>
+    </row>
+    <row r="214" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A214" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="D214" t="s">
+        <v>409</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F214" t="s">
+        <v>69</v>
+      </c>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+      <c r="I214" s="2"/>
+      <c r="J214" s="2"/>
+      <c r="K214" s="30"/>
+      <c r="L214" s="2"/>
+      <c r="M214" s="2"/>
+      <c r="N214" s="2"/>
+      <c r="O214">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="P214">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="Q214">
+        <v>1279.92</v>
+      </c>
+      <c r="R214">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="S214">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="T214">
+        <v>1</v>
+      </c>
+      <c r="U214">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="V214">
+        <v>0.57699999999999996</v>
+      </c>
+    </row>
+    <row r="215" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A215" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C215" t="s">
+        <v>491</v>
+      </c>
+      <c r="D215" t="s">
+        <v>409</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F215" t="s">
+        <v>69</v>
+      </c>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="30"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="P215">
+        <v>0.37</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>492</v>
+      </c>
+      <c r="R215">
+        <v>0.496</v>
+      </c>
+      <c r="S215">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="T215">
+        <v>1</v>
+      </c>
+      <c r="U215">
+        <v>0.63</v>
+      </c>
+      <c r="V215">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A216" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C216" t="s">
+        <v>493</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F216" t="s">
+        <v>495</v>
+      </c>
+      <c r="G216" s="23"/>
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
+      <c r="J216" s="2"/>
+      <c r="K216" s="2"/>
+      <c r="L216" s="2"/>
+      <c r="M216" s="2"/>
+      <c r="N216" s="2"/>
+      <c r="O216" s="2">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="P216" s="2">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="Q216" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="R216" s="2">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="S216" s="2">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="T216" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="U216" s="4">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="V216" s="6">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="217" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A217" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C217" s="12" t="s">
+        <v>497</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>499</v>
+      </c>
+      <c r="F217" s="2"/>
+      <c r="G217" s="2"/>
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
+      <c r="J217" s="2"/>
+      <c r="K217" s="2"/>
+      <c r="L217" s="2"/>
+      <c r="M217" s="2"/>
+      <c r="N217" s="2"/>
+      <c r="O217" s="2"/>
+      <c r="P217" s="2"/>
+      <c r="Q217" s="2"/>
+      <c r="R217" s="2"/>
+      <c r="S217" s="2"/>
+      <c r="T217" s="2"/>
+      <c r="U217" s="4"/>
+      <c r="V217" s="6"/>
+    </row>
+    <row r="218" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A218" s="13"/>
+      <c r="B218" s="10"/>
+      <c r="C218" s="12"/>
+      <c r="D218" s="2"/>
+      <c r="E218" s="2"/>
+      <c r="F218" s="2"/>
+      <c r="G218" s="2"/>
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
+      <c r="J218" s="2"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
+      <c r="M218" s="2"/>
+      <c r="N218" s="2"/>
+      <c r="O218" s="2"/>
+      <c r="P218" s="2"/>
+      <c r="Q218" s="2"/>
+      <c r="R218" s="2"/>
+      <c r="S218" s="2"/>
+      <c r="T218" s="2"/>
+      <c r="U218" s="4"/>
+      <c r="V218" s="6"/>
+    </row>
+    <row r="219" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A219" s="13"/>
+      <c r="B219" s="10"/>
+      <c r="C219" s="12"/>
+      <c r="D219" s="2"/>
+      <c r="E219" s="2"/>
+      <c r="F219" s="2"/>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
+      <c r="J219" s="2"/>
+      <c r="K219" s="2"/>
+      <c r="L219" s="2"/>
+      <c r="M219" s="2"/>
+      <c r="N219" s="2"/>
+      <c r="O219" s="2"/>
+      <c r="P219" s="2"/>
+      <c r="Q219" s="2"/>
+      <c r="R219" s="2"/>
+      <c r="S219" s="2"/>
+      <c r="T219" s="2"/>
+      <c r="U219" s="4"/>
+      <c r="V219" s="6"/>
+    </row>
+    <row r="220" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A220" s="13"/>
+      <c r="B220" s="10"/>
+      <c r="C220" s="12"/>
+      <c r="D220" s="2"/>
+      <c r="E220" s="2"/>
+      <c r="F220" s="2"/>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="2"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220" s="2"/>
+      <c r="P220" s="2"/>
+      <c r="Q220" s="2"/>
+      <c r="R220" s="2"/>
+      <c r="S220" s="2"/>
+      <c r="T220" s="2"/>
+      <c r="U220" s="4"/>
+      <c r="V220" s="6"/>
+    </row>
+    <row r="221" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A221" s="13"/>
+      <c r="B221" s="10"/>
+      <c r="C221" s="12"/>
+      <c r="D221" s="2"/>
+      <c r="E221" s="2"/>
+      <c r="F221" s="2"/>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+      <c r="N221" s="2"/>
+      <c r="O221" s="2"/>
+      <c r="P221" s="2"/>
+      <c r="Q221" s="2"/>
+      <c r="R221" s="2"/>
+      <c r="S221" s="2"/>
+      <c r="T221" s="2"/>
+      <c r="U221" s="4"/>
+      <c r="V221" s="6"/>
+    </row>
+    <row r="222" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A222" s="13"/>
+      <c r="B222" s="10"/>
+      <c r="C222" s="12"/>
+      <c r="D222" s="2"/>
+      <c r="E222" s="2"/>
+      <c r="F222" s="2"/>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+      <c r="M222" s="2"/>
+      <c r="N222" s="2"/>
+      <c r="O222" s="2"/>
+      <c r="P222" s="2"/>
+      <c r="Q222" s="2"/>
+      <c r="R222" s="2"/>
+      <c r="S222" s="2"/>
+      <c r="T222" s="2"/>
+      <c r="U222" s="4"/>
+      <c r="V222" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:A4"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3697" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27518C61-5283-4F14-ACDC-9826A2D50C43}"/>
+  <xr:revisionPtr revIDLastSave="3964" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE32F0F1-F4BF-48BD-8129-3D1AE406121E}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1240" uniqueCount="476">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="522">
   <si>
     <t>Date</t>
   </si>
@@ -1470,6 +1470,144 @@
   </si>
   <si>
     <t>678.99 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> gemma4:e2b</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>~4.6 GB</t>
+  </si>
+  <si>
+    <t>5721.52 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deepcoder:1.5b</t>
+  </si>
+  <si>
+    <t>1.5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 GB </t>
+  </si>
+  <si>
+    <t>smollm:1.7b-instruct-v0.2-q4_K_M</t>
+  </si>
+  <si>
+    <t>1.7B</t>
+  </si>
+  <si>
+    <t>Qwen2 1.5B</t>
+  </si>
+  <si>
+    <t>934 MB</t>
+  </si>
+  <si>
+    <t>Medllama-1B-Instruct-v3-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 807 MB</t>
+  </si>
+  <si>
+    <t>Llama SmolTalk 3.2 1B Instruct Q4_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 672 MB</t>
+  </si>
+  <si>
+    <t>KittyLM MiniCPM5 1B</t>
+  </si>
+  <si>
+    <t>377.33 ms</t>
+  </si>
+  <si>
+    <t>atlas-coder</t>
+  </si>
+  <si>
+    <t>531 Mb</t>
+  </si>
+  <si>
+    <t>Pluto AI Labs</t>
+  </si>
+  <si>
+    <t>157380.2MS</t>
+  </si>
+  <si>
+    <t>LFM2.5-1.2B Thinking</t>
+  </si>
+  <si>
+    <t>731mb</t>
+  </si>
+  <si>
+    <t>Falcon3:1b</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.8 GB</t>
+  </si>
+  <si>
+    <t>1369.01 ms</t>
+  </si>
+  <si>
+    <t>StableLM Zephyr 1.6B</t>
+  </si>
+  <si>
+    <t>1.6B</t>
+  </si>
+  <si>
+    <t>980MB</t>
+  </si>
+  <si>
+    <t>741.99 ms</t>
+  </si>
+  <si>
+    <t>orca-mini:3b</t>
+  </si>
+  <si>
+    <t>355.08 ms</t>
+  </si>
+  <si>
+    <t>stable-beluga:latest</t>
+  </si>
+  <si>
+    <t>1138.41 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> qwen2:1.5b</t>
+  </si>
+  <si>
+    <t>597.96 ms</t>
+  </si>
+  <si>
+    <t>openelm</t>
+  </si>
+  <si>
+    <t>0.45b</t>
+  </si>
+  <si>
+    <t>289 MB</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>11827.33 ms</t>
+  </si>
+  <si>
+    <t>pythia</t>
+  </si>
+  <si>
+    <t>0.41b</t>
+  </si>
+  <si>
+    <t>267mb</t>
+  </si>
+  <si>
+    <t>EleutherAI</t>
+  </si>
+  <si>
+    <t>9333.3ms</t>
   </si>
 </sst>
 </file>
@@ -2383,7 +2521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V208"/>
+  <dimension ref="A1:V224"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -13124,6 +13262,829 @@
         <v>0.57299999999999995</v>
       </c>
     </row>
+    <row r="209" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A209" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C209" t="s">
+        <v>476</v>
+      </c>
+      <c r="D209" t="s">
+        <v>477</v>
+      </c>
+      <c r="E209" t="s">
+        <v>478</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G209" s="2"/>
+      <c r="H209" s="2"/>
+      <c r="I209" s="2"/>
+      <c r="J209" s="2"/>
+      <c r="K209" s="30"/>
+      <c r="L209" s="2"/>
+      <c r="M209" s="2"/>
+      <c r="N209" s="2"/>
+      <c r="O209">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="P209">
+        <v>0.501</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>479</v>
+      </c>
+      <c r="R209">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="S209">
+        <v>1</v>
+      </c>
+      <c r="T209">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="U209">
+        <v>1</v>
+      </c>
+      <c r="V209">
+        <v>0.53400000000000003</v>
+      </c>
+    </row>
+    <row r="210" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A210" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C210" t="s">
+        <v>480</v>
+      </c>
+      <c r="D210" t="s">
+        <v>481</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G210" s="2"/>
+      <c r="H210" s="2"/>
+      <c r="I210" s="2"/>
+      <c r="J210" s="2"/>
+      <c r="K210" s="30"/>
+      <c r="L210" s="2"/>
+      <c r="M210" s="2"/>
+      <c r="N210" s="2"/>
+      <c r="O210">
+        <v>0.307</v>
+      </c>
+      <c r="P210">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="Q210">
+        <v>227.69</v>
+      </c>
+      <c r="R210">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="S210">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="T210">
+        <v>1</v>
+      </c>
+      <c r="U210">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="V210">
+        <v>0.39600000000000002</v>
+      </c>
+    </row>
+    <row r="211" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A211" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C211" t="s">
+        <v>483</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2"/>
+      <c r="I211" s="2"/>
+      <c r="J211" s="2"/>
+      <c r="K211" s="30"/>
+      <c r="L211" s="2"/>
+      <c r="M211" s="2"/>
+      <c r="N211" s="2"/>
+      <c r="O211">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="P211">
+        <v>0.439</v>
+      </c>
+      <c r="Q211">
+        <v>1771.27</v>
+      </c>
+      <c r="R211">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="S211">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="T211">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U211">
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="V211">
+        <v>0.55200000000000005</v>
+      </c>
+    </row>
+    <row r="212" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A212" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C212" t="s">
+        <v>485</v>
+      </c>
+      <c r="D212" t="s">
+        <v>481</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+      <c r="I212" s="2"/>
+      <c r="J212" s="2"/>
+      <c r="K212" s="30"/>
+      <c r="L212" s="2"/>
+      <c r="M212" s="2"/>
+      <c r="N212" s="2"/>
+      <c r="O212">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="P212">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="Q212">
+        <v>795.2</v>
+      </c>
+      <c r="R212">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="S212">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="T212">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U212">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="V212">
+        <v>0.59099999999999997</v>
+      </c>
+    </row>
+    <row r="213" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A213" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
+      <c r="I213" s="2"/>
+      <c r="J213" s="2"/>
+      <c r="K213" s="30"/>
+      <c r="L213" s="2"/>
+      <c r="M213" s="2"/>
+      <c r="N213" s="2"/>
+      <c r="O213">
+        <v>0.754</v>
+      </c>
+      <c r="P213">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="Q213">
+        <v>1069.24</v>
+      </c>
+      <c r="R213">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="S213">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="T213">
+        <v>1</v>
+      </c>
+      <c r="U213">
+        <v>0.88800000000000001</v>
+      </c>
+      <c r="V213">
+        <v>0.57599999999999996</v>
+      </c>
+    </row>
+    <row r="214" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A214" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="D214" t="s">
+        <v>409</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F214" t="s">
+        <v>69</v>
+      </c>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+      <c r="I214" s="2"/>
+      <c r="J214" s="2"/>
+      <c r="K214" s="30"/>
+      <c r="L214" s="2"/>
+      <c r="M214" s="2"/>
+      <c r="N214" s="2"/>
+      <c r="O214">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="P214">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="Q214">
+        <v>1279.92</v>
+      </c>
+      <c r="R214">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="S214">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="T214">
+        <v>1</v>
+      </c>
+      <c r="U214">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="V214">
+        <v>0.57699999999999996</v>
+      </c>
+    </row>
+    <row r="215" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A215" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C215" t="s">
+        <v>491</v>
+      </c>
+      <c r="D215" t="s">
+        <v>409</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F215" t="s">
+        <v>69</v>
+      </c>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="30"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="P215">
+        <v>0.37</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>492</v>
+      </c>
+      <c r="R215">
+        <v>0.496</v>
+      </c>
+      <c r="S215">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="T215">
+        <v>1</v>
+      </c>
+      <c r="U215">
+        <v>0.63</v>
+      </c>
+      <c r="V215">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A216" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C216" t="s">
+        <v>493</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F216" t="s">
+        <v>495</v>
+      </c>
+      <c r="G216" s="23"/>
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
+      <c r="J216" s="2"/>
+      <c r="K216" s="2"/>
+      <c r="L216" s="2"/>
+      <c r="M216" s="2"/>
+      <c r="N216" s="2"/>
+      <c r="O216" s="2">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="P216" s="2">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="Q216" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="R216" s="2">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="S216" s="2">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="T216" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="U216" s="4">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="V216" s="6">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="217" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A217" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C217" t="s">
+        <v>497</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G217" s="23"/>
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
+      <c r="J217" s="2"/>
+      <c r="K217" s="2"/>
+      <c r="L217" s="2"/>
+      <c r="M217" s="2"/>
+      <c r="N217" s="2"/>
+      <c r="O217">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="P217">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="Q217">
+        <v>0.71</v>
+      </c>
+      <c r="R217">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="S217">
+        <v>1</v>
+      </c>
+      <c r="T217">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="U217">
+        <v>1</v>
+      </c>
+      <c r="V217">
+        <v>0.54700000000000004</v>
+      </c>
+    </row>
+    <row r="218" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A218" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C218" t="s">
+        <v>499</v>
+      </c>
+      <c r="D218" t="s">
+        <v>409</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G218" s="23"/>
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
+      <c r="J218" s="2"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
+      <c r="M218" s="2"/>
+      <c r="N218" s="2"/>
+      <c r="O218">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="P218">
+        <v>0.624</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>501</v>
+      </c>
+      <c r="R218">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="S218">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T218">
+        <v>1</v>
+      </c>
+      <c r="U218">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="V218">
+        <v>0.61799999999999999</v>
+      </c>
+    </row>
+    <row r="219" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A219" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C219" t="s">
+        <v>502</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
+      <c r="J219" s="2"/>
+      <c r="K219" s="2"/>
+      <c r="L219" s="2"/>
+      <c r="M219" s="2"/>
+      <c r="N219" s="30"/>
+      <c r="O219">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P219">
+        <v>0.624</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>505</v>
+      </c>
+      <c r="R219">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="S219">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T219">
+        <v>1</v>
+      </c>
+      <c r="U219">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="V219">
+        <v>0.60399999999999998</v>
+      </c>
+    </row>
+    <row r="220" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A220" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D220" t="s">
+        <v>468</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="30"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="P220">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>507</v>
+      </c>
+      <c r="R220">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="S220">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="T220" s="2">
+        <v>1</v>
+      </c>
+      <c r="U220">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="V220">
+        <v>0.56299999999999994</v>
+      </c>
+    </row>
+    <row r="221" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A221" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C221" t="s">
+        <v>508</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F221" t="s">
+        <v>88</v>
+      </c>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+      <c r="N221" s="30"/>
+      <c r="O221">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="P221">
+        <v>0.53</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>509</v>
+      </c>
+      <c r="R221">
+        <v>0.624</v>
+      </c>
+      <c r="S221">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="T221">
+        <v>1</v>
+      </c>
+      <c r="U221">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="V221">
+        <v>0.55900000000000005</v>
+      </c>
+    </row>
+    <row r="222" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A222" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B222" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C222" t="s">
+        <v>510</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+      <c r="M222" s="2"/>
+      <c r="N222" s="30"/>
+      <c r="O222">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="P222">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>511</v>
+      </c>
+      <c r="R222">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="S222">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="T222">
+        <v>1</v>
+      </c>
+      <c r="U222">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="V222">
+        <v>0.61599999999999999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A223" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B223" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C223" t="s">
+        <v>512</v>
+      </c>
+      <c r="D223" t="s">
+        <v>513</v>
+      </c>
+      <c r="E223" t="s">
+        <v>514</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G223" s="23"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="2"/>
+      <c r="O223">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="P223">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>516</v>
+      </c>
+      <c r="R223">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="S223">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="T223" s="2">
+        <v>1</v>
+      </c>
+      <c r="U223" s="4">
+        <v>0.52</v>
+      </c>
+      <c r="V223" s="6">
+        <v>0.36899999999999999</v>
+      </c>
+    </row>
+    <row r="224" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A224" s="33">
+        <v>46321</v>
+      </c>
+      <c r="B224" t="s">
+        <v>367</v>
+      </c>
+      <c r="C224" t="s">
+        <v>517</v>
+      </c>
+      <c r="D224" t="s">
+        <v>518</v>
+      </c>
+      <c r="E224" t="s">
+        <v>519</v>
+      </c>
+      <c r="F224" t="s">
+        <v>520</v>
+      </c>
+      <c r="G224" s="23"/>
+      <c r="O224">
+        <v>0.217</v>
+      </c>
+      <c r="P224">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>521</v>
+      </c>
+      <c r="R224">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="S224">
+        <v>0.69</v>
+      </c>
+      <c r="T224">
+        <v>1</v>
+      </c>
+      <c r="U224">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="V224">
+        <v>0.30199999999999999</v>
+      </c>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:A4"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3849" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{0BAD1469-1582-4F0E-8A9A-6B2FDB9D4045}"/>
+  <xr:revisionPtr revIDLastSave="3964" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE32F0F1-F4BF-48BD-8129-3D1AE406121E}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1286" uniqueCount="500">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="522">
   <si>
     <t>Date</t>
   </si>
@@ -1535,13 +1535,79 @@
     <t>157380.2MS</t>
   </si>
   <si>
-    <t>qwen3.5-0.8b</t>
-  </si>
-  <si>
-    <t>8b</t>
-  </si>
-  <si>
-    <t>5GB</t>
+    <t>LFM2.5-1.2B Thinking</t>
+  </si>
+  <si>
+    <t>731mb</t>
+  </si>
+  <si>
+    <t>Falcon3:1b</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.8 GB</t>
+  </si>
+  <si>
+    <t>1369.01 ms</t>
+  </si>
+  <si>
+    <t>StableLM Zephyr 1.6B</t>
+  </si>
+  <si>
+    <t>1.6B</t>
+  </si>
+  <si>
+    <t>980MB</t>
+  </si>
+  <si>
+    <t>741.99 ms</t>
+  </si>
+  <si>
+    <t>orca-mini:3b</t>
+  </si>
+  <si>
+    <t>355.08 ms</t>
+  </si>
+  <si>
+    <t>stable-beluga:latest</t>
+  </si>
+  <si>
+    <t>1138.41 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> qwen2:1.5b</t>
+  </si>
+  <si>
+    <t>597.96 ms</t>
+  </si>
+  <si>
+    <t>openelm</t>
+  </si>
+  <si>
+    <t>0.45b</t>
+  </si>
+  <si>
+    <t>289 MB</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>11827.33 ms</t>
+  </si>
+  <si>
+    <t>pythia</t>
+  </si>
+  <si>
+    <t>0.41b</t>
+  </si>
+  <si>
+    <t>267mb</t>
+  </si>
+  <si>
+    <t>EleutherAI</t>
+  </si>
+  <si>
+    <t>9333.3ms</t>
   </si>
 </sst>
 </file>
@@ -2455,7 +2521,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V222"/>
+  <dimension ref="A1:V224"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -13617,17 +13683,19 @@
       <c r="B217" s="10" t="s">
         <v>393</v>
       </c>
-      <c r="C217" s="12" t="s">
+      <c r="C217" t="s">
         <v>497</v>
       </c>
       <c r="D217" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E217" s="2" t="s">
         <v>498</v>
       </c>
-      <c r="E217" s="2" t="s">
-        <v>499</v>
-      </c>
-      <c r="F217" s="2"/>
-      <c r="G217" s="2"/>
+      <c r="F217" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G217" s="23"/>
       <c r="H217" s="2"/>
       <c r="I217" s="2"/>
       <c r="J217" s="2"/>
@@ -13635,23 +13703,51 @@
       <c r="L217" s="2"/>
       <c r="M217" s="2"/>
       <c r="N217" s="2"/>
-      <c r="O217" s="2"/>
-      <c r="P217" s="2"/>
-      <c r="Q217" s="2"/>
-      <c r="R217" s="2"/>
-      <c r="S217" s="2"/>
-      <c r="T217" s="2"/>
-      <c r="U217" s="4"/>
-      <c r="V217" s="6"/>
+      <c r="O217">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="P217">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="Q217">
+        <v>0.71</v>
+      </c>
+      <c r="R217">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="S217">
+        <v>1</v>
+      </c>
+      <c r="T217">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="U217">
+        <v>1</v>
+      </c>
+      <c r="V217">
+        <v>0.54700000000000004</v>
+      </c>
     </row>
     <row r="218" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A218" s="13"/>
-      <c r="B218" s="10"/>
-      <c r="C218" s="12"/>
-      <c r="D218" s="2"/>
-      <c r="E218" s="2"/>
-      <c r="F218" s="2"/>
-      <c r="G218" s="2"/>
+      <c r="A218" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C218" t="s">
+        <v>499</v>
+      </c>
+      <c r="D218" t="s">
+        <v>409</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G218" s="23"/>
       <c r="H218" s="2"/>
       <c r="I218" s="2"/>
       <c r="J218" s="2"/>
@@ -13659,22 +13755,50 @@
       <c r="L218" s="2"/>
       <c r="M218" s="2"/>
       <c r="N218" s="2"/>
-      <c r="O218" s="2"/>
-      <c r="P218" s="2"/>
-      <c r="Q218" s="2"/>
-      <c r="R218" s="2"/>
-      <c r="S218" s="2"/>
-      <c r="T218" s="2"/>
-      <c r="U218" s="4"/>
-      <c r="V218" s="6"/>
+      <c r="O218">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="P218">
+        <v>0.624</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>501</v>
+      </c>
+      <c r="R218">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="S218">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T218">
+        <v>1</v>
+      </c>
+      <c r="U218">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="V218">
+        <v>0.61799999999999999</v>
+      </c>
     </row>
     <row r="219" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A219" s="13"/>
-      <c r="B219" s="10"/>
-      <c r="C219" s="12"/>
-      <c r="D219" s="2"/>
-      <c r="E219" s="2"/>
-      <c r="F219" s="2"/>
+      <c r="A219" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C219" t="s">
+        <v>502</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>88</v>
+      </c>
       <c r="G219" s="2"/>
       <c r="H219" s="2"/>
       <c r="I219" s="2"/>
@@ -13682,47 +13806,103 @@
       <c r="K219" s="2"/>
       <c r="L219" s="2"/>
       <c r="M219" s="2"/>
-      <c r="N219" s="2"/>
-      <c r="O219" s="2"/>
-      <c r="P219" s="2"/>
-      <c r="Q219" s="2"/>
-      <c r="R219" s="2"/>
-      <c r="S219" s="2"/>
-      <c r="T219" s="2"/>
-      <c r="U219" s="4"/>
-      <c r="V219" s="6"/>
+      <c r="N219" s="30"/>
+      <c r="O219">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P219">
+        <v>0.624</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>505</v>
+      </c>
+      <c r="R219">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="S219">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T219">
+        <v>1</v>
+      </c>
+      <c r="U219">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="V219">
+        <v>0.60399999999999998</v>
+      </c>
     </row>
     <row r="220" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A220" s="13"/>
-      <c r="B220" s="10"/>
-      <c r="C220" s="12"/>
-      <c r="D220" s="2"/>
-      <c r="E220" s="2"/>
-      <c r="F220" s="2"/>
+      <c r="A220" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D220" t="s">
+        <v>468</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G220" s="2"/>
       <c r="H220" s="2"/>
       <c r="I220" s="2"/>
       <c r="J220" s="2"/>
-      <c r="K220" s="2"/>
+      <c r="K220" s="30"/>
       <c r="L220" s="2"/>
       <c r="M220" s="2"/>
       <c r="N220" s="2"/>
-      <c r="O220" s="2"/>
-      <c r="P220" s="2"/>
-      <c r="Q220" s="2"/>
-      <c r="R220" s="2"/>
-      <c r="S220" s="2"/>
-      <c r="T220" s="2"/>
-      <c r="U220" s="4"/>
-      <c r="V220" s="6"/>
+      <c r="O220">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="P220">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>507</v>
+      </c>
+      <c r="R220">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="S220">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="T220" s="2">
+        <v>1</v>
+      </c>
+      <c r="U220">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="V220">
+        <v>0.56299999999999994</v>
+      </c>
     </row>
     <row r="221" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A221" s="13"/>
-      <c r="B221" s="10"/>
-      <c r="C221" s="12"/>
-      <c r="D221" s="2"/>
-      <c r="E221" s="2"/>
-      <c r="F221" s="2"/>
+      <c r="A221" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C221" t="s">
+        <v>508</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F221" t="s">
+        <v>88</v>
+      </c>
       <c r="G221" s="2"/>
       <c r="H221" s="2"/>
       <c r="I221" s="2"/>
@@ -13730,23 +13910,51 @@
       <c r="K221" s="2"/>
       <c r="L221" s="2"/>
       <c r="M221" s="2"/>
-      <c r="N221" s="2"/>
-      <c r="O221" s="2"/>
-      <c r="P221" s="2"/>
-      <c r="Q221" s="2"/>
-      <c r="R221" s="2"/>
-      <c r="S221" s="2"/>
-      <c r="T221" s="2"/>
-      <c r="U221" s="4"/>
-      <c r="V221" s="6"/>
+      <c r="N221" s="30"/>
+      <c r="O221">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="P221">
+        <v>0.53</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>509</v>
+      </c>
+      <c r="R221">
+        <v>0.624</v>
+      </c>
+      <c r="S221">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="T221">
+        <v>1</v>
+      </c>
+      <c r="U221">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="V221">
+        <v>0.55900000000000005</v>
+      </c>
     </row>
     <row r="222" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A222" s="13"/>
-      <c r="B222" s="10"/>
-      <c r="C222" s="12"/>
-      <c r="D222" s="2"/>
-      <c r="E222" s="2"/>
-      <c r="F222" s="2"/>
+      <c r="A222" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B222" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C222" t="s">
+        <v>510</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="G222" s="2"/>
       <c r="H222" s="2"/>
       <c r="I222" s="2"/>
@@ -13754,15 +13962,128 @@
       <c r="K222" s="2"/>
       <c r="L222" s="2"/>
       <c r="M222" s="2"/>
-      <c r="N222" s="2"/>
-      <c r="O222" s="2"/>
-      <c r="P222" s="2"/>
-      <c r="Q222" s="2"/>
-      <c r="R222" s="2"/>
-      <c r="S222" s="2"/>
-      <c r="T222" s="2"/>
-      <c r="U222" s="4"/>
-      <c r="V222" s="6"/>
+      <c r="N222" s="30"/>
+      <c r="O222">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="P222">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>511</v>
+      </c>
+      <c r="R222">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="S222">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="T222">
+        <v>1</v>
+      </c>
+      <c r="U222">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="V222">
+        <v>0.61599999999999999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A223" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B223" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C223" t="s">
+        <v>512</v>
+      </c>
+      <c r="D223" t="s">
+        <v>513</v>
+      </c>
+      <c r="E223" t="s">
+        <v>514</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G223" s="23"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="2"/>
+      <c r="O223">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="P223">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>516</v>
+      </c>
+      <c r="R223">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="S223">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="T223" s="2">
+        <v>1</v>
+      </c>
+      <c r="U223" s="4">
+        <v>0.52</v>
+      </c>
+      <c r="V223" s="6">
+        <v>0.36899999999999999</v>
+      </c>
+    </row>
+    <row r="224" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A224" s="33">
+        <v>46321</v>
+      </c>
+      <c r="B224" t="s">
+        <v>367</v>
+      </c>
+      <c r="C224" t="s">
+        <v>517</v>
+      </c>
+      <c r="D224" t="s">
+        <v>518</v>
+      </c>
+      <c r="E224" t="s">
+        <v>519</v>
+      </c>
+      <c r="F224" t="s">
+        <v>520</v>
+      </c>
+      <c r="G224" s="23"/>
+      <c r="O224">
+        <v>0.217</v>
+      </c>
+      <c r="P224">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>521</v>
+      </c>
+      <c r="R224">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="S224">
+        <v>0.69</v>
+      </c>
+      <c r="T224">
+        <v>1</v>
+      </c>
+      <c r="U224">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="V224">
+        <v>0.30199999999999999</v>
+      </c>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30610"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3588" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E37EE749-A618-4E1E-AFF9-591BEE3BC393}"/>
+  <xr:revisionPtr revIDLastSave="4064" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EEE79EC-44BA-4F66-961A-363F0D4E6545}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$4</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$4:$V$204</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1180" uniqueCount="435">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="539">
   <si>
     <t>Date</t>
   </si>
@@ -1347,6 +1347,318 @@
   </si>
   <si>
     <t>7631.99 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> granite3.2</t>
+  </si>
+  <si>
+    <t>1707.52 ms</t>
+  </si>
+  <si>
+    <t>h2oai</t>
+  </si>
+  <si>
+    <t>350 MB</t>
+  </si>
+  <si>
+    <t>H2O.ai</t>
+  </si>
+  <si>
+    <t>1161.33 ms</t>
+  </si>
+  <si>
+    <t>aya-expanse</t>
+  </si>
+  <si>
+    <t>8B</t>
+  </si>
+  <si>
+    <t>5.0 GB</t>
+  </si>
+  <si>
+    <t>Cohere</t>
+  </si>
+  <si>
+    <t>4022.08 ms</t>
+  </si>
+  <si>
+    <t>command-r7b:latest</t>
+  </si>
+  <si>
+    <t>7B</t>
+  </si>
+  <si>
+    <t>5.1GB</t>
+  </si>
+  <si>
+    <t>4854.99 ms</t>
+  </si>
+  <si>
+    <t>mistral-nemo:12b</t>
+  </si>
+  <si>
+    <t>12B</t>
+  </si>
+  <si>
+    <t>7.1 GB</t>
+  </si>
+  <si>
+    <t>3382.15 ms</t>
+  </si>
+  <si>
+    <t>Ling-3.0-tiny-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>7.9B total (1.3B active)</t>
+  </si>
+  <si>
+    <t>6.4GB</t>
+  </si>
+  <si>
+    <t>inclusionAI</t>
+  </si>
+  <si>
+    <t>3023.63 ms</t>
+  </si>
+  <si>
+    <t>EXAONE Deep 2.4B</t>
+  </si>
+  <si>
+    <t>2.4B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.2 GB </t>
+  </si>
+  <si>
+    <t>6742.69 ms</t>
+  </si>
+  <si>
+    <t>Phi-4-mini-instruct</t>
+  </si>
+  <si>
+    <t>3.8B</t>
+  </si>
+  <si>
+    <t>2.49 GB</t>
+  </si>
+  <si>
+    <t>2222.52 ms</t>
+  </si>
+  <si>
+    <t>Stable Code Instruct 3B Q4_K_M</t>
+  </si>
+  <si>
+    <t>3B</t>
+  </si>
+  <si>
+    <t>Stability A</t>
+  </si>
+  <si>
+    <t>429.65 ms</t>
+  </si>
+  <si>
+    <t>Nemotron Mini 4B Instruct Q4_K_M</t>
+  </si>
+  <si>
+    <t>4B</t>
+  </si>
+  <si>
+    <t>2.7GB</t>
+  </si>
+  <si>
+    <t>NVIDIA</t>
+  </si>
+  <si>
+    <t>678.99 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> gemma4:e2b</t>
+  </si>
+  <si>
+    <t>2B</t>
+  </si>
+  <si>
+    <t>~4.6 GB</t>
+  </si>
+  <si>
+    <t>5721.52 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> deepcoder:1.5b</t>
+  </si>
+  <si>
+    <t>1.5B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.1 GB </t>
+  </si>
+  <si>
+    <t>smollm:1.7b-instruct-v0.2-q4_K_M</t>
+  </si>
+  <si>
+    <t>1.7B</t>
+  </si>
+  <si>
+    <t>Qwen2 1.5B</t>
+  </si>
+  <si>
+    <t>934 MB</t>
+  </si>
+  <si>
+    <t>Medllama-1B-Instruct-v3-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 807 MB</t>
+  </si>
+  <si>
+    <t>Llama SmolTalk 3.2 1B Instruct Q4_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 672 MB</t>
+  </si>
+  <si>
+    <t>KittyLM MiniCPM5 1B</t>
+  </si>
+  <si>
+    <t>377.33 ms</t>
+  </si>
+  <si>
+    <t>atlas-coder</t>
+  </si>
+  <si>
+    <t>531 Mb</t>
+  </si>
+  <si>
+    <t>Pluto AI Labs</t>
+  </si>
+  <si>
+    <t>157380.2MS</t>
+  </si>
+  <si>
+    <t>LFM2.5-1.2B Thinking</t>
+  </si>
+  <si>
+    <t>731mb</t>
+  </si>
+  <si>
+    <t>Falcon3:1b</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.8 GB</t>
+  </si>
+  <si>
+    <t>1369.01 ms</t>
+  </si>
+  <si>
+    <t>StableLM Zephyr 1.6B</t>
+  </si>
+  <si>
+    <t>1.6B</t>
+  </si>
+  <si>
+    <t>980MB</t>
+  </si>
+  <si>
+    <t>741.99 ms</t>
+  </si>
+  <si>
+    <t>orca-mini:3b</t>
+  </si>
+  <si>
+    <t>355.08 ms</t>
+  </si>
+  <si>
+    <t>stable-beluga:latest</t>
+  </si>
+  <si>
+    <t>1138.41 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> qwen2:1.5b</t>
+  </si>
+  <si>
+    <t>597.96 ms</t>
+  </si>
+  <si>
+    <t>openelm</t>
+  </si>
+  <si>
+    <t>0.45b</t>
+  </si>
+  <si>
+    <t>289 MB</t>
+  </si>
+  <si>
+    <t>Apple</t>
+  </si>
+  <si>
+    <t>11827.33 ms</t>
+  </si>
+  <si>
+    <t>pythia</t>
+  </si>
+  <si>
+    <t>0.41b</t>
+  </si>
+  <si>
+    <t>267mb</t>
+  </si>
+  <si>
+    <t>EleutherAI</t>
+  </si>
+  <si>
+    <t>9333.3ms</t>
+  </si>
+  <si>
+    <t>Llama 3.2 1B Instruct (Q4_K_M)</t>
+  </si>
+  <si>
+    <t>807mb</t>
+  </si>
+  <si>
+    <t>765.95 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> neural-chat:7b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4.7 GB</t>
+  </si>
+  <si>
+    <t>1356.38 ms</t>
+  </si>
+  <si>
+    <t>dolphin-phi</t>
+  </si>
+  <si>
+    <t>1.6GB</t>
+  </si>
+  <si>
+    <t>954.49 ms</t>
+  </si>
+  <si>
+    <t>dolphin-mistral:latest</t>
+  </si>
+  <si>
+    <t>1548.55 ms</t>
+  </si>
+  <si>
+    <t>granite3.1-dense:2b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6GB </t>
+  </si>
+  <si>
+    <t>1503.92 ms</t>
+  </si>
+  <si>
+    <t>openhermes:latest</t>
+  </si>
+  <si>
+    <t>Teknium</t>
+  </si>
+  <si>
+    <t>1460.91 ms</t>
   </si>
 </sst>
 </file>
@@ -2260,7 +2572,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V208"/>
+  <dimension ref="A1:V240"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -12485,9 +12797,24 @@
       </c>
     </row>
     <row r="199" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A199" s="10"/>
-      <c r="B199" s="10"/>
-      <c r="D199" s="10"/>
+      <c r="A199" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B199" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C199" t="s">
+        <v>435</v>
+      </c>
+      <c r="D199" s="10" t="s">
+        <v>244</v>
+      </c>
+      <c r="E199" t="s">
+        <v>95</v>
+      </c>
+      <c r="F199" t="s">
+        <v>83</v>
+      </c>
       <c r="G199" s="10"/>
       <c r="H199" s="10"/>
       <c r="I199" s="10"/>
@@ -12495,23 +12822,51 @@
       <c r="K199" s="10"/>
       <c r="L199" s="10"/>
       <c r="M199" s="10"/>
-      <c r="N199" s="10"/>
-      <c r="O199" s="10"/>
-      <c r="P199" s="10"/>
-      <c r="Q199" s="10"/>
-      <c r="R199" s="10"/>
-      <c r="S199" s="10"/>
-      <c r="T199" s="10"/>
-      <c r="U199" s="10"/>
-      <c r="V199" s="10"/>
+      <c r="N199" s="30"/>
+      <c r="O199">
+        <v>0.76200000000000001</v>
+      </c>
+      <c r="P199">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="Q199" t="s">
+        <v>436</v>
+      </c>
+      <c r="R199">
+        <v>0.71</v>
+      </c>
+      <c r="S199">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="T199">
+        <v>1</v>
+      </c>
+      <c r="U199">
+        <v>0.873</v>
+      </c>
+      <c r="V199">
+        <v>0.623</v>
+      </c>
     </row>
     <row r="200" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A200" s="10"/>
-      <c r="B200" s="10"/>
-      <c r="C200" s="10"/>
-      <c r="D200" s="10"/>
-      <c r="E200" s="10"/>
-      <c r="F200" s="10"/>
+      <c r="A200" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B200" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C200" t="s">
+        <v>437</v>
+      </c>
+      <c r="D200" s="10" t="s">
+        <v>419</v>
+      </c>
+      <c r="E200" t="s">
+        <v>438</v>
+      </c>
+      <c r="F200" t="s">
+        <v>439</v>
+      </c>
       <c r="G200" s="10"/>
       <c r="H200" s="10"/>
       <c r="I200" s="10"/>
@@ -12519,210 +12874,1821 @@
       <c r="K200" s="10"/>
       <c r="L200" s="10"/>
       <c r="M200" s="10"/>
-      <c r="N200" s="10"/>
-      <c r="O200" s="10"/>
-      <c r="P200" s="10"/>
-      <c r="Q200" s="10"/>
-      <c r="R200" s="10"/>
-      <c r="S200" s="10"/>
-      <c r="T200" s="10"/>
-      <c r="U200" s="10"/>
-      <c r="V200" s="10"/>
+      <c r="N200" s="30"/>
+      <c r="O200">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="P200">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="Q200" t="s">
+        <v>440</v>
+      </c>
+      <c r="R200">
+        <v>0.67900000000000005</v>
+      </c>
+      <c r="T200">
+        <v>1</v>
+      </c>
+      <c r="U200">
+        <v>0.81100000000000005</v>
+      </c>
+      <c r="V200">
+        <v>0.57499999999999996</v>
+      </c>
     </row>
     <row r="201" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A201" s="10"/>
-      <c r="B201" s="10"/>
-      <c r="C201" s="10"/>
-      <c r="D201" s="10"/>
-      <c r="E201" s="10"/>
-      <c r="F201" s="10"/>
+      <c r="A201" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B201" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C201" t="s">
+        <v>441</v>
+      </c>
+      <c r="D201" t="s">
+        <v>442</v>
+      </c>
+      <c r="E201" t="s">
+        <v>443</v>
+      </c>
+      <c r="F201" t="s">
+        <v>444</v>
+      </c>
       <c r="G201" s="10"/>
       <c r="H201" s="10"/>
       <c r="I201" s="10"/>
       <c r="J201" s="10"/>
-      <c r="K201" s="10"/>
+      <c r="K201" s="30"/>
       <c r="L201" s="10"/>
       <c r="M201" s="10"/>
       <c r="N201" s="10"/>
-      <c r="O201" s="10"/>
-      <c r="P201" s="10"/>
-      <c r="Q201" s="10"/>
-      <c r="R201" s="10"/>
-      <c r="S201" s="10"/>
-      <c r="T201" s="10"/>
-      <c r="U201" s="10"/>
-      <c r="V201" s="10"/>
+      <c r="O201">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="P201">
+        <v>0.47799999999999998</v>
+      </c>
+      <c r="Q201" t="s">
+        <v>445</v>
+      </c>
+      <c r="R201">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="S201">
+        <v>0.59899999999999998</v>
+      </c>
+      <c r="T201">
+        <v>1</v>
+      </c>
+      <c r="U201">
+        <v>0.92</v>
+      </c>
+      <c r="V201">
+        <v>0.59399999999999997</v>
+      </c>
     </row>
     <row r="202" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A202" s="10"/>
-      <c r="B202" s="10"/>
-      <c r="C202" s="10"/>
-      <c r="D202" s="10"/>
-      <c r="E202" s="10"/>
-      <c r="F202" s="10"/>
+      <c r="A202" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B202" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C202" t="s">
+        <v>446</v>
+      </c>
+      <c r="D202" t="s">
+        <v>447</v>
+      </c>
+      <c r="E202" t="s">
+        <v>448</v>
+      </c>
+      <c r="F202" t="s">
+        <v>444</v>
+      </c>
       <c r="G202" s="10"/>
       <c r="H202" s="10"/>
       <c r="I202" s="10"/>
       <c r="J202" s="10"/>
-      <c r="K202" s="10"/>
+      <c r="K202" s="30"/>
       <c r="L202" s="10"/>
       <c r="M202" s="10"/>
       <c r="N202" s="10"/>
-      <c r="O202" s="10"/>
-      <c r="P202" s="10"/>
-      <c r="Q202" s="10"/>
-      <c r="R202" s="10"/>
-      <c r="S202" s="10"/>
-      <c r="T202" s="10"/>
-      <c r="U202" s="10"/>
-      <c r="V202" s="10"/>
+      <c r="O202">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="P202">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="Q202" t="s">
+        <v>449</v>
+      </c>
+      <c r="R202">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="S202">
+        <v>0.61</v>
+      </c>
+      <c r="T202">
+        <v>1</v>
+      </c>
+      <c r="U202">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="V202">
+        <v>0.59</v>
+      </c>
     </row>
     <row r="203" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A203" s="10"/>
-      <c r="B203" s="10"/>
-      <c r="C203" s="10"/>
-      <c r="D203" s="10"/>
-      <c r="E203" s="10"/>
-      <c r="F203" s="10"/>
+      <c r="A203" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B203" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C203" t="s">
+        <v>450</v>
+      </c>
+      <c r="D203" t="s">
+        <v>451</v>
+      </c>
+      <c r="E203" t="s">
+        <v>452</v>
+      </c>
+      <c r="F203" s="10" t="s">
+        <v>104</v>
+      </c>
       <c r="G203" s="10"/>
       <c r="H203" s="10"/>
       <c r="I203" s="10"/>
       <c r="J203" s="10"/>
-      <c r="K203" s="10"/>
+      <c r="K203" s="30"/>
       <c r="L203" s="10"/>
       <c r="M203" s="10"/>
       <c r="N203" s="10"/>
-      <c r="O203" s="10"/>
-      <c r="P203" s="10"/>
-      <c r="Q203" s="10"/>
-      <c r="R203" s="10"/>
-      <c r="S203" s="10"/>
-      <c r="T203" s="10"/>
-      <c r="U203" s="10"/>
-      <c r="V203" s="10"/>
+      <c r="O203">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="P203">
+        <v>0.45100000000000001</v>
+      </c>
+      <c r="Q203" t="s">
+        <v>453</v>
+      </c>
+      <c r="R203">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="S203">
+        <v>0.61599999999999999</v>
+      </c>
+      <c r="T203">
+        <v>0.83</v>
+      </c>
+      <c r="U203">
+        <v>0.91400000000000003</v>
+      </c>
+      <c r="V203">
+        <v>0.56599999999999995</v>
+      </c>
     </row>
     <row r="204" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A204" s="10"/>
-      <c r="B204" s="10"/>
-      <c r="C204" s="10"/>
-      <c r="D204" s="10"/>
-      <c r="E204" s="10"/>
-      <c r="F204" s="10"/>
+      <c r="A204" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B204" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C204" s="10" t="s">
+        <v>454</v>
+      </c>
+      <c r="D204" t="s">
+        <v>455</v>
+      </c>
+      <c r="E204" s="10" t="s">
+        <v>456</v>
+      </c>
+      <c r="F204" t="s">
+        <v>457</v>
+      </c>
       <c r="G204" s="10"/>
       <c r="H204" s="10"/>
       <c r="I204" s="10"/>
       <c r="J204" s="10"/>
-      <c r="K204" s="10"/>
+      <c r="K204" s="30"/>
       <c r="L204" s="10"/>
       <c r="M204" s="10"/>
       <c r="N204" s="10"/>
-      <c r="O204" s="10"/>
-      <c r="P204" s="10"/>
-      <c r="Q204" s="10"/>
-      <c r="R204" s="10"/>
-      <c r="S204" s="10"/>
-      <c r="T204" s="10"/>
-      <c r="U204" s="10"/>
-      <c r="V204" s="10"/>
+      <c r="O204">
+        <v>0.69099999999999995</v>
+      </c>
+      <c r="P204">
+        <v>0.48699999999999999</v>
+      </c>
+      <c r="Q204" t="s">
+        <v>458</v>
+      </c>
+      <c r="R204">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="S204">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="T204">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U204">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="V204">
+        <v>0.54</v>
+      </c>
     </row>
     <row r="205" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A205" s="10"/>
-      <c r="B205" s="10"/>
-      <c r="C205" s="10"/>
-      <c r="D205" s="10"/>
-      <c r="E205" s="10"/>
-      <c r="F205" s="10"/>
+      <c r="A205" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B205" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C205" t="s">
+        <v>459</v>
+      </c>
+      <c r="D205" t="s">
+        <v>460</v>
+      </c>
+      <c r="E205" s="10" t="s">
+        <v>461</v>
+      </c>
+      <c r="F205" t="s">
+        <v>384</v>
+      </c>
       <c r="G205" s="10"/>
       <c r="H205" s="10"/>
       <c r="I205" s="10"/>
       <c r="J205" s="10"/>
-      <c r="K205" s="10"/>
+      <c r="K205" s="30"/>
       <c r="L205" s="10"/>
       <c r="M205" s="10"/>
       <c r="N205" s="10"/>
-      <c r="O205" s="10"/>
-      <c r="P205" s="10"/>
-      <c r="Q205" s="10"/>
-      <c r="R205" s="10"/>
-      <c r="S205" s="10"/>
-      <c r="T205" s="10"/>
-      <c r="U205" s="10"/>
-      <c r="V205" s="10"/>
+      <c r="O205">
+        <v>0.92900000000000005</v>
+      </c>
+      <c r="P205">
+        <v>0.443</v>
+      </c>
+      <c r="Q205" t="s">
+        <v>462</v>
+      </c>
+      <c r="R205">
+        <v>0.55400000000000005</v>
+      </c>
+      <c r="S205">
+        <v>0.627</v>
+      </c>
+      <c r="T205">
+        <v>1</v>
+      </c>
+      <c r="U205">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="V205">
+        <v>0.59799999999999998</v>
+      </c>
     </row>
     <row r="206" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A206" s="10"/>
-      <c r="B206" s="10"/>
-      <c r="C206" s="10"/>
-      <c r="D206" s="10"/>
-      <c r="E206" s="10"/>
-      <c r="F206" s="10"/>
+      <c r="A206" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B206" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C206" t="s">
+        <v>463</v>
+      </c>
+      <c r="D206" t="s">
+        <v>464</v>
+      </c>
+      <c r="E206" t="s">
+        <v>465</v>
+      </c>
+      <c r="F206" s="10" t="s">
+        <v>50</v>
+      </c>
       <c r="G206" s="10"/>
       <c r="H206" s="10"/>
       <c r="I206" s="10"/>
       <c r="J206" s="10"/>
-      <c r="K206" s="10"/>
+      <c r="K206" s="30"/>
       <c r="L206" s="10"/>
       <c r="M206" s="10"/>
       <c r="N206" s="10"/>
-      <c r="O206" s="10"/>
-      <c r="P206" s="10"/>
-      <c r="Q206" s="10"/>
-      <c r="R206" s="10"/>
-      <c r="S206" s="10"/>
-      <c r="T206" s="10"/>
-      <c r="U206" s="10"/>
-      <c r="V206" s="10"/>
+      <c r="O206">
+        <v>0.78</v>
+      </c>
+      <c r="P206">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="Q206" t="s">
+        <v>466</v>
+      </c>
+      <c r="R206">
+        <v>0.61299999999999999</v>
+      </c>
+      <c r="S206">
+        <v>0.59</v>
+      </c>
+      <c r="T206">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U206">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="V206">
+        <v>0.57599999999999996</v>
+      </c>
     </row>
     <row r="207" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A207" s="10"/>
-      <c r="B207" s="10"/>
-      <c r="C207" s="10"/>
-      <c r="D207" s="10"/>
-      <c r="E207" s="10"/>
-      <c r="F207" s="10"/>
+      <c r="A207" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B207" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C207" t="s">
+        <v>467</v>
+      </c>
+      <c r="D207" t="s">
+        <v>468</v>
+      </c>
+      <c r="E207" s="10" t="s">
+        <v>245</v>
+      </c>
+      <c r="F207" t="s">
+        <v>469</v>
+      </c>
       <c r="G207" s="10"/>
       <c r="H207" s="10"/>
       <c r="I207" s="10"/>
       <c r="J207" s="10"/>
-      <c r="K207" s="10"/>
+      <c r="K207" s="30"/>
       <c r="L207" s="10"/>
       <c r="M207" s="10"/>
       <c r="N207" s="10"/>
-      <c r="O207" s="10"/>
-      <c r="P207" s="10"/>
-      <c r="Q207" s="10"/>
-      <c r="R207" s="10"/>
-      <c r="S207" s="10"/>
-      <c r="T207" s="10"/>
-      <c r="U207" s="10"/>
-      <c r="V207" s="10"/>
+      <c r="O207">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="P207">
+        <v>0.498</v>
+      </c>
+      <c r="Q207" t="s">
+        <v>470</v>
+      </c>
+      <c r="R207">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="S207">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="T207">
+        <v>1</v>
+      </c>
+      <c r="U207">
+        <v>0.79500000000000004</v>
+      </c>
+      <c r="V207">
+        <v>0.55200000000000005</v>
+      </c>
     </row>
     <row r="208" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A208" s="10"/>
-      <c r="B208" s="10"/>
-      <c r="C208" s="10"/>
-      <c r="D208" s="10"/>
-      <c r="E208" s="10"/>
-      <c r="F208" s="10"/>
+      <c r="A208" s="13">
+        <v>46318</v>
+      </c>
+      <c r="B208" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C208" t="s">
+        <v>471</v>
+      </c>
+      <c r="D208" t="s">
+        <v>472</v>
+      </c>
+      <c r="E208" s="10" t="s">
+        <v>473</v>
+      </c>
+      <c r="F208" t="s">
+        <v>474</v>
+      </c>
       <c r="G208" s="10"/>
       <c r="H208" s="10"/>
       <c r="I208" s="10"/>
       <c r="J208" s="10"/>
-      <c r="K208" s="10"/>
+      <c r="K208" s="30"/>
       <c r="L208" s="10"/>
       <c r="M208" s="10"/>
       <c r="N208" s="10"/>
-      <c r="O208" s="10"/>
-      <c r="P208" s="10"/>
-      <c r="Q208" s="10"/>
-      <c r="R208" s="10"/>
-      <c r="S208" s="10"/>
-      <c r="T208" s="10"/>
-      <c r="U208" s="10"/>
-      <c r="V208" s="10"/>
+      <c r="O208">
+        <v>0.59499999999999997</v>
+      </c>
+      <c r="P208">
+        <v>0.53600000000000003</v>
+      </c>
+      <c r="Q208" t="s">
+        <v>475</v>
+      </c>
+      <c r="R208">
+        <v>0.629</v>
+      </c>
+      <c r="S208">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="T208">
+        <v>1</v>
+      </c>
+      <c r="U208">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="V208">
+        <v>0.57299999999999995</v>
+      </c>
+    </row>
+    <row r="209" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A209" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B209" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C209" t="s">
+        <v>476</v>
+      </c>
+      <c r="D209" t="s">
+        <v>477</v>
+      </c>
+      <c r="E209" t="s">
+        <v>478</v>
+      </c>
+      <c r="F209" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G209" s="2"/>
+      <c r="H209" s="2"/>
+      <c r="I209" s="2"/>
+      <c r="J209" s="2"/>
+      <c r="K209" s="30"/>
+      <c r="L209" s="2"/>
+      <c r="M209" s="2"/>
+      <c r="N209" s="2"/>
+      <c r="O209">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="P209">
+        <v>0.501</v>
+      </c>
+      <c r="Q209" t="s">
+        <v>479</v>
+      </c>
+      <c r="R209">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="S209">
+        <v>1</v>
+      </c>
+      <c r="T209">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="U209">
+        <v>1</v>
+      </c>
+      <c r="V209">
+        <v>0.53400000000000003</v>
+      </c>
+    </row>
+    <row r="210" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A210" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B210" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C210" t="s">
+        <v>480</v>
+      </c>
+      <c r="D210" t="s">
+        <v>481</v>
+      </c>
+      <c r="E210" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F210" s="2" t="s">
+        <v>123</v>
+      </c>
+      <c r="G210" s="2"/>
+      <c r="H210" s="2"/>
+      <c r="I210" s="2"/>
+      <c r="J210" s="2"/>
+      <c r="K210" s="30"/>
+      <c r="L210" s="2"/>
+      <c r="M210" s="2"/>
+      <c r="N210" s="2"/>
+      <c r="O210">
+        <v>0.307</v>
+      </c>
+      <c r="P210">
+        <v>0.34799999999999998</v>
+      </c>
+      <c r="Q210">
+        <v>227.69</v>
+      </c>
+      <c r="R210">
+        <v>0.47899999999999998</v>
+      </c>
+      <c r="S210">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="T210">
+        <v>1</v>
+      </c>
+      <c r="U210">
+        <v>0.38700000000000001</v>
+      </c>
+      <c r="V210">
+        <v>0.39600000000000002</v>
+      </c>
+    </row>
+    <row r="211" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A211" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B211" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C211" t="s">
+        <v>483</v>
+      </c>
+      <c r="D211" s="2" t="s">
+        <v>484</v>
+      </c>
+      <c r="E211" s="2" t="s">
+        <v>482</v>
+      </c>
+      <c r="F211" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G211" s="2"/>
+      <c r="H211" s="2"/>
+      <c r="I211" s="2"/>
+      <c r="J211" s="2"/>
+      <c r="K211" s="30"/>
+      <c r="L211" s="2"/>
+      <c r="M211" s="2"/>
+      <c r="N211" s="2"/>
+      <c r="O211">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="P211">
+        <v>0.439</v>
+      </c>
+      <c r="Q211">
+        <v>1771.27</v>
+      </c>
+      <c r="R211">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="S211">
+        <v>0.61699999999999999</v>
+      </c>
+      <c r="T211">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U211">
+        <v>0.92100000000000004</v>
+      </c>
+      <c r="V211">
+        <v>0.55200000000000005</v>
+      </c>
+    </row>
+    <row r="212" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A212" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B212" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C212" t="s">
+        <v>485</v>
+      </c>
+      <c r="D212" t="s">
+        <v>481</v>
+      </c>
+      <c r="E212" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F212" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G212" s="2"/>
+      <c r="H212" s="2"/>
+      <c r="I212" s="2"/>
+      <c r="J212" s="2"/>
+      <c r="K212" s="30"/>
+      <c r="L212" s="2"/>
+      <c r="M212" s="2"/>
+      <c r="N212" s="2"/>
+      <c r="O212">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="P212">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="Q212">
+        <v>795.2</v>
+      </c>
+      <c r="R212">
+        <v>0.63400000000000001</v>
+      </c>
+      <c r="S212">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="T212">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U212">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="V212">
+        <v>0.59099999999999997</v>
+      </c>
+    </row>
+    <row r="213" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A213" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B213" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C213" s="12" t="s">
+        <v>487</v>
+      </c>
+      <c r="D213" s="2"/>
+      <c r="E213" s="2" t="s">
+        <v>488</v>
+      </c>
+      <c r="F213" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G213" s="2"/>
+      <c r="H213" s="2"/>
+      <c r="I213" s="2"/>
+      <c r="J213" s="2"/>
+      <c r="K213" s="30"/>
+      <c r="L213" s="2"/>
+      <c r="M213" s="2"/>
+      <c r="N213" s="2"/>
+      <c r="O213">
+        <v>0.754</v>
+      </c>
+      <c r="P213">
+        <v>0.45200000000000001</v>
+      </c>
+      <c r="Q213">
+        <v>1069.24</v>
+      </c>
+      <c r="R213">
+        <v>0.56200000000000006</v>
+      </c>
+      <c r="S213">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="T213">
+        <v>1</v>
+      </c>
+      <c r="U213">
+        <v>0.88800000000000001</v>
+      </c>
+      <c r="V213">
+        <v>0.57599999999999996</v>
+      </c>
+    </row>
+    <row r="214" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A214" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B214" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C214" s="12" t="s">
+        <v>489</v>
+      </c>
+      <c r="D214" t="s">
+        <v>409</v>
+      </c>
+      <c r="E214" s="2" t="s">
+        <v>490</v>
+      </c>
+      <c r="F214" t="s">
+        <v>69</v>
+      </c>
+      <c r="G214" s="2"/>
+      <c r="H214" s="2"/>
+      <c r="I214" s="2"/>
+      <c r="J214" s="2"/>
+      <c r="K214" s="30"/>
+      <c r="L214" s="2"/>
+      <c r="M214" s="2"/>
+      <c r="N214" s="2"/>
+      <c r="O214">
+        <v>0.81599999999999995</v>
+      </c>
+      <c r="P214">
+        <v>0.44600000000000001</v>
+      </c>
+      <c r="Q214">
+        <v>1279.92</v>
+      </c>
+      <c r="R214">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="S214">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="T214">
+        <v>1</v>
+      </c>
+      <c r="U214">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="V214">
+        <v>0.57699999999999996</v>
+      </c>
+    </row>
+    <row r="215" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A215" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B215" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C215" t="s">
+        <v>491</v>
+      </c>
+      <c r="D215" t="s">
+        <v>409</v>
+      </c>
+      <c r="E215" s="2" t="s">
+        <v>177</v>
+      </c>
+      <c r="F215" t="s">
+        <v>69</v>
+      </c>
+      <c r="G215" s="2"/>
+      <c r="H215" s="2"/>
+      <c r="I215" s="2"/>
+      <c r="J215" s="2"/>
+      <c r="K215" s="30"/>
+      <c r="L215" s="2"/>
+      <c r="M215" s="2"/>
+      <c r="N215" s="2"/>
+      <c r="O215">
+        <v>0.14799999999999999</v>
+      </c>
+      <c r="P215">
+        <v>0.37</v>
+      </c>
+      <c r="Q215" t="s">
+        <v>492</v>
+      </c>
+      <c r="R215">
+        <v>0.496</v>
+      </c>
+      <c r="S215">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="T215">
+        <v>1</v>
+      </c>
+      <c r="U215">
+        <v>0.63</v>
+      </c>
+      <c r="V215">
+        <v>0.4</v>
+      </c>
+    </row>
+    <row r="216" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A216" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B216" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C216" t="s">
+        <v>493</v>
+      </c>
+      <c r="D216" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="E216" s="2" t="s">
+        <v>494</v>
+      </c>
+      <c r="F216" t="s">
+        <v>495</v>
+      </c>
+      <c r="G216" s="23"/>
+      <c r="H216" s="2"/>
+      <c r="I216" s="2"/>
+      <c r="J216" s="2"/>
+      <c r="K216" s="2"/>
+      <c r="L216" s="2"/>
+      <c r="M216" s="2"/>
+      <c r="N216" s="2"/>
+      <c r="O216" s="2">
+        <v>0.51200000000000001</v>
+      </c>
+      <c r="P216" s="2">
+        <v>0.40400000000000003</v>
+      </c>
+      <c r="Q216" s="2" t="s">
+        <v>496</v>
+      </c>
+      <c r="R216" s="2">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="S216" s="2">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="T216" s="2">
+        <v>0.97</v>
+      </c>
+      <c r="U216" s="4">
+        <v>0.77800000000000002</v>
+      </c>
+      <c r="V216" s="6">
+        <v>0.48</v>
+      </c>
+    </row>
+    <row r="217" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A217" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B217" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C217" t="s">
+        <v>497</v>
+      </c>
+      <c r="D217" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E217" s="2" t="s">
+        <v>498</v>
+      </c>
+      <c r="F217" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G217" s="23"/>
+      <c r="H217" s="2"/>
+      <c r="I217" s="2"/>
+      <c r="J217" s="2"/>
+      <c r="K217" s="2"/>
+      <c r="L217" s="2"/>
+      <c r="M217" s="2"/>
+      <c r="N217" s="2"/>
+      <c r="O217">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="P217">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="Q217">
+        <v>0.71</v>
+      </c>
+      <c r="R217">
+        <v>0.90600000000000003</v>
+      </c>
+      <c r="S217">
+        <v>1</v>
+      </c>
+      <c r="T217">
+        <v>0.33300000000000002</v>
+      </c>
+      <c r="U217">
+        <v>1</v>
+      </c>
+      <c r="V217">
+        <v>0.54700000000000004</v>
+      </c>
+    </row>
+    <row r="218" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A218" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B218" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C218" t="s">
+        <v>499</v>
+      </c>
+      <c r="D218" t="s">
+        <v>409</v>
+      </c>
+      <c r="E218" s="2" t="s">
+        <v>500</v>
+      </c>
+      <c r="F218" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G218" s="23"/>
+      <c r="H218" s="2"/>
+      <c r="I218" s="2"/>
+      <c r="J218" s="2"/>
+      <c r="K218" s="2"/>
+      <c r="L218" s="2"/>
+      <c r="M218" s="2"/>
+      <c r="N218" s="2"/>
+      <c r="O218">
+        <v>0.78800000000000003</v>
+      </c>
+      <c r="P218">
+        <v>0.624</v>
+      </c>
+      <c r="Q218" t="s">
+        <v>501</v>
+      </c>
+      <c r="R218">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="S218">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T218">
+        <v>1</v>
+      </c>
+      <c r="U218">
+        <v>0.81499999999999995</v>
+      </c>
+      <c r="V218">
+        <v>0.61799999999999999</v>
+      </c>
+    </row>
+    <row r="219" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A219" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B219" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C219" t="s">
+        <v>502</v>
+      </c>
+      <c r="D219" s="2" t="s">
+        <v>503</v>
+      </c>
+      <c r="E219" s="2" t="s">
+        <v>504</v>
+      </c>
+      <c r="F219" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="G219" s="2"/>
+      <c r="H219" s="2"/>
+      <c r="I219" s="2"/>
+      <c r="J219" s="2"/>
+      <c r="K219" s="2"/>
+      <c r="L219" s="2"/>
+      <c r="M219" s="2"/>
+      <c r="N219" s="30"/>
+      <c r="O219">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P219">
+        <v>0.624</v>
+      </c>
+      <c r="Q219" t="s">
+        <v>505</v>
+      </c>
+      <c r="R219">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="S219">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="T219">
+        <v>1</v>
+      </c>
+      <c r="U219">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="V219">
+        <v>0.60399999999999998</v>
+      </c>
+    </row>
+    <row r="220" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A220" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B220" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C220" s="12" t="s">
+        <v>506</v>
+      </c>
+      <c r="D220" t="s">
+        <v>468</v>
+      </c>
+      <c r="E220" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F220" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G220" s="2"/>
+      <c r="H220" s="2"/>
+      <c r="I220" s="2"/>
+      <c r="J220" s="2"/>
+      <c r="K220" s="30"/>
+      <c r="L220" s="2"/>
+      <c r="M220" s="2"/>
+      <c r="N220" s="2"/>
+      <c r="O220">
+        <v>0.63200000000000001</v>
+      </c>
+      <c r="P220">
+        <v>0.48799999999999999</v>
+      </c>
+      <c r="Q220" t="s">
+        <v>507</v>
+      </c>
+      <c r="R220">
+        <v>0.59099999999999997</v>
+      </c>
+      <c r="S220">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="T220" s="2">
+        <v>1</v>
+      </c>
+      <c r="U220">
+        <v>0.84599999999999997</v>
+      </c>
+      <c r="V220">
+        <v>0.56299999999999994</v>
+      </c>
+    </row>
+    <row r="221" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A221" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B221" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C221" t="s">
+        <v>508</v>
+      </c>
+      <c r="D221" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E221" s="2" t="s">
+        <v>119</v>
+      </c>
+      <c r="F221" t="s">
+        <v>88</v>
+      </c>
+      <c r="G221" s="2"/>
+      <c r="H221" s="2"/>
+      <c r="I221" s="2"/>
+      <c r="J221" s="2"/>
+      <c r="K221" s="2"/>
+      <c r="L221" s="2"/>
+      <c r="M221" s="2"/>
+      <c r="N221" s="30"/>
+      <c r="O221">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="P221">
+        <v>0.53</v>
+      </c>
+      <c r="Q221" t="s">
+        <v>509</v>
+      </c>
+      <c r="R221">
+        <v>0.624</v>
+      </c>
+      <c r="S221">
+        <v>0.58099999999999996</v>
+      </c>
+      <c r="T221">
+        <v>1</v>
+      </c>
+      <c r="U221">
+        <v>0.90100000000000002</v>
+      </c>
+      <c r="V221">
+        <v>0.55900000000000005</v>
+      </c>
+    </row>
+    <row r="222" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A222" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B222" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C222" t="s">
+        <v>510</v>
+      </c>
+      <c r="D222" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E222" s="2" t="s">
+        <v>486</v>
+      </c>
+      <c r="F222" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G222" s="2"/>
+      <c r="H222" s="2"/>
+      <c r="I222" s="2"/>
+      <c r="J222" s="2"/>
+      <c r="K222" s="2"/>
+      <c r="L222" s="2"/>
+      <c r="M222" s="2"/>
+      <c r="N222" s="30"/>
+      <c r="O222">
+        <v>0.78900000000000003</v>
+      </c>
+      <c r="P222">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="Q222" t="s">
+        <v>511</v>
+      </c>
+      <c r="R222">
+        <v>0.68100000000000005</v>
+      </c>
+      <c r="S222">
+        <v>0.55600000000000005</v>
+      </c>
+      <c r="T222">
+        <v>1</v>
+      </c>
+      <c r="U222">
+        <v>0.80200000000000005</v>
+      </c>
+      <c r="V222">
+        <v>0.61599999999999999</v>
+      </c>
+    </row>
+    <row r="223" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A223" s="13">
+        <v>46321</v>
+      </c>
+      <c r="B223" s="10" t="s">
+        <v>367</v>
+      </c>
+      <c r="C223" t="s">
+        <v>512</v>
+      </c>
+      <c r="D223" t="s">
+        <v>513</v>
+      </c>
+      <c r="E223" t="s">
+        <v>514</v>
+      </c>
+      <c r="F223" s="2" t="s">
+        <v>515</v>
+      </c>
+      <c r="G223" s="23"/>
+      <c r="H223" s="2"/>
+      <c r="I223" s="2"/>
+      <c r="J223" s="2"/>
+      <c r="K223" s="2"/>
+      <c r="L223" s="2"/>
+      <c r="M223" s="2"/>
+      <c r="N223" s="2"/>
+      <c r="O223">
+        <v>0.22900000000000001</v>
+      </c>
+      <c r="P223">
+        <v>0.34300000000000003</v>
+      </c>
+      <c r="Q223" t="s">
+        <v>516</v>
+      </c>
+      <c r="R223">
+        <v>0.45500000000000002</v>
+      </c>
+      <c r="S223">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="T223" s="2">
+        <v>1</v>
+      </c>
+      <c r="U223" s="4">
+        <v>0.52</v>
+      </c>
+      <c r="V223" s="6">
+        <v>0.36899999999999999</v>
+      </c>
+    </row>
+    <row r="224" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A224" s="33">
+        <v>46321</v>
+      </c>
+      <c r="B224" t="s">
+        <v>367</v>
+      </c>
+      <c r="C224" t="s">
+        <v>517</v>
+      </c>
+      <c r="D224" t="s">
+        <v>518</v>
+      </c>
+      <c r="E224" t="s">
+        <v>519</v>
+      </c>
+      <c r="F224" t="s">
+        <v>520</v>
+      </c>
+      <c r="G224" s="23"/>
+      <c r="O224">
+        <v>0.217</v>
+      </c>
+      <c r="P224">
+        <v>0.23300000000000001</v>
+      </c>
+      <c r="Q224" t="s">
+        <v>521</v>
+      </c>
+      <c r="R224">
+        <v>0.33800000000000002</v>
+      </c>
+      <c r="S224">
+        <v>0.69</v>
+      </c>
+      <c r="T224">
+        <v>1</v>
+      </c>
+      <c r="U224">
+        <v>0.32500000000000001</v>
+      </c>
+      <c r="V224">
+        <v>0.30199999999999999</v>
+      </c>
+    </row>
+    <row r="225" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A225" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B225" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C225" t="s">
+        <v>522</v>
+      </c>
+      <c r="D225" t="s">
+        <v>409</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>523</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G225" s="24"/>
+      <c r="H225" s="24"/>
+      <c r="I225" s="24"/>
+      <c r="J225" s="13"/>
+      <c r="K225" s="13"/>
+      <c r="L225" s="13"/>
+      <c r="M225" s="24"/>
+      <c r="N225" s="23"/>
+      <c r="O225">
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="P225">
+        <v>0.623</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>524</v>
+      </c>
+      <c r="R225">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="S225">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="T225">
+        <v>1</v>
+      </c>
+      <c r="U225">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="V225">
+        <v>0.59599999999999997</v>
+      </c>
+    </row>
+    <row r="226" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A226" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="D226" t="s">
+        <v>257</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>526</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G226" s="13"/>
+      <c r="H226" s="24"/>
+      <c r="I226" s="24"/>
+      <c r="J226" s="13"/>
+      <c r="K226" s="23"/>
+      <c r="L226" s="13"/>
+      <c r="M226" s="24"/>
+      <c r="N226" s="13"/>
+      <c r="O226">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="P226">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>527</v>
+      </c>
+      <c r="R226">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="S226">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="T226">
+        <v>1</v>
+      </c>
+      <c r="U226">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="V226">
+        <v>0.61299999999999999</v>
+      </c>
+    </row>
+    <row r="227" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A227" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B227" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C227" t="s">
+        <v>528</v>
+      </c>
+      <c r="D227" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>529</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G227" s="13"/>
+      <c r="H227" s="24"/>
+      <c r="I227" s="24"/>
+      <c r="J227" s="13"/>
+      <c r="K227" s="23"/>
+      <c r="L227" s="13"/>
+      <c r="M227" s="24"/>
+      <c r="N227" s="13"/>
+      <c r="O227">
+        <v>0.83</v>
+      </c>
+      <c r="P227">
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>530</v>
+      </c>
+      <c r="R227">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="S227">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="T227">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U227">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="V227">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="228" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A228" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>531</v>
+      </c>
+      <c r="D228" t="s">
+        <v>257</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G228" s="13"/>
+      <c r="H228" s="24"/>
+      <c r="I228" s="24"/>
+      <c r="J228" s="13"/>
+      <c r="K228" s="23"/>
+      <c r="L228" s="13"/>
+      <c r="M228" s="24"/>
+      <c r="N228" s="13"/>
+      <c r="O228">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="P228">
+        <v>0.497</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>532</v>
+      </c>
+      <c r="R228">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="S228">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="T228">
+        <v>1</v>
+      </c>
+      <c r="U228">
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="V228">
+        <v>0.60499999999999998</v>
+      </c>
+    </row>
+    <row r="229" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A229" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B229" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>533</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>534</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G229" s="13"/>
+      <c r="H229" s="24"/>
+      <c r="I229" s="24"/>
+      <c r="J229" s="13"/>
+      <c r="K229" s="23"/>
+      <c r="L229" s="13"/>
+      <c r="M229" s="24"/>
+      <c r="N229" s="13"/>
+      <c r="O229">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="P229">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>535</v>
+      </c>
+      <c r="R229">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="S229">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="T229">
+        <v>1</v>
+      </c>
+      <c r="U229">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="V229">
+        <v>0.61899999999999999</v>
+      </c>
+    </row>
+    <row r="230" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A230" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>536</v>
+      </c>
+      <c r="D230" t="s">
+        <v>257</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F230" t="s">
+        <v>537</v>
+      </c>
+      <c r="G230" s="13"/>
+      <c r="H230" s="23"/>
+      <c r="I230" s="24"/>
+      <c r="J230" s="13"/>
+      <c r="K230" s="13"/>
+      <c r="L230" s="13"/>
+      <c r="M230" s="24"/>
+      <c r="N230" s="13"/>
+      <c r="O230">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="P230">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>538</v>
+      </c>
+      <c r="R230">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="S230">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="T230">
+        <v>0.82</v>
+      </c>
+      <c r="U230">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="V230">
+        <v>0.61699999999999999</v>
+      </c>
+    </row>
+    <row r="231" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A231" s="13"/>
+      <c r="B231" s="10"/>
+      <c r="C231" s="12"/>
+      <c r="D231" s="2"/>
+      <c r="E231" s="2"/>
+      <c r="F231" s="2"/>
+      <c r="G231" s="13"/>
+      <c r="H231" s="24"/>
+      <c r="I231" s="24"/>
+      <c r="J231" s="13"/>
+      <c r="K231" s="13"/>
+      <c r="L231" s="13"/>
+      <c r="M231" s="24"/>
+      <c r="N231" s="13"/>
+      <c r="O231" s="10"/>
+      <c r="P231" s="10"/>
+      <c r="Q231" s="10"/>
+      <c r="R231" s="10"/>
+      <c r="S231" s="10"/>
+      <c r="T231" s="10"/>
+      <c r="U231" s="10"/>
+      <c r="V231" s="6"/>
+    </row>
+    <row r="232" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A232" s="13"/>
+      <c r="B232" s="10"/>
+      <c r="C232" s="12"/>
+      <c r="D232" s="2"/>
+      <c r="E232" s="2"/>
+      <c r="F232" s="2"/>
+      <c r="G232" s="13"/>
+      <c r="H232" s="24"/>
+      <c r="I232" s="24"/>
+      <c r="J232" s="13"/>
+      <c r="K232" s="13"/>
+      <c r="L232" s="13"/>
+      <c r="M232" s="24"/>
+      <c r="N232" s="13"/>
+      <c r="O232" s="10"/>
+      <c r="P232" s="10"/>
+      <c r="Q232" s="10"/>
+      <c r="R232" s="10"/>
+      <c r="S232" s="10"/>
+      <c r="T232" s="10"/>
+      <c r="U232" s="10"/>
+      <c r="V232" s="6"/>
+    </row>
+    <row r="233" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A233" s="13"/>
+      <c r="B233" s="10"/>
+      <c r="C233" s="12"/>
+      <c r="D233" s="2"/>
+      <c r="E233" s="2"/>
+      <c r="F233" s="2"/>
+      <c r="G233" s="13"/>
+      <c r="H233" s="24"/>
+      <c r="I233" s="24"/>
+      <c r="J233" s="13"/>
+      <c r="K233" s="13"/>
+      <c r="L233" s="13"/>
+      <c r="M233" s="24"/>
+      <c r="N233" s="13"/>
+      <c r="O233" s="10"/>
+      <c r="P233" s="10"/>
+      <c r="Q233" s="10"/>
+      <c r="R233" s="10"/>
+      <c r="S233" s="10"/>
+      <c r="T233" s="10"/>
+      <c r="U233" s="10"/>
+      <c r="V233" s="6"/>
+    </row>
+    <row r="234" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A234" s="13"/>
+      <c r="B234" s="10"/>
+      <c r="C234" s="12"/>
+      <c r="D234" s="2"/>
+      <c r="E234" s="2"/>
+      <c r="F234" s="2"/>
+      <c r="G234" s="13"/>
+      <c r="H234" s="24"/>
+      <c r="I234" s="24"/>
+      <c r="J234" s="13"/>
+      <c r="K234" s="13"/>
+      <c r="L234" s="13"/>
+      <c r="M234" s="24"/>
+      <c r="N234" s="13"/>
+      <c r="O234" s="10"/>
+      <c r="P234" s="10"/>
+      <c r="Q234" s="10"/>
+      <c r="R234" s="10"/>
+      <c r="S234" s="10"/>
+      <c r="T234" s="10"/>
+      <c r="U234" s="10"/>
+      <c r="V234" s="6"/>
+    </row>
+    <row r="235" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A235" s="13"/>
+      <c r="B235" s="10"/>
+      <c r="C235" s="12"/>
+      <c r="D235" s="2"/>
+      <c r="E235" s="2"/>
+      <c r="F235" s="2"/>
+      <c r="G235" s="13"/>
+      <c r="H235" s="24"/>
+      <c r="I235" s="24"/>
+      <c r="J235" s="13"/>
+      <c r="K235" s="13"/>
+      <c r="L235" s="13"/>
+      <c r="M235" s="24"/>
+      <c r="N235" s="13"/>
+      <c r="O235" s="10"/>
+      <c r="P235" s="10"/>
+      <c r="Q235" s="10"/>
+      <c r="R235" s="10"/>
+      <c r="S235" s="10"/>
+      <c r="T235" s="10"/>
+      <c r="U235" s="10"/>
+      <c r="V235" s="6"/>
+    </row>
+    <row r="236" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A236" s="13"/>
+      <c r="B236" s="10"/>
+      <c r="C236" s="12"/>
+      <c r="D236" s="2"/>
+      <c r="E236" s="2"/>
+      <c r="F236" s="2"/>
+      <c r="G236" s="13"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="13"/>
+      <c r="K236" s="13"/>
+      <c r="L236" s="13"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="13"/>
+      <c r="O236" s="10"/>
+      <c r="P236" s="10"/>
+      <c r="Q236" s="10"/>
+      <c r="R236" s="10"/>
+      <c r="S236" s="10"/>
+      <c r="T236" s="10"/>
+      <c r="U236" s="10"/>
+      <c r="V236" s="6"/>
+    </row>
+    <row r="237" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A237" s="13"/>
+      <c r="B237" s="10"/>
+      <c r="C237" s="12"/>
+      <c r="D237" s="2"/>
+      <c r="E237" s="2"/>
+      <c r="F237" s="2"/>
+      <c r="G237" s="13"/>
+      <c r="H237" s="24"/>
+      <c r="I237" s="24"/>
+      <c r="J237" s="13"/>
+      <c r="K237" s="13"/>
+      <c r="L237" s="13"/>
+      <c r="M237" s="24"/>
+      <c r="N237" s="13"/>
+      <c r="O237" s="10"/>
+      <c r="P237" s="10"/>
+      <c r="Q237" s="10"/>
+      <c r="R237" s="10"/>
+      <c r="S237" s="10"/>
+      <c r="T237" s="10"/>
+      <c r="U237" s="10"/>
+      <c r="V237" s="6"/>
+    </row>
+    <row r="238" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A238" s="13"/>
+      <c r="B238" s="10"/>
+      <c r="C238" s="12"/>
+      <c r="D238" s="2"/>
+      <c r="E238" s="2"/>
+      <c r="F238" s="2"/>
+      <c r="G238" s="13"/>
+      <c r="H238" s="24"/>
+      <c r="I238" s="24"/>
+      <c r="J238" s="13"/>
+      <c r="K238" s="13"/>
+      <c r="L238" s="13"/>
+      <c r="M238" s="24"/>
+      <c r="N238" s="13"/>
+      <c r="O238" s="10"/>
+      <c r="P238" s="10"/>
+      <c r="Q238" s="10"/>
+      <c r="R238" s="10"/>
+      <c r="S238" s="10"/>
+      <c r="T238" s="10"/>
+      <c r="U238" s="10"/>
+      <c r="V238" s="6"/>
+    </row>
+    <row r="239" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A239" s="13"/>
+      <c r="B239" s="10"/>
+      <c r="C239" s="12"/>
+      <c r="D239" s="2"/>
+      <c r="E239" s="2"/>
+      <c r="F239" s="2"/>
+      <c r="G239" s="13"/>
+      <c r="H239" s="24"/>
+      <c r="I239" s="24"/>
+      <c r="J239" s="13"/>
+      <c r="K239" s="13"/>
+      <c r="L239" s="13"/>
+      <c r="M239" s="24"/>
+      <c r="N239" s="13"/>
+      <c r="O239" s="10"/>
+      <c r="P239" s="10"/>
+      <c r="Q239" s="10"/>
+      <c r="R239" s="10"/>
+      <c r="S239" s="10"/>
+      <c r="T239" s="10"/>
+      <c r="U239" s="10"/>
+      <c r="V239" s="6"/>
+    </row>
+    <row r="240" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A240" s="13"/>
+      <c r="B240" s="10"/>
+      <c r="C240" s="12"/>
+      <c r="D240" s="2"/>
+      <c r="E240" s="2"/>
+      <c r="F240" s="2"/>
+      <c r="G240" s="13"/>
+      <c r="H240" s="24"/>
+      <c r="I240" s="24"/>
+      <c r="J240" s="13"/>
+      <c r="K240" s="13"/>
+      <c r="L240" s="13"/>
+      <c r="M240" s="24"/>
+      <c r="N240" s="13"/>
+      <c r="O240" s="10"/>
+      <c r="P240" s="10"/>
+      <c r="Q240" s="10"/>
+      <c r="R240" s="10"/>
+      <c r="S240" s="10"/>
+      <c r="T240" s="10"/>
+      <c r="U240" s="10"/>
+      <c r="V240" s="6"/>
     </row>
   </sheetData>
-  <autoFilter ref="A4:V177" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}"/>
   <mergeCells count="7">
     <mergeCell ref="A2:A4"/>
     <mergeCell ref="B2:B4"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4064" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6EEE79EC-44BA-4F66-961A-363F0D4E6545}"/>
+  <xr:revisionPtr revIDLastSave="4220" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E1C4631-164C-4A43-8BD4-03151C405F81}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1365" uniqueCount="539">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="577">
   <si>
     <t>Date</t>
   </si>
@@ -1508,6 +1508,9 @@
     <t>Medllama-1B-Instruct-v3-GGUF:Q4_K_M</t>
   </si>
   <si>
+    <t>1 B</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 807 MB</t>
   </si>
   <si>
@@ -1659,13 +1662,136 @@
   </si>
   <si>
     <t>1460.91 ms</t>
+  </si>
+  <si>
+    <t>5741.76 ms</t>
+  </si>
+  <si>
+    <t>xwinlm:7b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7b </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3.8 GB</t>
+  </si>
+  <si>
+    <r>
+      <t>Xwin-LM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> team</t>
+    </r>
+  </si>
+  <si>
+    <t>4550.93 ms</t>
+  </si>
+  <si>
+    <t>starling-lm:7b</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.1 GB</t>
+  </si>
+  <si>
+    <t>nexusflow</t>
+  </si>
+  <si>
+    <t>3069.47 ms</t>
+  </si>
+  <si>
+    <t>falcon:7b-instruct</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.2 GB</t>
+  </si>
+  <si>
+    <t>Technology Innovation Institute</t>
+  </si>
+  <si>
+    <t>512.88 ms</t>
+  </si>
+  <si>
+    <t>qwen2.5:1.5b</t>
+  </si>
+  <si>
+    <t>Alibaba Cloud (Qwen team)</t>
+  </si>
+  <si>
+    <t>1587.89 ms</t>
+  </si>
+  <si>
+    <t>qwen2.5:3b</t>
+  </si>
+  <si>
+    <t>3b</t>
+  </si>
+  <si>
+    <t>1.9GB</t>
+  </si>
+  <si>
+    <t>1360.21 ms</t>
+  </si>
+  <si>
+    <t>qwen3:1.7b</t>
+  </si>
+  <si>
+    <t>1.4GB</t>
+  </si>
+  <si>
+    <t>6113.64 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> gemma2:2b</t>
+  </si>
+  <si>
+    <t>2.2b</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.6 GB</t>
+  </si>
+  <si>
+    <t>2703.15 ms</t>
+  </si>
+  <si>
+    <t>sam860/olmo2:1b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allem Institute </t>
+  </si>
+  <si>
+    <t>1341.61 ms</t>
+  </si>
+  <si>
+    <t>opencoder:1.5b-instruct-q4_K_M</t>
+  </si>
+  <si>
+    <t>Infly</t>
+  </si>
+  <si>
+    <t>1515.96 ms</t>
+  </si>
+  <si>
+    <t>qwen2.5-coder:1.5b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">986 MB </t>
+  </si>
+  <si>
+    <t>497.10 ms</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1704,6 +1830,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Google Sans"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -2147,7 +2279,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2187,6 +2319,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2572,7 +2705,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V240"/>
+  <dimension ref="A1:V254"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -2587,70 +2720,70 @@
   <sheetData>
     <row r="1" spans="1:22"/>
     <row r="2" spans="1:22" ht="21">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="48" t="s">
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="42" t="s">
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="44"/>
     </row>
     <row r="3" spans="1:22" ht="18.75">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="40" t="s">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40" t="s">
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="42"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="11" t="s">
         <v>7</v>
       </c>
@@ -13531,9 +13664,11 @@
       <c r="C213" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="D213" s="2"/>
+      <c r="D213" s="2" t="s">
+        <v>488</v>
+      </c>
       <c r="E213" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>69</v>
@@ -13579,13 +13714,13 @@
         <v>393</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D214" t="s">
         <v>409</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F214" t="s">
         <v>69</v>
@@ -13631,7 +13766,7 @@
         <v>398</v>
       </c>
       <c r="C215" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D215" t="s">
         <v>409</v>
@@ -13657,7 +13792,7 @@
         <v>0.37</v>
       </c>
       <c r="Q215" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R215">
         <v>0.496</v>
@@ -13683,16 +13818,16 @@
         <v>367</v>
       </c>
       <c r="C216" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F216" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G216" s="23"/>
       <c r="H216" s="2"/>
@@ -13709,7 +13844,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="Q216" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R216" s="2">
         <v>0.52300000000000002</v>
@@ -13735,13 +13870,13 @@
         <v>393</v>
       </c>
       <c r="C217" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>477</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>69</v>
@@ -13787,13 +13922,13 @@
         <v>398</v>
       </c>
       <c r="C218" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D218" t="s">
         <v>409</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>69</v>
@@ -13813,7 +13948,7 @@
         <v>0.624</v>
       </c>
       <c r="Q218" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="R218">
         <v>0.69899999999999995</v>
@@ -13839,13 +13974,13 @@
         <v>393</v>
       </c>
       <c r="C219" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>88</v>
@@ -13865,7 +14000,7 @@
         <v>0.624</v>
       </c>
       <c r="Q219" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="R219">
         <v>0.69899999999999995</v>
@@ -13891,7 +14026,7 @@
         <v>398</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D220" t="s">
         <v>468</v>
@@ -13917,7 +14052,7 @@
         <v>0.48799999999999999</v>
       </c>
       <c r="Q220" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="R220">
         <v>0.59099999999999997</v>
@@ -13943,7 +14078,7 @@
         <v>393</v>
       </c>
       <c r="C221" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>376</v>
@@ -13969,7 +14104,7 @@
         <v>0.53</v>
       </c>
       <c r="Q221" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="R221">
         <v>0.624</v>
@@ -13995,7 +14130,7 @@
         <v>398</v>
       </c>
       <c r="C222" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>34</v>
@@ -14021,7 +14156,7 @@
         <v>0.60099999999999998</v>
       </c>
       <c r="Q222" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="R222">
         <v>0.68100000000000005</v>
@@ -14047,16 +14182,16 @@
         <v>367</v>
       </c>
       <c r="C223" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D223" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E223" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G223" s="23"/>
       <c r="H223" s="2"/>
@@ -14073,7 +14208,7 @@
         <v>0.34300000000000003</v>
       </c>
       <c r="Q223" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="R223">
         <v>0.45500000000000002</v>
@@ -14099,16 +14234,16 @@
         <v>367</v>
       </c>
       <c r="C224" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D224" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E224" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F224" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G224" s="23"/>
       <c r="O224">
@@ -14118,7 +14253,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="Q224" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R224">
         <v>0.33800000000000002</v>
@@ -14144,13 +14279,13 @@
         <v>393</v>
       </c>
       <c r="C225" t="s">
-        <v>522</v>
+        <v>523</v>
       </c>
       <c r="D225" t="s">
         <v>409</v>
       </c>
       <c r="E225" s="2" t="s">
-        <v>523</v>
+        <v>524</v>
       </c>
       <c r="F225" s="2" t="s">
         <v>69</v>
@@ -14170,7 +14305,7 @@
         <v>0.623</v>
       </c>
       <c r="Q225" t="s">
-        <v>524</v>
+        <v>525</v>
       </c>
       <c r="R225">
         <v>0.69899999999999995</v>
@@ -14196,13 +14331,13 @@
         <v>398</v>
       </c>
       <c r="C226" s="12" t="s">
-        <v>525</v>
+        <v>526</v>
       </c>
       <c r="D226" t="s">
         <v>257</v>
       </c>
       <c r="E226" s="2" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="F226" s="2" t="s">
         <v>69</v>
@@ -14222,7 +14357,7 @@
         <v>0.49099999999999999</v>
       </c>
       <c r="Q226" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="R226">
         <v>0.59299999999999997</v>
@@ -14248,13 +14383,13 @@
         <v>393</v>
       </c>
       <c r="C227" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="D227" s="36" t="s">
         <v>115</v>
       </c>
       <c r="E227" s="2" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="F227" s="2" t="s">
         <v>69</v>
@@ -14274,7 +14409,7 @@
         <v>0.45400000000000001</v>
       </c>
       <c r="Q227" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="R227">
         <v>0.56299999999999994</v>
@@ -14300,7 +14435,7 @@
         <v>398</v>
       </c>
       <c r="C228" s="12" t="s">
-        <v>531</v>
+        <v>532</v>
       </c>
       <c r="D228" t="s">
         <v>257</v>
@@ -14326,7 +14461,7 @@
         <v>0.497</v>
       </c>
       <c r="Q228" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="R228">
         <v>0.59799999999999998</v>
@@ -14352,13 +14487,13 @@
         <v>393</v>
       </c>
       <c r="C229" s="12" t="s">
-        <v>533</v>
+        <v>534</v>
       </c>
       <c r="D229" s="2" t="s">
         <v>244</v>
       </c>
       <c r="E229" s="2" t="s">
-        <v>534</v>
+        <v>535</v>
       </c>
       <c r="F229" s="2" t="s">
         <v>83</v>
@@ -14378,7 +14513,7 @@
         <v>0.54600000000000004</v>
       </c>
       <c r="Q229" t="s">
-        <v>535</v>
+        <v>536</v>
       </c>
       <c r="R229">
         <v>0.63700000000000001</v>
@@ -14404,7 +14539,7 @@
         <v>398</v>
       </c>
       <c r="C230" s="12" t="s">
-        <v>536</v>
+        <v>537</v>
       </c>
       <c r="D230" t="s">
         <v>257</v>
@@ -14413,7 +14548,7 @@
         <v>258</v>
       </c>
       <c r="F230" t="s">
-        <v>537</v>
+        <v>538</v>
       </c>
       <c r="G230" s="13"/>
       <c r="H230" s="23"/>
@@ -14430,7 +14565,7 @@
         <v>0.69699999999999995</v>
       </c>
       <c r="Q230" t="s">
-        <v>538</v>
+        <v>539</v>
       </c>
       <c r="R230">
         <v>0.75800000000000001</v>
@@ -14449,85 +14584,181 @@
       </c>
     </row>
     <row r="231" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A231" s="13"/>
-      <c r="B231" s="10"/>
-      <c r="C231" s="12"/>
-      <c r="D231" s="2"/>
-      <c r="E231" s="2"/>
-      <c r="F231" s="2"/>
+      <c r="A231" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B231" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G231" s="13"/>
       <c r="H231" s="24"/>
-      <c r="I231" s="24"/>
+      <c r="I231" s="23"/>
       <c r="J231" s="13"/>
       <c r="K231" s="13"/>
       <c r="L231" s="13"/>
       <c r="M231" s="24"/>
       <c r="N231" s="13"/>
-      <c r="O231" s="10"/>
-      <c r="P231" s="10"/>
-      <c r="Q231" s="10"/>
-      <c r="R231" s="10"/>
-      <c r="S231" s="10"/>
-      <c r="T231" s="10"/>
-      <c r="U231" s="10"/>
-      <c r="V231" s="6"/>
+      <c r="O231">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="P231">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>540</v>
+      </c>
+      <c r="R231">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="S231">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="T231">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="U231">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="V231">
+        <v>0.63300000000000001</v>
+      </c>
     </row>
     <row r="232" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A232" s="13"/>
-      <c r="B232" s="10"/>
-      <c r="C232" s="12"/>
-      <c r="D232" s="2"/>
-      <c r="E232" s="2"/>
-      <c r="F232" s="2"/>
+      <c r="A232" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F232" s="37" t="s">
+        <v>544</v>
+      </c>
       <c r="G232" s="13"/>
       <c r="H232" s="24"/>
       <c r="I232" s="24"/>
       <c r="J232" s="13"/>
       <c r="K232" s="13"/>
-      <c r="L232" s="13"/>
+      <c r="L232" s="23"/>
       <c r="M232" s="24"/>
       <c r="N232" s="13"/>
-      <c r="O232" s="10"/>
-      <c r="P232" s="10"/>
-      <c r="Q232" s="10"/>
-      <c r="R232" s="10"/>
-      <c r="S232" s="10"/>
-      <c r="T232" s="10"/>
-      <c r="U232" s="10"/>
-      <c r="V232" s="6"/>
+      <c r="O232">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="P232">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>545</v>
+      </c>
+      <c r="R232">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="S232">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="T232">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="U232">
+        <v>0.877</v>
+      </c>
+      <c r="V232">
+        <v>0.59199999999999997</v>
+      </c>
     </row>
     <row r="233" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A233" s="13"/>
-      <c r="B233" s="10"/>
-      <c r="C233" s="12"/>
-      <c r="D233" s="2"/>
-      <c r="E233" s="2"/>
-      <c r="F233" s="2"/>
+      <c r="A233" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>548</v>
+      </c>
       <c r="G233" s="13"/>
       <c r="H233" s="24"/>
       <c r="I233" s="24"/>
       <c r="J233" s="13"/>
       <c r="K233" s="13"/>
       <c r="L233" s="13"/>
-      <c r="M233" s="24"/>
+      <c r="M233" s="23"/>
       <c r="N233" s="13"/>
-      <c r="O233" s="10"/>
-      <c r="P233" s="10"/>
-      <c r="Q233" s="10"/>
-      <c r="R233" s="10"/>
-      <c r="S233" s="10"/>
-      <c r="T233" s="10"/>
-      <c r="U233" s="10"/>
-      <c r="V233" s="6"/>
+      <c r="O233">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="P233">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>549</v>
+      </c>
+      <c r="R233">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="S233">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="T233">
+        <v>1</v>
+      </c>
+      <c r="U233">
+        <v>0.88</v>
+      </c>
+      <c r="V233">
+        <v>0.60099999999999998</v>
+      </c>
     </row>
     <row r="234" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A234" s="13"/>
-      <c r="B234" s="10"/>
-      <c r="C234" s="12"/>
-      <c r="D234" s="2"/>
-      <c r="E234" s="2"/>
-      <c r="F234" s="2"/>
-      <c r="G234" s="13"/>
+      <c r="A234" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="F234" t="s">
+        <v>552</v>
+      </c>
+      <c r="G234" s="23"/>
       <c r="H234" s="24"/>
       <c r="I234" s="24"/>
       <c r="J234" s="13"/>
@@ -14535,70 +14766,154 @@
       <c r="L234" s="13"/>
       <c r="M234" s="24"/>
       <c r="N234" s="13"/>
-      <c r="O234" s="10"/>
-      <c r="P234" s="10"/>
-      <c r="Q234" s="10"/>
-      <c r="R234" s="10"/>
-      <c r="S234" s="10"/>
-      <c r="T234" s="10"/>
-      <c r="U234" s="10"/>
-      <c r="V234" s="6"/>
+      <c r="O234">
+        <v>0.3</v>
+      </c>
+      <c r="P234">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>553</v>
+      </c>
+      <c r="R234">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="S234">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="T234">
+        <v>1</v>
+      </c>
+      <c r="U234">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="V234">
+        <v>0.46</v>
+      </c>
     </row>
     <row r="235" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A235" s="13"/>
-      <c r="B235" s="10"/>
-      <c r="C235" s="12"/>
-      <c r="D235" s="2"/>
-      <c r="E235" s="2"/>
-      <c r="F235" s="2"/>
+      <c r="A235" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B235" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E235" t="s">
+        <v>197</v>
+      </c>
+      <c r="F235" t="s">
+        <v>555</v>
+      </c>
       <c r="G235" s="13"/>
       <c r="H235" s="24"/>
-      <c r="I235" s="24"/>
+      <c r="I235" s="23"/>
       <c r="J235" s="13"/>
       <c r="K235" s="13"/>
       <c r="L235" s="13"/>
       <c r="M235" s="24"/>
       <c r="N235" s="13"/>
-      <c r="O235" s="10"/>
-      <c r="P235" s="10"/>
-      <c r="Q235" s="10"/>
-      <c r="R235" s="10"/>
-      <c r="S235" s="10"/>
-      <c r="T235" s="10"/>
-      <c r="U235" s="10"/>
-      <c r="V235" s="6"/>
+      <c r="O235">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="P235">
+        <v>0.65</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>556</v>
+      </c>
+      <c r="R235">
+        <v>0.72</v>
+      </c>
+      <c r="S235">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="T235">
+        <v>0.878</v>
+      </c>
+      <c r="U235">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="V235">
+        <v>0.63100000000000001</v>
+      </c>
     </row>
     <row r="236" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A236" s="13"/>
-      <c r="B236" s="10"/>
-      <c r="C236" s="12"/>
-      <c r="D236" s="2"/>
-      <c r="E236" s="2"/>
-      <c r="F236" s="2"/>
+      <c r="A236" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E236" t="s">
+        <v>559</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>555</v>
+      </c>
       <c r="G236" s="13"/>
       <c r="H236" s="24"/>
       <c r="I236" s="24"/>
       <c r="J236" s="13"/>
-      <c r="K236" s="13"/>
+      <c r="K236" s="23"/>
       <c r="L236" s="13"/>
       <c r="M236" s="24"/>
       <c r="N236" s="13"/>
-      <c r="O236" s="10"/>
-      <c r="P236" s="10"/>
-      <c r="Q236" s="10"/>
-      <c r="R236" s="10"/>
-      <c r="S236" s="10"/>
-      <c r="T236" s="10"/>
-      <c r="U236" s="10"/>
-      <c r="V236" s="6"/>
+      <c r="O236">
+        <v>0.78</v>
+      </c>
+      <c r="P236">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>560</v>
+      </c>
+      <c r="R236">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="S236">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="T236">
+        <v>1</v>
+      </c>
+      <c r="U236">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="V236">
+        <v>0.59299999999999997</v>
+      </c>
     </row>
     <row r="237" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A237" s="13"/>
-      <c r="B237" s="10"/>
-      <c r="C237" s="12"/>
-      <c r="D237" s="2"/>
-      <c r="E237" s="2"/>
-      <c r="F237" s="2"/>
+      <c r="A237" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>31</v>
+      </c>
       <c r="G237" s="13"/>
       <c r="H237" s="24"/>
       <c r="I237" s="24"/>
@@ -14606,87 +14921,550 @@
       <c r="K237" s="13"/>
       <c r="L237" s="13"/>
       <c r="M237" s="24"/>
-      <c r="N237" s="13"/>
-      <c r="O237" s="10"/>
-      <c r="P237" s="10"/>
-      <c r="Q237" s="10"/>
-      <c r="R237" s="10"/>
-      <c r="S237" s="10"/>
-      <c r="T237" s="10"/>
-      <c r="U237" s="10"/>
-      <c r="V237" s="6"/>
+      <c r="N237" s="23"/>
+      <c r="O237">
+        <v>0.78</v>
+      </c>
+      <c r="P237">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>563</v>
+      </c>
+      <c r="R237">
+        <v>0.67</v>
+      </c>
+      <c r="S237">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="T237">
+        <v>1</v>
+      </c>
+      <c r="U237">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="V237">
+        <v>0.60199999999999998</v>
+      </c>
     </row>
     <row r="238" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A238" s="13"/>
-      <c r="B238" s="10"/>
-      <c r="C238" s="12"/>
-      <c r="D238" s="2"/>
-      <c r="E238" s="2"/>
-      <c r="F238" s="2"/>
+      <c r="A238" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="G238" s="13"/>
       <c r="H238" s="24"/>
       <c r="I238" s="24"/>
-      <c r="J238" s="13"/>
+      <c r="J238" s="23"/>
       <c r="K238" s="13"/>
       <c r="L238" s="13"/>
       <c r="M238" s="24"/>
       <c r="N238" s="13"/>
-      <c r="O238" s="10"/>
-      <c r="P238" s="10"/>
-      <c r="Q238" s="10"/>
-      <c r="R238" s="10"/>
-      <c r="S238" s="10"/>
-      <c r="T238" s="10"/>
-      <c r="U238" s="10"/>
-      <c r="V238" s="6"/>
+      <c r="O238">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="P238">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>567</v>
+      </c>
+      <c r="R238">
+        <v>0.73</v>
+      </c>
+      <c r="S238">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="T238">
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="U238">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="V238">
+        <v>0.621</v>
+      </c>
     </row>
     <row r="239" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A239" s="13"/>
-      <c r="B239" s="10"/>
-      <c r="C239" s="12"/>
-      <c r="D239" s="2"/>
-      <c r="E239" s="2"/>
-      <c r="F239" s="2"/>
+      <c r="A239" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B239" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>569</v>
+      </c>
       <c r="G239" s="13"/>
       <c r="H239" s="24"/>
-      <c r="I239" s="24"/>
+      <c r="I239" s="13"/>
       <c r="J239" s="13"/>
       <c r="K239" s="13"/>
-      <c r="L239" s="13"/>
+      <c r="L239" s="23"/>
       <c r="M239" s="24"/>
       <c r="N239" s="13"/>
-      <c r="O239" s="10"/>
-      <c r="P239" s="10"/>
-      <c r="Q239" s="10"/>
-      <c r="R239" s="10"/>
-      <c r="S239" s="10"/>
-      <c r="T239" s="10"/>
-      <c r="U239" s="10"/>
-      <c r="V239" s="6"/>
+      <c r="O239">
+        <v>0.76</v>
+      </c>
+      <c r="P239">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>570</v>
+      </c>
+      <c r="R239">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="S239">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="T239">
+        <v>0.85</v>
+      </c>
+      <c r="U239">
+        <v>0.878</v>
+      </c>
+      <c r="V239">
+        <v>0.59499999999999997</v>
+      </c>
     </row>
     <row r="240" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A240" s="13"/>
-      <c r="B240" s="10"/>
-      <c r="C240" s="12"/>
-      <c r="D240" s="2"/>
-      <c r="E240" s="2"/>
-      <c r="F240" s="2"/>
+      <c r="A240" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C240" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>572</v>
+      </c>
       <c r="G240" s="13"/>
       <c r="H240" s="24"/>
       <c r="I240" s="24"/>
       <c r="J240" s="13"/>
       <c r="K240" s="13"/>
       <c r="L240" s="13"/>
-      <c r="M240" s="24"/>
+      <c r="M240" s="23"/>
       <c r="N240" s="13"/>
-      <c r="O240" s="10"/>
-      <c r="P240" s="10"/>
-      <c r="Q240" s="10"/>
-      <c r="R240" s="10"/>
-      <c r="S240" s="10"/>
-      <c r="T240" s="10"/>
-      <c r="U240" s="10"/>
-      <c r="V240" s="6"/>
+      <c r="O240">
+        <v>0.78</v>
+      </c>
+      <c r="P240">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>573</v>
+      </c>
+      <c r="R240">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="S240">
+        <v>0.624</v>
+      </c>
+      <c r="T240">
+        <v>1</v>
+      </c>
+      <c r="U240">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="V240">
+        <v>0.54600000000000004</v>
+      </c>
+    </row>
+    <row r="241" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A241" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B241" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C241" t="s">
+        <v>574</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F241" t="s">
+        <v>69</v>
+      </c>
+      <c r="G241" s="13"/>
+      <c r="H241" s="24"/>
+      <c r="I241" s="24"/>
+      <c r="J241" s="13"/>
+      <c r="K241" s="13"/>
+      <c r="L241" s="13"/>
+      <c r="M241" s="24"/>
+      <c r="N241" s="23"/>
+      <c r="O241">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="P241">
+        <v>0.65200000000000002</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>576</v>
+      </c>
+      <c r="R241">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="S241">
+        <v>0.54</v>
+      </c>
+      <c r="T241">
+        <v>1</v>
+      </c>
+      <c r="U241">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="V241">
+        <v>0.60599999999999998</v>
+      </c>
+    </row>
+    <row r="242" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A242" s="13"/>
+      <c r="B242" s="10"/>
+      <c r="D242" s="2"/>
+      <c r="E242" s="2"/>
+      <c r="F242" s="2"/>
+      <c r="G242" s="13"/>
+      <c r="H242" s="24"/>
+      <c r="I242" s="24"/>
+      <c r="J242" s="13"/>
+      <c r="K242" s="13"/>
+      <c r="L242" s="13"/>
+      <c r="M242" s="24"/>
+      <c r="N242" s="13"/>
+      <c r="O242" s="10"/>
+      <c r="P242" s="10"/>
+      <c r="Q242" s="10"/>
+      <c r="R242" s="10"/>
+      <c r="S242" s="10"/>
+      <c r="T242" s="10"/>
+      <c r="U242" s="10"/>
+      <c r="V242" s="6"/>
+    </row>
+    <row r="243" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A243" s="13"/>
+      <c r="B243" s="10"/>
+      <c r="C243" s="12"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="13"/>
+      <c r="H243" s="24"/>
+      <c r="I243" s="24"/>
+      <c r="J243" s="13"/>
+      <c r="K243" s="13"/>
+      <c r="L243" s="13"/>
+      <c r="M243" s="24"/>
+      <c r="N243" s="13"/>
+      <c r="O243" s="10"/>
+      <c r="P243" s="10"/>
+      <c r="Q243" s="10"/>
+      <c r="R243" s="10"/>
+      <c r="S243" s="10"/>
+      <c r="T243" s="10"/>
+      <c r="U243" s="10"/>
+      <c r="V243" s="6"/>
+    </row>
+    <row r="244" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A244" s="13"/>
+      <c r="B244" s="10"/>
+      <c r="C244" s="12"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="13"/>
+      <c r="H244" s="24"/>
+      <c r="I244" s="24"/>
+      <c r="J244" s="13"/>
+      <c r="K244" s="13"/>
+      <c r="L244" s="13"/>
+      <c r="M244" s="24"/>
+      <c r="N244" s="13"/>
+      <c r="O244" s="10"/>
+      <c r="P244" s="10"/>
+      <c r="Q244" s="10"/>
+      <c r="R244" s="10"/>
+      <c r="S244" s="10"/>
+      <c r="T244" s="10"/>
+      <c r="U244" s="10"/>
+      <c r="V244" s="6"/>
+    </row>
+    <row r="245" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A245" s="13"/>
+      <c r="B245" s="10"/>
+      <c r="C245" s="12"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="13"/>
+      <c r="H245" s="24"/>
+      <c r="I245" s="24"/>
+      <c r="J245" s="13"/>
+      <c r="K245" s="13"/>
+      <c r="L245" s="13"/>
+      <c r="M245" s="24"/>
+      <c r="N245" s="13"/>
+      <c r="O245" s="10"/>
+      <c r="P245" s="10"/>
+      <c r="Q245" s="10"/>
+      <c r="R245" s="10"/>
+      <c r="S245" s="10"/>
+      <c r="T245" s="10"/>
+      <c r="U245" s="10"/>
+      <c r="V245" s="6"/>
+    </row>
+    <row r="246" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A246" s="13"/>
+      <c r="B246" s="10"/>
+      <c r="C246" s="12"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+      <c r="F246" s="2"/>
+      <c r="G246" s="13"/>
+      <c r="H246" s="24"/>
+      <c r="I246" s="24"/>
+      <c r="J246" s="13"/>
+      <c r="K246" s="13"/>
+      <c r="L246" s="13"/>
+      <c r="M246" s="24"/>
+      <c r="N246" s="13"/>
+      <c r="O246" s="10"/>
+      <c r="P246" s="10"/>
+      <c r="Q246" s="10"/>
+      <c r="R246" s="10"/>
+      <c r="S246" s="10"/>
+      <c r="T246" s="10"/>
+      <c r="U246" s="10"/>
+      <c r="V246" s="6"/>
+    </row>
+    <row r="247" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A247" s="13"/>
+      <c r="B247" s="10"/>
+      <c r="C247" s="12"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="13"/>
+      <c r="H247" s="24"/>
+      <c r="I247" s="24"/>
+      <c r="J247" s="13"/>
+      <c r="K247" s="13"/>
+      <c r="L247" s="13"/>
+      <c r="M247" s="24"/>
+      <c r="N247" s="13"/>
+      <c r="O247" s="10"/>
+      <c r="P247" s="10"/>
+      <c r="Q247" s="10"/>
+      <c r="R247" s="10"/>
+      <c r="S247" s="10"/>
+      <c r="T247" s="10"/>
+      <c r="U247" s="10"/>
+      <c r="V247" s="6"/>
+    </row>
+    <row r="248" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A248" s="13"/>
+      <c r="B248" s="10"/>
+      <c r="C248" s="12"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="13"/>
+      <c r="H248" s="24"/>
+      <c r="I248" s="24"/>
+      <c r="J248" s="13"/>
+      <c r="K248" s="13"/>
+      <c r="L248" s="13"/>
+      <c r="M248" s="24"/>
+      <c r="N248" s="13"/>
+      <c r="O248" s="10"/>
+      <c r="P248" s="10"/>
+      <c r="Q248" s="10"/>
+      <c r="R248" s="10"/>
+      <c r="S248" s="10"/>
+      <c r="T248" s="10"/>
+      <c r="U248" s="10"/>
+      <c r="V248" s="6"/>
+    </row>
+    <row r="249" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A249" s="13"/>
+      <c r="B249" s="10"/>
+      <c r="C249" s="12"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="13"/>
+      <c r="H249" s="24"/>
+      <c r="I249" s="24"/>
+      <c r="J249" s="13"/>
+      <c r="K249" s="13"/>
+      <c r="L249" s="13"/>
+      <c r="M249" s="24"/>
+      <c r="N249" s="13"/>
+      <c r="O249" s="10"/>
+      <c r="P249" s="10"/>
+      <c r="Q249" s="10"/>
+      <c r="R249" s="10"/>
+      <c r="S249" s="10"/>
+      <c r="T249" s="10"/>
+      <c r="U249" s="10"/>
+      <c r="V249" s="6"/>
+    </row>
+    <row r="250" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A250" s="13"/>
+      <c r="B250" s="10"/>
+      <c r="C250" s="12"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="13"/>
+      <c r="H250" s="24"/>
+      <c r="I250" s="24"/>
+      <c r="J250" s="13"/>
+      <c r="K250" s="13"/>
+      <c r="L250" s="13"/>
+      <c r="M250" s="24"/>
+      <c r="N250" s="13"/>
+      <c r="O250" s="10"/>
+      <c r="P250" s="10"/>
+      <c r="Q250" s="10"/>
+      <c r="R250" s="10"/>
+      <c r="S250" s="10"/>
+      <c r="T250" s="10"/>
+      <c r="U250" s="10"/>
+      <c r="V250" s="6"/>
+    </row>
+    <row r="251" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A251" s="13"/>
+      <c r="B251" s="10"/>
+      <c r="C251" s="12"/>
+      <c r="D251" s="2"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="13"/>
+      <c r="H251" s="24"/>
+      <c r="I251" s="24"/>
+      <c r="J251" s="13"/>
+      <c r="K251" s="13"/>
+      <c r="L251" s="13"/>
+      <c r="M251" s="24"/>
+      <c r="N251" s="13"/>
+      <c r="O251" s="10"/>
+      <c r="P251" s="10"/>
+      <c r="Q251" s="10"/>
+      <c r="R251" s="10"/>
+      <c r="S251" s="10"/>
+      <c r="T251" s="10"/>
+      <c r="U251" s="10"/>
+      <c r="V251" s="6"/>
+    </row>
+    <row r="252" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A252" s="13"/>
+      <c r="B252" s="10"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="13"/>
+      <c r="H252" s="24"/>
+      <c r="I252" s="24"/>
+      <c r="J252" s="13"/>
+      <c r="K252" s="13"/>
+      <c r="L252" s="13"/>
+      <c r="M252" s="24"/>
+      <c r="N252" s="13"/>
+      <c r="O252" s="10"/>
+      <c r="P252" s="10"/>
+      <c r="Q252" s="10"/>
+      <c r="R252" s="10"/>
+      <c r="S252" s="10"/>
+      <c r="T252" s="10"/>
+      <c r="U252" s="10"/>
+      <c r="V252" s="6"/>
+    </row>
+    <row r="253" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A253" s="13"/>
+      <c r="B253" s="10"/>
+      <c r="C253" s="12"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="2"/>
+      <c r="F253" s="2"/>
+      <c r="G253" s="13"/>
+      <c r="H253" s="24"/>
+      <c r="I253" s="24"/>
+      <c r="J253" s="13"/>
+      <c r="K253" s="13"/>
+      <c r="L253" s="13"/>
+      <c r="M253" s="24"/>
+      <c r="N253" s="13"/>
+      <c r="O253" s="10"/>
+      <c r="P253" s="10"/>
+      <c r="Q253" s="10"/>
+      <c r="R253" s="10"/>
+      <c r="S253" s="10"/>
+      <c r="T253" s="10"/>
+      <c r="U253" s="10"/>
+      <c r="V253" s="6"/>
+    </row>
+    <row r="254" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A254" s="13"/>
+      <c r="B254" s="10"/>
+      <c r="C254" s="12"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="13"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="13"/>
+      <c r="K254" s="13"/>
+      <c r="L254" s="13"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="13"/>
+      <c r="O254" s="10"/>
+      <c r="P254" s="10"/>
+      <c r="Q254" s="10"/>
+      <c r="R254" s="10"/>
+      <c r="S254" s="10"/>
+      <c r="T254" s="10"/>
+      <c r="U254" s="10"/>
+      <c r="V254" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="3964" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{BE32F0F1-F4BF-48BD-8129-3D1AE406121E}"/>
+  <xr:revisionPtr revIDLastSave="4244" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C43EDE8A-B74A-4D47-BC10-02FE8F00520B}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1329" uniqueCount="522">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="581">
   <si>
     <t>Date</t>
   </si>
@@ -1508,6 +1508,9 @@
     <t>Medllama-1B-Instruct-v3-GGUF:Q4_K_M</t>
   </si>
   <si>
+    <t>1 B</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 807 MB</t>
   </si>
   <si>
@@ -1608,13 +1611,199 @@
   </si>
   <si>
     <t>9333.3ms</t>
+  </si>
+  <si>
+    <t>Llama 3.2 1B Instruct (Q4_K_M)</t>
+  </si>
+  <si>
+    <t>807mb</t>
+  </si>
+  <si>
+    <t>765.95 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> neural-chat:7b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    4.7 GB</t>
+  </si>
+  <si>
+    <t>1356.38 ms</t>
+  </si>
+  <si>
+    <t>dolphin-phi</t>
+  </si>
+  <si>
+    <t>1.6GB</t>
+  </si>
+  <si>
+    <t>954.49 ms</t>
+  </si>
+  <si>
+    <t>dolphin-mistral:latest</t>
+  </si>
+  <si>
+    <t>1548.55 ms</t>
+  </si>
+  <si>
+    <t>granite3.1-dense:2b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1.6GB </t>
+  </si>
+  <si>
+    <t>1503.92 ms</t>
+  </si>
+  <si>
+    <t>openhermes:latest</t>
+  </si>
+  <si>
+    <t>Teknium</t>
+  </si>
+  <si>
+    <t>1460.91 ms</t>
+  </si>
+  <si>
+    <t>5741.76 ms</t>
+  </si>
+  <si>
+    <t>xwinlm:7b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">7b </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 3.8 GB</t>
+  </si>
+  <si>
+    <r>
+      <t>Xwin-LM</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="12"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> team</t>
+    </r>
+  </si>
+  <si>
+    <t>4550.93 ms</t>
+  </si>
+  <si>
+    <t>starling-lm:7b</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.1 GB</t>
+  </si>
+  <si>
+    <t>nexusflow</t>
+  </si>
+  <si>
+    <t>3069.47 ms</t>
+  </si>
+  <si>
+    <t>falcon:7b-instruct</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.2 GB</t>
+  </si>
+  <si>
+    <t>Technology Innovation Institute</t>
+  </si>
+  <si>
+    <t>512.88 ms</t>
+  </si>
+  <si>
+    <t>qwen2.5:1.5b</t>
+  </si>
+  <si>
+    <t>Alibaba Cloud (Qwen team)</t>
+  </si>
+  <si>
+    <t>1587.89 ms</t>
+  </si>
+  <si>
+    <t>qwen2.5:3b</t>
+  </si>
+  <si>
+    <t>3b</t>
+  </si>
+  <si>
+    <t>1.9GB</t>
+  </si>
+  <si>
+    <t>1360.21 ms</t>
+  </si>
+  <si>
+    <t>qwen3:1.7b</t>
+  </si>
+  <si>
+    <t>1.4GB</t>
+  </si>
+  <si>
+    <t>6113.64 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> gemma2:2b</t>
+  </si>
+  <si>
+    <t>2.2b</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.6 GB</t>
+  </si>
+  <si>
+    <t>2703.15 ms</t>
+  </si>
+  <si>
+    <t>sam860/olmo2:1b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Allem Institute </t>
+  </si>
+  <si>
+    <t>1341.61 ms</t>
+  </si>
+  <si>
+    <t>opencoder:1.5b-instruct-q4_K_M</t>
+  </si>
+  <si>
+    <t>Infly</t>
+  </si>
+  <si>
+    <t>1515.96 ms</t>
+  </si>
+  <si>
+    <t>smollm:1.7b</t>
+  </si>
+  <si>
+    <t>1GB</t>
+  </si>
+  <si>
+    <t>1562.33 ms</t>
+  </si>
+  <si>
+    <t>hf.co/dengcao/ERNIE-4.5-0.3B-PT-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>0.3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240MB </t>
+  </si>
+  <si>
+    <t>340.65 ms</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6">
+  <fonts count="7">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -1653,6 +1842,12 @@
       <sz val="12"/>
       <color rgb="FF000000"/>
       <name val="Aptos Narrow"/>
+      <charset val="1"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="1"/>
+      <name val="Google Sans"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -2096,7 +2291,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="54">
+  <cellXfs count="55">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
@@ -2136,6 +2331,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="17" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -2521,7 +2717,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V224"/>
+  <dimension ref="A1:V254"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -2536,70 +2732,70 @@
   <sheetData>
     <row r="1" spans="1:22"/>
     <row r="2" spans="1:22" ht="21">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="38" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="38" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="44" t="s">
+      <c r="C2" s="45" t="s">
         <v>2</v>
       </c>
-      <c r="D2" s="45"/>
-      <c r="E2" s="45"/>
-      <c r="F2" s="45"/>
-      <c r="G2" s="48" t="s">
+      <c r="D2" s="46"/>
+      <c r="E2" s="46"/>
+      <c r="F2" s="46"/>
+      <c r="G2" s="49" t="s">
         <v>3</v>
       </c>
-      <c r="H2" s="49"/>
-      <c r="I2" s="49"/>
-      <c r="J2" s="49"/>
-      <c r="K2" s="49"/>
-      <c r="L2" s="49"/>
-      <c r="M2" s="49"/>
-      <c r="N2" s="50"/>
-      <c r="O2" s="42" t="s">
+      <c r="H2" s="50"/>
+      <c r="I2" s="50"/>
+      <c r="J2" s="50"/>
+      <c r="K2" s="50"/>
+      <c r="L2" s="50"/>
+      <c r="M2" s="50"/>
+      <c r="N2" s="51"/>
+      <c r="O2" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="P2" s="42"/>
-      <c r="Q2" s="42"/>
-      <c r="R2" s="42"/>
-      <c r="S2" s="42"/>
-      <c r="T2" s="42"/>
-      <c r="U2" s="42"/>
-      <c r="V2" s="43"/>
+      <c r="P2" s="43"/>
+      <c r="Q2" s="43"/>
+      <c r="R2" s="43"/>
+      <c r="S2" s="43"/>
+      <c r="T2" s="43"/>
+      <c r="U2" s="43"/>
+      <c r="V2" s="44"/>
     </row>
     <row r="3" spans="1:22" ht="18.75">
-      <c r="A3" s="38"/>
-      <c r="B3" s="38"/>
-      <c r="C3" s="46"/>
-      <c r="D3" s="47"/>
-      <c r="E3" s="47"/>
-      <c r="F3" s="47"/>
-      <c r="G3" s="51"/>
-      <c r="H3" s="52"/>
-      <c r="I3" s="52"/>
-      <c r="J3" s="52"/>
-      <c r="K3" s="52"/>
-      <c r="L3" s="52"/>
-      <c r="M3" s="52"/>
-      <c r="N3" s="53"/>
-      <c r="O3" s="40" t="s">
+      <c r="A3" s="39"/>
+      <c r="B3" s="39"/>
+      <c r="C3" s="47"/>
+      <c r="D3" s="48"/>
+      <c r="E3" s="48"/>
+      <c r="F3" s="48"/>
+      <c r="G3" s="52"/>
+      <c r="H3" s="53"/>
+      <c r="I3" s="53"/>
+      <c r="J3" s="53"/>
+      <c r="K3" s="53"/>
+      <c r="L3" s="53"/>
+      <c r="M3" s="53"/>
+      <c r="N3" s="54"/>
+      <c r="O3" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="P3" s="40"/>
-      <c r="Q3" s="40"/>
-      <c r="R3" s="40" t="s">
+      <c r="P3" s="41"/>
+      <c r="Q3" s="41"/>
+      <c r="R3" s="41" t="s">
         <v>6</v>
       </c>
-      <c r="S3" s="40"/>
-      <c r="T3" s="40"/>
-      <c r="U3" s="40"/>
-      <c r="V3" s="41"/>
+      <c r="S3" s="41"/>
+      <c r="T3" s="41"/>
+      <c r="U3" s="41"/>
+      <c r="V3" s="42"/>
     </row>
     <row r="4" spans="1:22">
-      <c r="A4" s="39"/>
-      <c r="B4" s="39"/>
+      <c r="A4" s="40"/>
+      <c r="B4" s="40"/>
       <c r="C4" s="11" t="s">
         <v>7</v>
       </c>
@@ -13480,9 +13676,11 @@
       <c r="C213" s="12" t="s">
         <v>487</v>
       </c>
-      <c r="D213" s="2"/>
+      <c r="D213" s="2" t="s">
+        <v>488</v>
+      </c>
       <c r="E213" s="2" t="s">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="F213" s="2" t="s">
         <v>69</v>
@@ -13528,13 +13726,13 @@
         <v>393</v>
       </c>
       <c r="C214" s="12" t="s">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="D214" t="s">
         <v>409</v>
       </c>
       <c r="E214" s="2" t="s">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="F214" t="s">
         <v>69</v>
@@ -13580,7 +13778,7 @@
         <v>398</v>
       </c>
       <c r="C215" t="s">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="D215" t="s">
         <v>409</v>
@@ -13606,7 +13804,7 @@
         <v>0.37</v>
       </c>
       <c r="Q215" t="s">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="R215">
         <v>0.496</v>
@@ -13632,16 +13830,16 @@
         <v>367</v>
       </c>
       <c r="C216" t="s">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="D216" s="2" t="s">
         <v>53</v>
       </c>
       <c r="E216" s="2" t="s">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="F216" t="s">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="G216" s="23"/>
       <c r="H216" s="2"/>
@@ -13658,7 +13856,7 @@
         <v>0.40400000000000003</v>
       </c>
       <c r="Q216" s="2" t="s">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="R216" s="2">
         <v>0.52300000000000002</v>
@@ -13684,13 +13882,13 @@
         <v>393</v>
       </c>
       <c r="C217" t="s">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="D217" s="2" t="s">
         <v>477</v>
       </c>
       <c r="E217" s="2" t="s">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="F217" s="2" t="s">
         <v>69</v>
@@ -13736,13 +13934,13 @@
         <v>398</v>
       </c>
       <c r="C218" t="s">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="D218" t="s">
         <v>409</v>
       </c>
       <c r="E218" s="2" t="s">
-        <v>500</v>
+        <v>501</v>
       </c>
       <c r="F218" s="2" t="s">
         <v>69</v>
@@ -13762,7 +13960,7 @@
         <v>0.624</v>
       </c>
       <c r="Q218" t="s">
-        <v>501</v>
+        <v>502</v>
       </c>
       <c r="R218">
         <v>0.69899999999999995</v>
@@ -13788,13 +13986,13 @@
         <v>393</v>
       </c>
       <c r="C219" t="s">
-        <v>502</v>
+        <v>503</v>
       </c>
       <c r="D219" s="2" t="s">
-        <v>503</v>
+        <v>504</v>
       </c>
       <c r="E219" s="2" t="s">
-        <v>504</v>
+        <v>505</v>
       </c>
       <c r="F219" s="2" t="s">
         <v>88</v>
@@ -13814,7 +14012,7 @@
         <v>0.624</v>
       </c>
       <c r="Q219" t="s">
-        <v>505</v>
+        <v>506</v>
       </c>
       <c r="R219">
         <v>0.69899999999999995</v>
@@ -13840,7 +14038,7 @@
         <v>398</v>
       </c>
       <c r="C220" s="12" t="s">
-        <v>506</v>
+        <v>507</v>
       </c>
       <c r="D220" t="s">
         <v>468</v>
@@ -13866,7 +14064,7 @@
         <v>0.48799999999999999</v>
       </c>
       <c r="Q220" t="s">
-        <v>507</v>
+        <v>508</v>
       </c>
       <c r="R220">
         <v>0.59099999999999997</v>
@@ -13892,7 +14090,7 @@
         <v>393</v>
       </c>
       <c r="C221" t="s">
-        <v>508</v>
+        <v>509</v>
       </c>
       <c r="D221" s="2" t="s">
         <v>376</v>
@@ -13918,7 +14116,7 @@
         <v>0.53</v>
       </c>
       <c r="Q221" t="s">
-        <v>509</v>
+        <v>510</v>
       </c>
       <c r="R221">
         <v>0.624</v>
@@ -13944,7 +14142,7 @@
         <v>398</v>
       </c>
       <c r="C222" t="s">
-        <v>510</v>
+        <v>511</v>
       </c>
       <c r="D222" s="2" t="s">
         <v>34</v>
@@ -13970,7 +14168,7 @@
         <v>0.60099999999999998</v>
       </c>
       <c r="Q222" t="s">
-        <v>511</v>
+        <v>512</v>
       </c>
       <c r="R222">
         <v>0.68100000000000005</v>
@@ -13996,16 +14194,16 @@
         <v>367</v>
       </c>
       <c r="C223" t="s">
-        <v>512</v>
+        <v>513</v>
       </c>
       <c r="D223" t="s">
-        <v>513</v>
+        <v>514</v>
       </c>
       <c r="E223" t="s">
-        <v>514</v>
+        <v>515</v>
       </c>
       <c r="F223" s="2" t="s">
-        <v>515</v>
+        <v>516</v>
       </c>
       <c r="G223" s="23"/>
       <c r="H223" s="2"/>
@@ -14022,7 +14220,7 @@
         <v>0.34300000000000003</v>
       </c>
       <c r="Q223" t="s">
-        <v>516</v>
+        <v>517</v>
       </c>
       <c r="R223">
         <v>0.45500000000000002</v>
@@ -14048,16 +14246,16 @@
         <v>367</v>
       </c>
       <c r="C224" t="s">
-        <v>517</v>
+        <v>518</v>
       </c>
       <c r="D224" t="s">
-        <v>518</v>
+        <v>519</v>
       </c>
       <c r="E224" t="s">
-        <v>519</v>
+        <v>520</v>
       </c>
       <c r="F224" t="s">
-        <v>520</v>
+        <v>521</v>
       </c>
       <c r="G224" s="23"/>
       <c r="O224">
@@ -14067,7 +14265,7 @@
         <v>0.23300000000000001</v>
       </c>
       <c r="Q224" t="s">
-        <v>521</v>
+        <v>522</v>
       </c>
       <c r="R224">
         <v>0.33800000000000002</v>
@@ -14084,6 +14282,1230 @@
       <c r="V224">
         <v>0.30199999999999999</v>
       </c>
+    </row>
+    <row r="225" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A225" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B225" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C225" t="s">
+        <v>523</v>
+      </c>
+      <c r="D225" t="s">
+        <v>409</v>
+      </c>
+      <c r="E225" s="2" t="s">
+        <v>524</v>
+      </c>
+      <c r="F225" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G225" s="24"/>
+      <c r="H225" s="24"/>
+      <c r="I225" s="24"/>
+      <c r="J225" s="13"/>
+      <c r="K225" s="13"/>
+      <c r="L225" s="13"/>
+      <c r="M225" s="24"/>
+      <c r="N225" s="23"/>
+      <c r="O225">
+        <v>0.65100000000000002</v>
+      </c>
+      <c r="P225">
+        <v>0.623</v>
+      </c>
+      <c r="Q225" t="s">
+        <v>525</v>
+      </c>
+      <c r="R225">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="S225">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="T225">
+        <v>1</v>
+      </c>
+      <c r="U225">
+        <v>0.82399999999999995</v>
+      </c>
+      <c r="V225">
+        <v>0.59599999999999997</v>
+      </c>
+    </row>
+    <row r="226" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A226" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B226" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C226" s="12" t="s">
+        <v>526</v>
+      </c>
+      <c r="D226" t="s">
+        <v>257</v>
+      </c>
+      <c r="E226" s="2" t="s">
+        <v>527</v>
+      </c>
+      <c r="F226" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G226" s="13"/>
+      <c r="H226" s="24"/>
+      <c r="I226" s="24"/>
+      <c r="J226" s="13"/>
+      <c r="K226" s="23"/>
+      <c r="L226" s="13"/>
+      <c r="M226" s="24"/>
+      <c r="N226" s="13"/>
+      <c r="O226">
+        <v>0.89300000000000002</v>
+      </c>
+      <c r="P226">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="Q226" t="s">
+        <v>528</v>
+      </c>
+      <c r="R226">
+        <v>0.59299999999999997</v>
+      </c>
+      <c r="S226">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="T226">
+        <v>1</v>
+      </c>
+      <c r="U226">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="V226">
+        <v>0.61299999999999999</v>
+      </c>
+    </row>
+    <row r="227" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A227" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B227" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C227" t="s">
+        <v>529</v>
+      </c>
+      <c r="D227" s="36" t="s">
+        <v>115</v>
+      </c>
+      <c r="E227" s="2" t="s">
+        <v>530</v>
+      </c>
+      <c r="F227" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G227" s="13"/>
+      <c r="H227" s="24"/>
+      <c r="I227" s="24"/>
+      <c r="J227" s="13"/>
+      <c r="K227" s="23"/>
+      <c r="L227" s="13"/>
+      <c r="M227" s="24"/>
+      <c r="N227" s="13"/>
+      <c r="O227">
+        <v>0.83</v>
+      </c>
+      <c r="P227">
+        <v>0.45400000000000001</v>
+      </c>
+      <c r="Q227" t="s">
+        <v>531</v>
+      </c>
+      <c r="R227">
+        <v>0.56299999999999994</v>
+      </c>
+      <c r="S227">
+        <v>0.61199999999999999</v>
+      </c>
+      <c r="T227">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U227">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="V227">
+        <v>0.56999999999999995</v>
+      </c>
+    </row>
+    <row r="228" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A228" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B228" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C228" s="12" t="s">
+        <v>532</v>
+      </c>
+      <c r="D228" t="s">
+        <v>257</v>
+      </c>
+      <c r="E228" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="F228" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G228" s="13"/>
+      <c r="H228" s="24"/>
+      <c r="I228" s="24"/>
+      <c r="J228" s="13"/>
+      <c r="K228" s="23"/>
+      <c r="L228" s="13"/>
+      <c r="M228" s="24"/>
+      <c r="N228" s="13"/>
+      <c r="O228">
+        <v>0.85699999999999998</v>
+      </c>
+      <c r="P228">
+        <v>0.497</v>
+      </c>
+      <c r="Q228" t="s">
+        <v>533</v>
+      </c>
+      <c r="R228">
+        <v>0.59799999999999998</v>
+      </c>
+      <c r="S228">
+        <v>0.59599999999999997</v>
+      </c>
+      <c r="T228">
+        <v>1</v>
+      </c>
+      <c r="U228">
+        <v>0.88300000000000001</v>
+      </c>
+      <c r="V228">
+        <v>0.60499999999999998</v>
+      </c>
+    </row>
+    <row r="229" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A229" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B229" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C229" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="D229" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E229" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F229" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G229" s="13"/>
+      <c r="H229" s="24"/>
+      <c r="I229" s="24"/>
+      <c r="J229" s="13"/>
+      <c r="K229" s="23"/>
+      <c r="L229" s="13"/>
+      <c r="M229" s="24"/>
+      <c r="N229" s="13"/>
+      <c r="O229">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="P229">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="Q229" t="s">
+        <v>536</v>
+      </c>
+      <c r="R229">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="S229">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="T229">
+        <v>1</v>
+      </c>
+      <c r="U229">
+        <v>0.88900000000000001</v>
+      </c>
+      <c r="V229">
+        <v>0.61899999999999999</v>
+      </c>
+    </row>
+    <row r="230" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A230" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B230" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C230" s="12" t="s">
+        <v>537</v>
+      </c>
+      <c r="D230" t="s">
+        <v>257</v>
+      </c>
+      <c r="E230" s="2" t="s">
+        <v>258</v>
+      </c>
+      <c r="F230" t="s">
+        <v>538</v>
+      </c>
+      <c r="G230" s="13"/>
+      <c r="H230" s="23"/>
+      <c r="I230" s="24"/>
+      <c r="J230" s="13"/>
+      <c r="K230" s="13"/>
+      <c r="L230" s="13"/>
+      <c r="M230" s="24"/>
+      <c r="N230" s="13"/>
+      <c r="O230">
+        <v>0.72199999999999998</v>
+      </c>
+      <c r="P230">
+        <v>0.69699999999999995</v>
+      </c>
+      <c r="Q230" t="s">
+        <v>539</v>
+      </c>
+      <c r="R230">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="S230">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="T230">
+        <v>0.82</v>
+      </c>
+      <c r="U230">
+        <v>0.94199999999999995</v>
+      </c>
+      <c r="V230">
+        <v>0.61699999999999999</v>
+      </c>
+    </row>
+    <row r="231" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A231" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B231" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C231" s="12" t="s">
+        <v>446</v>
+      </c>
+      <c r="D231" s="2" t="s">
+        <v>257</v>
+      </c>
+      <c r="E231" s="2" t="s">
+        <v>448</v>
+      </c>
+      <c r="F231" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G231" s="13"/>
+      <c r="H231" s="24"/>
+      <c r="I231" s="23"/>
+      <c r="J231" s="13"/>
+      <c r="K231" s="13"/>
+      <c r="L231" s="13"/>
+      <c r="M231" s="24"/>
+      <c r="N231" s="13"/>
+      <c r="O231">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="P231">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="Q231" t="s">
+        <v>540</v>
+      </c>
+      <c r="R231">
+        <v>0.71499999999999997</v>
+      </c>
+      <c r="S231">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="T231">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="U231">
+        <v>0.92800000000000005</v>
+      </c>
+      <c r="V231">
+        <v>0.63300000000000001</v>
+      </c>
+    </row>
+    <row r="232" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A232" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B232" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C232" s="12" t="s">
+        <v>541</v>
+      </c>
+      <c r="D232" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E232" s="2" t="s">
+        <v>543</v>
+      </c>
+      <c r="F232" s="37" t="s">
+        <v>544</v>
+      </c>
+      <c r="G232" s="13"/>
+      <c r="H232" s="24"/>
+      <c r="I232" s="24"/>
+      <c r="J232" s="13"/>
+      <c r="K232" s="13"/>
+      <c r="L232" s="23"/>
+      <c r="M232" s="24"/>
+      <c r="N232" s="13"/>
+      <c r="O232">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="P232">
+        <v>0.58499999999999996</v>
+      </c>
+      <c r="Q232" t="s">
+        <v>545</v>
+      </c>
+      <c r="R232">
+        <v>0.66800000000000004</v>
+      </c>
+      <c r="S232">
+        <v>0.56499999999999995</v>
+      </c>
+      <c r="T232">
+        <v>0.90200000000000002</v>
+      </c>
+      <c r="U232">
+        <v>0.877</v>
+      </c>
+      <c r="V232">
+        <v>0.59199999999999997</v>
+      </c>
+    </row>
+    <row r="233" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A233" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B233" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C233" s="12" t="s">
+        <v>546</v>
+      </c>
+      <c r="D233" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E233" s="2" t="s">
+        <v>547</v>
+      </c>
+      <c r="F233" s="2" t="s">
+        <v>548</v>
+      </c>
+      <c r="G233" s="13"/>
+      <c r="H233" s="24"/>
+      <c r="I233" s="24"/>
+      <c r="J233" s="13"/>
+      <c r="K233" s="13"/>
+      <c r="L233" s="13"/>
+      <c r="M233" s="23"/>
+      <c r="N233" s="13"/>
+      <c r="O233">
+        <v>0.70499999999999996</v>
+      </c>
+      <c r="P233">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="Q233" t="s">
+        <v>549</v>
+      </c>
+      <c r="R233">
+        <v>0.68700000000000006</v>
+      </c>
+      <c r="S233">
+        <v>0.55500000000000005</v>
+      </c>
+      <c r="T233">
+        <v>1</v>
+      </c>
+      <c r="U233">
+        <v>0.88</v>
+      </c>
+      <c r="V233">
+        <v>0.60099999999999998</v>
+      </c>
+    </row>
+    <row r="234" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A234" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B234" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C234" s="12" t="s">
+        <v>550</v>
+      </c>
+      <c r="D234" s="2" t="s">
+        <v>542</v>
+      </c>
+      <c r="E234" s="2" t="s">
+        <v>551</v>
+      </c>
+      <c r="F234" t="s">
+        <v>552</v>
+      </c>
+      <c r="G234" s="23"/>
+      <c r="H234" s="24"/>
+      <c r="I234" s="24"/>
+      <c r="J234" s="13"/>
+      <c r="K234" s="13"/>
+      <c r="L234" s="13"/>
+      <c r="M234" s="24"/>
+      <c r="N234" s="13"/>
+      <c r="O234">
+        <v>0.3</v>
+      </c>
+      <c r="P234">
+        <v>0.48499999999999999</v>
+      </c>
+      <c r="Q234" t="s">
+        <v>553</v>
+      </c>
+      <c r="R234">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="S234">
+        <v>0.60099999999999998</v>
+      </c>
+      <c r="T234">
+        <v>1</v>
+      </c>
+      <c r="U234">
+        <v>0.66600000000000004</v>
+      </c>
+      <c r="V234">
+        <v>0.46</v>
+      </c>
+    </row>
+    <row r="235" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A235" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B235" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C235" s="12" t="s">
+        <v>554</v>
+      </c>
+      <c r="D235" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E235" t="s">
+        <v>197</v>
+      </c>
+      <c r="F235" t="s">
+        <v>555</v>
+      </c>
+      <c r="G235" s="13"/>
+      <c r="H235" s="24"/>
+      <c r="I235" s="23"/>
+      <c r="J235" s="13"/>
+      <c r="K235" s="13"/>
+      <c r="L235" s="13"/>
+      <c r="M235" s="24"/>
+      <c r="N235" s="13"/>
+      <c r="O235">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="P235">
+        <v>0.65</v>
+      </c>
+      <c r="Q235" t="s">
+        <v>556</v>
+      </c>
+      <c r="R235">
+        <v>0.72</v>
+      </c>
+      <c r="S235">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="T235">
+        <v>0.878</v>
+      </c>
+      <c r="U235">
+        <v>0.86399999999999999</v>
+      </c>
+      <c r="V235">
+        <v>0.63100000000000001</v>
+      </c>
+    </row>
+    <row r="236" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A236" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B236" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C236" s="12" t="s">
+        <v>557</v>
+      </c>
+      <c r="D236" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E236" t="s">
+        <v>559</v>
+      </c>
+      <c r="F236" s="2" t="s">
+        <v>555</v>
+      </c>
+      <c r="G236" s="13"/>
+      <c r="H236" s="24"/>
+      <c r="I236" s="24"/>
+      <c r="J236" s="13"/>
+      <c r="K236" s="23"/>
+      <c r="L236" s="13"/>
+      <c r="M236" s="24"/>
+      <c r="N236" s="13"/>
+      <c r="O236">
+        <v>0.78</v>
+      </c>
+      <c r="P236">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="Q236" t="s">
+        <v>560</v>
+      </c>
+      <c r="R236">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="S236">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="T236">
+        <v>1</v>
+      </c>
+      <c r="U236">
+        <v>0.86199999999999999</v>
+      </c>
+      <c r="V236">
+        <v>0.59299999999999997</v>
+      </c>
+    </row>
+    <row r="237" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A237" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B237" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C237" s="12" t="s">
+        <v>561</v>
+      </c>
+      <c r="D237" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E237" s="2" t="s">
+        <v>562</v>
+      </c>
+      <c r="F237" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="G237" s="13"/>
+      <c r="H237" s="24"/>
+      <c r="I237" s="24"/>
+      <c r="J237" s="13"/>
+      <c r="K237" s="13"/>
+      <c r="L237" s="13"/>
+      <c r="M237" s="24"/>
+      <c r="N237" s="23"/>
+      <c r="O237">
+        <v>0.78</v>
+      </c>
+      <c r="P237">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="Q237" t="s">
+        <v>563</v>
+      </c>
+      <c r="R237">
+        <v>0.67</v>
+      </c>
+      <c r="S237">
+        <v>0.57099999999999995</v>
+      </c>
+      <c r="T237">
+        <v>1</v>
+      </c>
+      <c r="U237">
+        <v>0.84499999999999997</v>
+      </c>
+      <c r="V237">
+        <v>0.60199999999999998</v>
+      </c>
+    </row>
+    <row r="238" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A238" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B238" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C238" s="12" t="s">
+        <v>564</v>
+      </c>
+      <c r="D238" s="2" t="s">
+        <v>565</v>
+      </c>
+      <c r="E238" s="2" t="s">
+        <v>566</v>
+      </c>
+      <c r="F238" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G238" s="13"/>
+      <c r="H238" s="24"/>
+      <c r="I238" s="24"/>
+      <c r="J238" s="23"/>
+      <c r="K238" s="13"/>
+      <c r="L238" s="13"/>
+      <c r="M238" s="24"/>
+      <c r="N238" s="13"/>
+      <c r="O238">
+        <v>0.75800000000000001</v>
+      </c>
+      <c r="P238">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="Q238" t="s">
+        <v>567</v>
+      </c>
+      <c r="R238">
+        <v>0.73</v>
+      </c>
+      <c r="S238">
+        <v>0.53500000000000003</v>
+      </c>
+      <c r="T238">
+        <v>0.93700000000000006</v>
+      </c>
+      <c r="U238">
+        <v>0.89800000000000002</v>
+      </c>
+      <c r="V238">
+        <v>0.621</v>
+      </c>
+    </row>
+    <row r="239" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A239" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B239" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C239" s="12" t="s">
+        <v>568</v>
+      </c>
+      <c r="D239" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E239" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F239" s="2" t="s">
+        <v>569</v>
+      </c>
+      <c r="G239" s="13"/>
+      <c r="H239" s="24"/>
+      <c r="I239" s="13"/>
+      <c r="J239" s="13"/>
+      <c r="K239" s="13"/>
+      <c r="L239" s="23"/>
+      <c r="M239" s="24"/>
+      <c r="N239" s="13"/>
+      <c r="O239">
+        <v>0.76</v>
+      </c>
+      <c r="P239">
+        <v>0.60899999999999999</v>
+      </c>
+      <c r="Q239" t="s">
+        <v>570</v>
+      </c>
+      <c r="R239">
+        <v>0.68799999999999994</v>
+      </c>
+      <c r="S239">
+        <v>0.55900000000000005</v>
+      </c>
+      <c r="T239">
+        <v>0.85</v>
+      </c>
+      <c r="U239">
+        <v>0.878</v>
+      </c>
+      <c r="V239">
+        <v>0.59499999999999997</v>
+      </c>
+    </row>
+    <row r="240" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A240" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B240" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C240" s="12" t="s">
+        <v>571</v>
+      </c>
+      <c r="D240" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E240" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F240" s="2" t="s">
+        <v>572</v>
+      </c>
+      <c r="G240" s="13"/>
+      <c r="H240" s="24"/>
+      <c r="I240" s="24"/>
+      <c r="J240" s="13"/>
+      <c r="K240" s="13"/>
+      <c r="L240" s="13"/>
+      <c r="M240" s="23"/>
+      <c r="N240" s="13"/>
+      <c r="O240">
+        <v>0.78</v>
+      </c>
+      <c r="P240">
+        <v>0.39500000000000002</v>
+      </c>
+      <c r="Q240" t="s">
+        <v>573</v>
+      </c>
+      <c r="R240">
+        <v>0.46600000000000003</v>
+      </c>
+      <c r="S240">
+        <v>0.624</v>
+      </c>
+      <c r="T240">
+        <v>1</v>
+      </c>
+      <c r="U240">
+        <v>0.82099999999999995</v>
+      </c>
+      <c r="V240">
+        <v>0.54600000000000004</v>
+      </c>
+    </row>
+    <row r="241" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A241" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B241" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C241" t="s">
+        <v>574</v>
+      </c>
+      <c r="D241" s="2" t="s">
+        <v>67</v>
+      </c>
+      <c r="E241" s="2" t="s">
+        <v>575</v>
+      </c>
+      <c r="F241" t="s">
+        <v>69</v>
+      </c>
+      <c r="G241" s="13"/>
+      <c r="H241" s="24"/>
+      <c r="I241" s="24"/>
+      <c r="J241" s="13"/>
+      <c r="K241" s="13"/>
+      <c r="L241" s="13"/>
+      <c r="M241" s="24"/>
+      <c r="N241" s="23"/>
+      <c r="O241">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="P241">
+        <v>0.55100000000000005</v>
+      </c>
+      <c r="Q241" t="s">
+        <v>576</v>
+      </c>
+      <c r="R241">
+        <v>0.64100000000000001</v>
+      </c>
+      <c r="S241">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="T241">
+        <v>1</v>
+      </c>
+      <c r="U241">
+        <v>0.88100000000000001</v>
+      </c>
+      <c r="V241">
+        <v>0.56899999999999995</v>
+      </c>
+    </row>
+    <row r="242" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A242" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C242" t="s">
+        <v>577</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="F242" t="s">
+        <v>69</v>
+      </c>
+      <c r="G242" s="23"/>
+      <c r="H242" s="24"/>
+      <c r="I242" s="24"/>
+      <c r="J242" s="13"/>
+      <c r="K242" s="13"/>
+      <c r="L242" s="13"/>
+      <c r="M242" s="24"/>
+      <c r="N242" s="13"/>
+      <c r="O242">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="P242">
+        <v>0.32</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>580</v>
+      </c>
+      <c r="R242">
+        <v>0.436</v>
+      </c>
+      <c r="S242">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="T242">
+        <v>1</v>
+      </c>
+      <c r="U242">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="V242">
+        <v>0.41699999999999998</v>
+      </c>
+    </row>
+    <row r="243" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A243" s="13"/>
+      <c r="B243" s="10"/>
+      <c r="C243" s="12"/>
+      <c r="D243" s="2"/>
+      <c r="E243" s="2"/>
+      <c r="F243" s="2"/>
+      <c r="G243" s="13"/>
+      <c r="H243" s="24"/>
+      <c r="I243" s="24"/>
+      <c r="J243" s="13"/>
+      <c r="K243" s="13"/>
+      <c r="L243" s="13"/>
+      <c r="M243" s="24"/>
+      <c r="N243" s="13"/>
+      <c r="O243" s="10"/>
+      <c r="P243" s="10"/>
+      <c r="Q243" s="10"/>
+      <c r="R243" s="10"/>
+      <c r="S243" s="10"/>
+      <c r="T243" s="10"/>
+      <c r="U243" s="10"/>
+      <c r="V243" s="6"/>
+    </row>
+    <row r="244" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A244" s="13"/>
+      <c r="B244" s="10"/>
+      <c r="C244" s="12"/>
+      <c r="D244" s="2"/>
+      <c r="E244" s="2"/>
+      <c r="F244" s="2"/>
+      <c r="G244" s="13"/>
+      <c r="H244" s="24"/>
+      <c r="I244" s="24"/>
+      <c r="J244" s="13"/>
+      <c r="K244" s="13"/>
+      <c r="L244" s="13"/>
+      <c r="M244" s="24"/>
+      <c r="N244" s="13"/>
+      <c r="O244" s="10"/>
+      <c r="P244" s="10"/>
+      <c r="Q244" s="10"/>
+      <c r="R244" s="10"/>
+      <c r="S244" s="10"/>
+      <c r="T244" s="10"/>
+      <c r="U244" s="10"/>
+      <c r="V244" s="6"/>
+    </row>
+    <row r="245" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A245" s="13"/>
+      <c r="B245" s="10"/>
+      <c r="C245" s="12"/>
+      <c r="D245" s="2"/>
+      <c r="E245" s="2"/>
+      <c r="F245" s="2"/>
+      <c r="G245" s="13"/>
+      <c r="H245" s="24"/>
+      <c r="I245" s="24"/>
+      <c r="J245" s="13"/>
+      <c r="K245" s="13"/>
+      <c r="L245" s="13"/>
+      <c r="M245" s="24"/>
+      <c r="N245" s="13"/>
+      <c r="O245" s="10"/>
+      <c r="P245" s="10"/>
+      <c r="Q245" s="10"/>
+      <c r="R245" s="10"/>
+      <c r="S245" s="10"/>
+      <c r="T245" s="10"/>
+      <c r="U245" s="10"/>
+      <c r="V245" s="6"/>
+    </row>
+    <row r="246" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A246" s="13"/>
+      <c r="B246" s="10"/>
+      <c r="C246" s="12"/>
+      <c r="D246" s="2"/>
+      <c r="E246" s="2"/>
+      <c r="F246" s="2"/>
+      <c r="G246" s="13"/>
+      <c r="H246" s="24"/>
+      <c r="I246" s="24"/>
+      <c r="J246" s="13"/>
+      <c r="K246" s="13"/>
+      <c r="L246" s="13"/>
+      <c r="M246" s="24"/>
+      <c r="N246" s="13"/>
+      <c r="O246" s="10"/>
+      <c r="P246" s="10"/>
+      <c r="Q246" s="10"/>
+      <c r="R246" s="10"/>
+      <c r="S246" s="10"/>
+      <c r="T246" s="10"/>
+      <c r="U246" s="10"/>
+      <c r="V246" s="6"/>
+    </row>
+    <row r="247" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A247" s="13"/>
+      <c r="B247" s="10"/>
+      <c r="C247" s="12"/>
+      <c r="D247" s="2"/>
+      <c r="E247" s="2"/>
+      <c r="F247" s="2"/>
+      <c r="G247" s="13"/>
+      <c r="H247" s="24"/>
+      <c r="I247" s="24"/>
+      <c r="J247" s="13"/>
+      <c r="K247" s="13"/>
+      <c r="L247" s="13"/>
+      <c r="M247" s="24"/>
+      <c r="N247" s="13"/>
+      <c r="O247" s="10"/>
+      <c r="P247" s="10"/>
+      <c r="Q247" s="10"/>
+      <c r="R247" s="10"/>
+      <c r="S247" s="10"/>
+      <c r="T247" s="10"/>
+      <c r="U247" s="10"/>
+      <c r="V247" s="6"/>
+    </row>
+    <row r="248" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A248" s="13"/>
+      <c r="B248" s="10"/>
+      <c r="C248" s="12"/>
+      <c r="D248" s="2"/>
+      <c r="E248" s="2"/>
+      <c r="F248" s="2"/>
+      <c r="G248" s="13"/>
+      <c r="H248" s="24"/>
+      <c r="I248" s="24"/>
+      <c r="J248" s="13"/>
+      <c r="K248" s="13"/>
+      <c r="L248" s="13"/>
+      <c r="M248" s="24"/>
+      <c r="N248" s="13"/>
+      <c r="O248" s="10"/>
+      <c r="P248" s="10"/>
+      <c r="Q248" s="10"/>
+      <c r="R248" s="10"/>
+      <c r="S248" s="10"/>
+      <c r="T248" s="10"/>
+      <c r="U248" s="10"/>
+      <c r="V248" s="6"/>
+    </row>
+    <row r="249" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A249" s="13"/>
+      <c r="B249" s="10"/>
+      <c r="C249" s="12"/>
+      <c r="D249" s="2"/>
+      <c r="E249" s="2"/>
+      <c r="F249" s="2"/>
+      <c r="G249" s="13"/>
+      <c r="H249" s="24"/>
+      <c r="I249" s="24"/>
+      <c r="J249" s="13"/>
+      <c r="K249" s="13"/>
+      <c r="L249" s="13"/>
+      <c r="M249" s="24"/>
+      <c r="N249" s="13"/>
+      <c r="O249" s="10"/>
+      <c r="P249" s="10"/>
+      <c r="Q249" s="10"/>
+      <c r="R249" s="10"/>
+      <c r="S249" s="10"/>
+      <c r="T249" s="10"/>
+      <c r="U249" s="10"/>
+      <c r="V249" s="6"/>
+    </row>
+    <row r="250" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A250" s="13"/>
+      <c r="B250" s="10"/>
+      <c r="C250" s="12"/>
+      <c r="D250" s="2"/>
+      <c r="E250" s="2"/>
+      <c r="F250" s="2"/>
+      <c r="G250" s="13"/>
+      <c r="H250" s="24"/>
+      <c r="I250" s="24"/>
+      <c r="J250" s="13"/>
+      <c r="K250" s="13"/>
+      <c r="L250" s="13"/>
+      <c r="M250" s="24"/>
+      <c r="N250" s="13"/>
+      <c r="O250" s="10"/>
+      <c r="P250" s="10"/>
+      <c r="Q250" s="10"/>
+      <c r="R250" s="10"/>
+      <c r="S250" s="10"/>
+      <c r="T250" s="10"/>
+      <c r="U250" s="10"/>
+      <c r="V250" s="6"/>
+    </row>
+    <row r="251" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A251" s="13"/>
+      <c r="B251" s="10"/>
+      <c r="C251" s="12"/>
+      <c r="D251" s="2"/>
+      <c r="E251" s="2"/>
+      <c r="F251" s="2"/>
+      <c r="G251" s="13"/>
+      <c r="H251" s="24"/>
+      <c r="I251" s="24"/>
+      <c r="J251" s="13"/>
+      <c r="K251" s="13"/>
+      <c r="L251" s="13"/>
+      <c r="M251" s="24"/>
+      <c r="N251" s="13"/>
+      <c r="O251" s="10"/>
+      <c r="P251" s="10"/>
+      <c r="Q251" s="10"/>
+      <c r="R251" s="10"/>
+      <c r="S251" s="10"/>
+      <c r="T251" s="10"/>
+      <c r="U251" s="10"/>
+      <c r="V251" s="6"/>
+    </row>
+    <row r="252" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A252" s="13"/>
+      <c r="B252" s="10"/>
+      <c r="C252" s="12"/>
+      <c r="D252" s="2"/>
+      <c r="E252" s="2"/>
+      <c r="F252" s="2"/>
+      <c r="G252" s="13"/>
+      <c r="H252" s="24"/>
+      <c r="I252" s="24"/>
+      <c r="J252" s="13"/>
+      <c r="K252" s="13"/>
+      <c r="L252" s="13"/>
+      <c r="M252" s="24"/>
+      <c r="N252" s="13"/>
+      <c r="O252" s="10"/>
+      <c r="P252" s="10"/>
+      <c r="Q252" s="10"/>
+      <c r="R252" s="10"/>
+      <c r="S252" s="10"/>
+      <c r="T252" s="10"/>
+      <c r="U252" s="10"/>
+      <c r="V252" s="6"/>
+    </row>
+    <row r="253" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A253" s="13"/>
+      <c r="B253" s="10"/>
+      <c r="C253" s="12"/>
+      <c r="D253" s="2"/>
+      <c r="E253" s="2"/>
+      <c r="F253" s="2"/>
+      <c r="G253" s="13"/>
+      <c r="H253" s="24"/>
+      <c r="I253" s="24"/>
+      <c r="J253" s="13"/>
+      <c r="K253" s="13"/>
+      <c r="L253" s="13"/>
+      <c r="M253" s="24"/>
+      <c r="N253" s="13"/>
+      <c r="O253" s="10"/>
+      <c r="P253" s="10"/>
+      <c r="Q253" s="10"/>
+      <c r="R253" s="10"/>
+      <c r="S253" s="10"/>
+      <c r="T253" s="10"/>
+      <c r="U253" s="10"/>
+      <c r="V253" s="6"/>
+    </row>
+    <row r="254" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A254" s="13"/>
+      <c r="B254" s="10"/>
+      <c r="C254" s="12"/>
+      <c r="D254" s="2"/>
+      <c r="E254" s="2"/>
+      <c r="F254" s="2"/>
+      <c r="G254" s="13"/>
+      <c r="H254" s="24"/>
+      <c r="I254" s="24"/>
+      <c r="J254" s="13"/>
+      <c r="K254" s="13"/>
+      <c r="L254" s="13"/>
+      <c r="M254" s="24"/>
+      <c r="N254" s="13"/>
+      <c r="O254" s="10"/>
+      <c r="P254" s="10"/>
+      <c r="Q254" s="10"/>
+      <c r="R254" s="10"/>
+      <c r="S254" s="10"/>
+      <c r="T254" s="10"/>
+      <c r="U254" s="10"/>
+      <c r="V254" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30613"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4220" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2E1C4631-164C-4A43-8BD4-03151C405F81}"/>
+  <xr:revisionPtr revIDLastSave="4244" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C43EDE8A-B74A-4D47-BC10-02FE8F00520B}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1432" uniqueCount="577">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="581">
   <si>
     <t>Date</t>
   </si>
@@ -1778,13 +1778,25 @@
     <t>1515.96 ms</t>
   </si>
   <si>
-    <t>qwen2.5-coder:1.5b</t>
-  </si>
-  <si>
-    <t xml:space="preserve">986 MB </t>
-  </si>
-  <si>
-    <t>497.10 ms</t>
+    <t>smollm:1.7b</t>
+  </si>
+  <si>
+    <t>1GB</t>
+  </si>
+  <si>
+    <t>1562.33 ms</t>
+  </si>
+  <si>
+    <t>hf.co/dengcao/ERNIE-4.5-0.3B-PT-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>0.3B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">240MB </t>
+  </si>
+  <si>
+    <t>340.65 ms</t>
   </si>
 </sst>
 </file>
@@ -15114,7 +15126,7 @@
         <v>574</v>
       </c>
       <c r="D241" s="2" t="s">
-        <v>34</v>
+        <v>67</v>
       </c>
       <c r="E241" s="2" t="s">
         <v>575</v>
@@ -15131,37 +15143,50 @@
       <c r="M241" s="24"/>
       <c r="N241" s="23"/>
       <c r="O241">
-        <v>0.63700000000000001</v>
+        <v>0.60399999999999998</v>
       </c>
       <c r="P241">
-        <v>0.65200000000000002</v>
+        <v>0.55100000000000005</v>
       </c>
       <c r="Q241" t="s">
         <v>576</v>
       </c>
       <c r="R241">
-        <v>0.72199999999999998</v>
+        <v>0.64100000000000001</v>
       </c>
       <c r="S241">
-        <v>0.54</v>
+        <v>0.57799999999999996</v>
       </c>
       <c r="T241">
         <v>1</v>
       </c>
       <c r="U241">
-        <v>0.83799999999999997</v>
+        <v>0.88100000000000001</v>
       </c>
       <c r="V241">
-        <v>0.60599999999999998</v>
+        <v>0.56899999999999995</v>
       </c>
     </row>
     <row r="242" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A242" s="13"/>
-      <c r="B242" s="10"/>
-      <c r="D242" s="2"/>
-      <c r="E242" s="2"/>
-      <c r="F242" s="2"/>
-      <c r="G242" s="13"/>
+      <c r="A242" s="13">
+        <v>46322</v>
+      </c>
+      <c r="B242" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C242" t="s">
+        <v>577</v>
+      </c>
+      <c r="D242" s="2" t="s">
+        <v>578</v>
+      </c>
+      <c r="E242" s="2" t="s">
+        <v>579</v>
+      </c>
+      <c r="F242" t="s">
+        <v>69</v>
+      </c>
+      <c r="G242" s="23"/>
       <c r="H242" s="24"/>
       <c r="I242" s="24"/>
       <c r="J242" s="13"/>
@@ -15169,14 +15194,30 @@
       <c r="L242" s="13"/>
       <c r="M242" s="24"/>
       <c r="N242" s="13"/>
-      <c r="O242" s="10"/>
-      <c r="P242" s="10"/>
-      <c r="Q242" s="10"/>
-      <c r="R242" s="10"/>
-      <c r="S242" s="10"/>
-      <c r="T242" s="10"/>
-      <c r="U242" s="10"/>
-      <c r="V242" s="6"/>
+      <c r="O242">
+        <v>0.26800000000000002</v>
+      </c>
+      <c r="P242">
+        <v>0.32</v>
+      </c>
+      <c r="Q242" t="s">
+        <v>580</v>
+      </c>
+      <c r="R242">
+        <v>0.436</v>
+      </c>
+      <c r="S242">
+        <v>0.65500000000000003</v>
+      </c>
+      <c r="T242">
+        <v>1</v>
+      </c>
+      <c r="U242">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="V242">
+        <v>0.41699999999999998</v>
+      </c>
     </row>
     <row r="243" spans="1:22" ht="15.75" customHeight="1">
       <c r="A243" s="13"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30621"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4244" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C43EDE8A-B74A-4D47-BC10-02FE8F00520B}"/>
+  <xr:revisionPtr revIDLastSave="4258" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C02618C9-4EC3-426C-B10F-4D42C33DC25B}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1438" uniqueCount="581">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="584">
   <si>
     <t>Date</t>
   </si>
@@ -1472,7 +1472,7 @@
     <t>678.99 ms</t>
   </si>
   <si>
-    <t xml:space="preserve"> gemma4:e2b</t>
+    <t>gemma4:e2b</t>
   </si>
   <si>
     <t>2B</t>
@@ -1484,7 +1484,7 @@
     <t>5721.52 ms</t>
   </si>
   <si>
-    <t xml:space="preserve"> deepcoder:1.5b</t>
+    <t>deepcoder:1.5b</t>
   </si>
   <si>
     <t>1.5B</t>
@@ -1748,7 +1748,7 @@
     <t>6113.64 ms</t>
   </si>
   <si>
-    <t xml:space="preserve"> gemma2:2b</t>
+    <t>gemma2:2b</t>
   </si>
   <si>
     <t>2.2b</t>
@@ -1797,6 +1797,15 @@
   </si>
   <si>
     <t>340.65 ms</t>
+  </si>
+  <si>
+    <t>blueishai/anant-base:q4</t>
+  </si>
+  <si>
+    <t>1.12 GB</t>
+  </si>
+  <si>
+    <t>970.50 ms</t>
   </si>
 </sst>
 </file>
@@ -15220,11 +15229,21 @@
       </c>
     </row>
     <row r="243" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A243" s="13"/>
-      <c r="B243" s="10"/>
-      <c r="C243" s="12"/>
-      <c r="D243" s="2"/>
-      <c r="E243" s="2"/>
+      <c r="A243" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B243" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C243" t="s">
+        <v>581</v>
+      </c>
+      <c r="D243" s="2" t="s">
+        <v>91</v>
+      </c>
+      <c r="E243" s="2" t="s">
+        <v>582</v>
+      </c>
       <c r="F243" s="2"/>
       <c r="G243" s="13"/>
       <c r="H243" s="24"/>
@@ -15233,15 +15252,31 @@
       <c r="K243" s="13"/>
       <c r="L243" s="13"/>
       <c r="M243" s="24"/>
-      <c r="N243" s="13"/>
-      <c r="O243" s="10"/>
-      <c r="P243" s="10"/>
-      <c r="Q243" s="10"/>
-      <c r="R243" s="10"/>
-      <c r="S243" s="10"/>
-      <c r="T243" s="10"/>
-      <c r="U243" s="10"/>
-      <c r="V243" s="6"/>
+      <c r="N243" s="23"/>
+      <c r="O243">
+        <v>0.89700000000000002</v>
+      </c>
+      <c r="P243">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="Q243" t="s">
+        <v>583</v>
+      </c>
+      <c r="R243">
+        <v>0.66500000000000004</v>
+      </c>
+      <c r="S243">
+        <v>0.49099999999999999</v>
+      </c>
+      <c r="T243">
+        <v>1</v>
+      </c>
+      <c r="U243">
+        <v>0.876</v>
+      </c>
+      <c r="V243">
+        <v>0.67200000000000004</v>
+      </c>
     </row>
     <row r="244" spans="1:22" ht="15.75" customHeight="1">
       <c r="A244" s="13"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4258" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C02618C9-4EC3-426C-B10F-4D42C33DC25B}"/>
+  <xr:revisionPtr revIDLastSave="4341" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DD2B8081-45FD-4D9B-8799-7E8447855B26}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1503" uniqueCount="611">
   <si>
     <t>Date</t>
   </si>
@@ -1806,6 +1806,87 @@
   </si>
   <si>
     <t>970.50 ms</t>
+  </si>
+  <si>
+    <t>hf.co/second-state/Bielik-1.5B-v3.0-Instruct-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>0.97 GB</t>
+  </si>
+  <si>
+    <t>5726.83 ms</t>
+  </si>
+  <si>
+    <t>hf.co/LiquidAI/LFM2-700M-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>700M</t>
+  </si>
+  <si>
+    <t>972 MB</t>
+  </si>
+  <si>
+    <t>1982.12 ms</t>
+  </si>
+  <si>
+    <t>SmolLM3-3B-GGUF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.9 GB</t>
+  </si>
+  <si>
+    <t>6406.44 ms</t>
+  </si>
+  <si>
+    <t>hf.co/openbmb/MiniCPM5-2B-GGUF:latest</t>
+  </si>
+  <si>
+    <t>6045.34 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> granite4:350m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350m </t>
+  </si>
+  <si>
+    <t>788.10 ms</t>
+  </si>
+  <si>
+    <t>5034.79 ms</t>
+  </si>
+  <si>
+    <t>Llama 3.2 1B</t>
+  </si>
+  <si>
+    <t>3592.43 ms</t>
+  </si>
+  <si>
+    <t>Falcon3-3B-Instruct</t>
+  </si>
+  <si>
+    <t>2gb</t>
+  </si>
+  <si>
+    <t>1289.53 ms</t>
+  </si>
+  <si>
+    <t>phi3:mini</t>
+  </si>
+  <si>
+    <t>MICROSOFT</t>
+  </si>
+  <si>
+    <t>4697.72 ms</t>
+  </si>
+  <si>
+    <t>granite3.3:2b</t>
+  </si>
+  <si>
+    <t>1.5GB</t>
   </si>
 </sst>
 </file>
@@ -2726,7 +2807,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V254"/>
+  <dimension ref="A1:V259"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -15244,7 +15325,9 @@
       <c r="E243" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="F243" s="2"/>
+      <c r="F243" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G243" s="13"/>
       <c r="H243" s="24"/>
       <c r="I243" s="24"/>
@@ -15279,13 +15362,25 @@
       </c>
     </row>
     <row r="244" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A244" s="13"/>
-      <c r="B244" s="10"/>
-      <c r="C244" s="12"/>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="13"/>
+      <c r="A244" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C244" t="s">
+        <v>584</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G244" s="23"/>
       <c r="H244" s="24"/>
       <c r="I244" s="24"/>
       <c r="J244" s="13"/>
@@ -15293,22 +15388,50 @@
       <c r="L244" s="13"/>
       <c r="M244" s="24"/>
       <c r="N244" s="13"/>
-      <c r="O244" s="10"/>
-      <c r="P244" s="10"/>
-      <c r="Q244" s="10"/>
-      <c r="R244" s="10"/>
-      <c r="S244" s="10"/>
-      <c r="T244" s="10"/>
-      <c r="U244" s="10"/>
-      <c r="V244" s="6"/>
+      <c r="O244">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="P244">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>586</v>
+      </c>
+      <c r="R244">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="S244">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="T244">
+        <v>0.97</v>
+      </c>
+      <c r="U244">
+        <v>0.752</v>
+      </c>
+      <c r="V244">
+        <v>0.503</v>
+      </c>
     </row>
     <row r="245" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A245" s="13"/>
-      <c r="B245" s="10"/>
-      <c r="C245" s="12"/>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
-      <c r="F245" s="2"/>
+      <c r="A245" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B245" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G245" s="13"/>
       <c r="H245" s="24"/>
       <c r="I245" s="24"/>
@@ -15317,22 +15440,50 @@
       <c r="L245" s="13"/>
       <c r="M245" s="24"/>
       <c r="N245" s="13"/>
-      <c r="O245" s="10"/>
-      <c r="P245" s="10"/>
-      <c r="Q245" s="10"/>
-      <c r="R245" s="10"/>
-      <c r="S245" s="10"/>
-      <c r="T245" s="10"/>
-      <c r="U245" s="10"/>
-      <c r="V245" s="6"/>
+      <c r="O245">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="P245">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>590</v>
+      </c>
+      <c r="R245">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="S245">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="T245">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="U245">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="V245">
+        <v>0.60399999999999998</v>
+      </c>
     </row>
     <row r="246" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A246" s="13"/>
-      <c r="B246" s="10"/>
-      <c r="C246" s="12"/>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
+      <c r="A246" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G246" s="13"/>
       <c r="H246" s="24"/>
       <c r="I246" s="24"/>
@@ -15340,23 +15491,51 @@
       <c r="K246" s="13"/>
       <c r="L246" s="13"/>
       <c r="M246" s="24"/>
-      <c r="N246" s="13"/>
-      <c r="O246" s="10"/>
-      <c r="P246" s="10"/>
-      <c r="Q246" s="10"/>
-      <c r="R246" s="10"/>
-      <c r="S246" s="10"/>
-      <c r="T246" s="10"/>
-      <c r="U246" s="10"/>
-      <c r="V246" s="6"/>
+      <c r="N246" s="23"/>
+      <c r="O246">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="P246">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>594</v>
+      </c>
+      <c r="R246">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="S246">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="T246">
+        <v>1</v>
+      </c>
+      <c r="U246">
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="V246">
+        <v>0.60199999999999998</v>
+      </c>
     </row>
     <row r="247" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A247" s="13"/>
-      <c r="B247" s="10"/>
-      <c r="C247" s="12"/>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
-      <c r="F247" s="2"/>
+      <c r="A247" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B247" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C247" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="G247" s="13"/>
       <c r="H247" s="24"/>
       <c r="I247" s="24"/>
@@ -15364,23 +15543,51 @@
       <c r="K247" s="13"/>
       <c r="L247" s="13"/>
       <c r="M247" s="24"/>
-      <c r="N247" s="13"/>
-      <c r="O247" s="10"/>
-      <c r="P247" s="10"/>
-      <c r="Q247" s="10"/>
-      <c r="R247" s="10"/>
-      <c r="S247" s="10"/>
-      <c r="T247" s="10"/>
-      <c r="U247" s="10"/>
-      <c r="V247" s="6"/>
+      <c r="N247" s="23"/>
+      <c r="O247">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="P247">
+        <v>0.64</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>596</v>
+      </c>
+      <c r="R247">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="S247">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="T247">
+        <v>1</v>
+      </c>
+      <c r="U247">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="V247">
+        <v>0.59899999999999998</v>
+      </c>
     </row>
     <row r="248" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A248" s="13"/>
-      <c r="B248" s="10"/>
-      <c r="C248" s="12"/>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
+      <c r="A248" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C248" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G248" s="13"/>
       <c r="H248" s="24"/>
       <c r="I248" s="24"/>
@@ -15388,23 +15595,51 @@
       <c r="K248" s="13"/>
       <c r="L248" s="13"/>
       <c r="M248" s="24"/>
-      <c r="N248" s="13"/>
-      <c r="O248" s="10"/>
-      <c r="P248" s="10"/>
-      <c r="Q248" s="10"/>
-      <c r="R248" s="10"/>
-      <c r="S248" s="10"/>
-      <c r="T248" s="10"/>
-      <c r="U248" s="10"/>
-      <c r="V248" s="6"/>
+      <c r="N248" s="23"/>
+      <c r="O248">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="P248">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>599</v>
+      </c>
+      <c r="R248">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="S248">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="T248">
+        <v>1</v>
+      </c>
+      <c r="U248">
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="V248">
+        <v>0.61099999999999999</v>
+      </c>
     </row>
     <row r="249" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A249" s="13"/>
-      <c r="B249" s="10"/>
-      <c r="C249" s="12"/>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
+      <c r="A249" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B249" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C249" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G249" s="13"/>
       <c r="H249" s="24"/>
       <c r="I249" s="24"/>
@@ -15412,23 +15647,51 @@
       <c r="K249" s="13"/>
       <c r="L249" s="13"/>
       <c r="M249" s="24"/>
-      <c r="N249" s="13"/>
-      <c r="O249" s="10"/>
-      <c r="P249" s="10"/>
-      <c r="Q249" s="10"/>
-      <c r="R249" s="10"/>
-      <c r="S249" s="10"/>
-      <c r="T249" s="10"/>
-      <c r="U249" s="10"/>
-      <c r="V249" s="6"/>
+      <c r="N249" s="23"/>
+      <c r="O249">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="P249">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>600</v>
+      </c>
+      <c r="R249">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="S249">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="T249">
+        <v>1</v>
+      </c>
+      <c r="U249">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="V249">
+        <v>0.61899999999999999</v>
+      </c>
     </row>
     <row r="250" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A250" s="13"/>
-      <c r="B250" s="10"/>
-      <c r="C250" s="12"/>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
-      <c r="F250" s="2"/>
+      <c r="A250" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C250" t="s">
+        <v>601</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G250" s="13"/>
       <c r="H250" s="24"/>
       <c r="I250" s="24"/>
@@ -15436,23 +15699,51 @@
       <c r="K250" s="13"/>
       <c r="L250" s="13"/>
       <c r="M250" s="24"/>
-      <c r="N250" s="13"/>
-      <c r="O250" s="10"/>
-      <c r="P250" s="10"/>
-      <c r="Q250" s="10"/>
-      <c r="R250" s="10"/>
-      <c r="S250" s="10"/>
-      <c r="T250" s="10"/>
-      <c r="U250" s="10"/>
-      <c r="V250" s="6"/>
+      <c r="N250" s="23"/>
+      <c r="O250">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="P250">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>602</v>
+      </c>
+      <c r="R250">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="S250">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="T250">
+        <v>1</v>
+      </c>
+      <c r="U250">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="V250">
+        <v>0.58899999999999997</v>
+      </c>
     </row>
     <row r="251" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A251" s="13"/>
-      <c r="B251" s="10"/>
-      <c r="C251" s="12"/>
-      <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
-      <c r="F251" s="2"/>
+      <c r="A251" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B251" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C251" t="s">
+        <v>603</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E251" t="s">
+        <v>604</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G251" s="13"/>
       <c r="H251" s="24"/>
       <c r="I251" s="24"/>
@@ -15460,23 +15751,51 @@
       <c r="K251" s="13"/>
       <c r="L251" s="13"/>
       <c r="M251" s="24"/>
-      <c r="N251" s="13"/>
-      <c r="O251" s="10"/>
-      <c r="P251" s="10"/>
-      <c r="Q251" s="10"/>
-      <c r="R251" s="10"/>
-      <c r="S251" s="10"/>
-      <c r="T251" s="10"/>
-      <c r="U251" s="10"/>
-      <c r="V251" s="6"/>
+      <c r="N251" s="23"/>
+      <c r="O251">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="P251">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>605</v>
+      </c>
+      <c r="R251">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="S251">
+        <v>0.6</v>
+      </c>
+      <c r="T251">
+        <v>1</v>
+      </c>
+      <c r="U251">
+        <v>0.03</v>
+      </c>
+      <c r="V251">
+        <v>0.255</v>
+      </c>
     </row>
     <row r="252" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A252" s="13"/>
-      <c r="B252" s="10"/>
-      <c r="C252" s="12"/>
-      <c r="D252" s="2"/>
-      <c r="E252" s="2"/>
-      <c r="F252" s="2"/>
+      <c r="A252" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C252" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="D252" t="s">
+        <v>464</v>
+      </c>
+      <c r="E252" t="s">
+        <v>49</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>607</v>
+      </c>
       <c r="G252" s="13"/>
       <c r="H252" s="24"/>
       <c r="I252" s="24"/>
@@ -15484,23 +15803,49 @@
       <c r="K252" s="13"/>
       <c r="L252" s="13"/>
       <c r="M252" s="24"/>
-      <c r="N252" s="13"/>
-      <c r="O252" s="10"/>
-      <c r="P252" s="10"/>
-      <c r="Q252" s="10"/>
-      <c r="R252" s="10"/>
-      <c r="S252" s="10"/>
-      <c r="T252" s="10"/>
-      <c r="U252" s="10"/>
-      <c r="V252" s="6"/>
+      <c r="N252" s="23"/>
+      <c r="O252">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="P252">
+        <v>0.66200000000000003</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>608</v>
+      </c>
+      <c r="R252">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="S252">
+        <v>0.54</v>
+      </c>
+      <c r="T252">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="U252">
+        <v>0.81699999999999995</v>
+      </c>
+      <c r="V252">
+        <v>0.61199999999999999</v>
+      </c>
     </row>
     <row r="253" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A253" s="13"/>
-      <c r="B253" s="10"/>
-      <c r="C253" s="12"/>
+      <c r="A253" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C253" s="12" t="s">
+        <v>609</v>
+      </c>
       <c r="D253" s="2"/>
-      <c r="E253" s="2"/>
-      <c r="F253" s="2"/>
+      <c r="E253" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G253" s="13"/>
       <c r="H253" s="24"/>
       <c r="I253" s="24"/>
@@ -15508,7 +15853,7 @@
       <c r="K253" s="13"/>
       <c r="L253" s="13"/>
       <c r="M253" s="24"/>
-      <c r="N253" s="13"/>
+      <c r="N253" s="23"/>
       <c r="O253" s="10"/>
       <c r="P253" s="10"/>
       <c r="Q253" s="10"/>
@@ -15542,6 +15887,126 @@
       <c r="U254" s="10"/>
       <c r="V254" s="6"/>
     </row>
+    <row r="255" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A255" s="13"/>
+      <c r="B255" s="10"/>
+      <c r="C255" s="12"/>
+      <c r="D255" s="2"/>
+      <c r="E255" s="2"/>
+      <c r="F255" s="2"/>
+      <c r="G255" s="13"/>
+      <c r="H255" s="24"/>
+      <c r="I255" s="24"/>
+      <c r="J255" s="13"/>
+      <c r="K255" s="13"/>
+      <c r="L255" s="13"/>
+      <c r="M255" s="24"/>
+      <c r="N255" s="13"/>
+      <c r="O255" s="10"/>
+      <c r="P255" s="10"/>
+      <c r="Q255" s="10"/>
+      <c r="R255" s="10"/>
+      <c r="S255" s="10"/>
+      <c r="T255" s="10"/>
+      <c r="U255" s="10"/>
+      <c r="V255" s="6"/>
+    </row>
+    <row r="256" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A256" s="13"/>
+      <c r="B256" s="10"/>
+      <c r="C256" s="12"/>
+      <c r="D256" s="2"/>
+      <c r="E256" s="2"/>
+      <c r="F256" s="2"/>
+      <c r="G256" s="13"/>
+      <c r="H256" s="24"/>
+      <c r="I256" s="24"/>
+      <c r="J256" s="13"/>
+      <c r="K256" s="13"/>
+      <c r="L256" s="13"/>
+      <c r="M256" s="24"/>
+      <c r="N256" s="13"/>
+      <c r="O256" s="10"/>
+      <c r="P256" s="10"/>
+      <c r="Q256" s="10"/>
+      <c r="R256" s="10"/>
+      <c r="S256" s="10"/>
+      <c r="T256" s="10"/>
+      <c r="U256" s="10"/>
+      <c r="V256" s="6"/>
+    </row>
+    <row r="257" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A257" s="13"/>
+      <c r="B257" s="10"/>
+      <c r="C257" s="12"/>
+      <c r="D257" s="2"/>
+      <c r="E257" s="2"/>
+      <c r="F257" s="2"/>
+      <c r="G257" s="13"/>
+      <c r="H257" s="24"/>
+      <c r="I257" s="24"/>
+      <c r="J257" s="13"/>
+      <c r="K257" s="13"/>
+      <c r="L257" s="13"/>
+      <c r="M257" s="24"/>
+      <c r="N257" s="13"/>
+      <c r="O257" s="10"/>
+      <c r="P257" s="10"/>
+      <c r="Q257" s="10"/>
+      <c r="R257" s="10"/>
+      <c r="S257" s="10"/>
+      <c r="T257" s="10"/>
+      <c r="U257" s="10"/>
+      <c r="V257" s="6"/>
+    </row>
+    <row r="258" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A258" s="13"/>
+      <c r="B258" s="10"/>
+      <c r="C258" s="12"/>
+      <c r="D258" s="2"/>
+      <c r="E258" s="2"/>
+      <c r="F258" s="2"/>
+      <c r="G258" s="13"/>
+      <c r="H258" s="24"/>
+      <c r="I258" s="24"/>
+      <c r="J258" s="13"/>
+      <c r="K258" s="13"/>
+      <c r="L258" s="13"/>
+      <c r="M258" s="24"/>
+      <c r="N258" s="13"/>
+      <c r="O258" s="10"/>
+      <c r="P258" s="10"/>
+      <c r="Q258" s="10"/>
+      <c r="R258" s="10"/>
+      <c r="S258" s="10"/>
+      <c r="T258" s="10"/>
+      <c r="U258" s="10"/>
+      <c r="V258" s="6"/>
+    </row>
+    <row r="259" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A259" s="13"/>
+      <c r="B259" s="10"/>
+      <c r="C259" s="12"/>
+      <c r="D259" s="2"/>
+      <c r="E259" s="2"/>
+      <c r="F259" s="2"/>
+      <c r="G259" s="13"/>
+      <c r="H259" s="24"/>
+      <c r="I259" s="24"/>
+      <c r="J259" s="13"/>
+      <c r="K259" s="13"/>
+      <c r="L259" s="13"/>
+      <c r="M259" s="24"/>
+      <c r="N259" s="13"/>
+      <c r="O259" s="10"/>
+      <c r="P259" s="10"/>
+      <c r="Q259" s="10"/>
+      <c r="R259" s="10"/>
+      <c r="S259" s="10"/>
+      <c r="T259" s="10"/>
+      <c r="U259" s="10"/>
+      <c r="V259" s="6"/>
+    </row>
   </sheetData>
   <mergeCells count="7">
     <mergeCell ref="A2:A4"/>

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4258" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C02618C9-4EC3-426C-B10F-4D42C33DC25B}"/>
+  <xr:revisionPtr revIDLastSave="4393" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E66A95E2-7844-4863-8408-10DE7D112023}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1443" uniqueCount="584">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="629">
   <si>
     <t>Date</t>
   </si>
@@ -1806,6 +1806,141 @@
   </si>
   <si>
     <t>970.50 ms</t>
+  </si>
+  <si>
+    <t>hf.co/second-state/Bielik-1.5B-v3.0-Instruct-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>0.97 GB</t>
+  </si>
+  <si>
+    <t>5726.83 ms</t>
+  </si>
+  <si>
+    <t>hf.co/LiquidAI/LFM2-700M-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>700M</t>
+  </si>
+  <si>
+    <t>972 MB</t>
+  </si>
+  <si>
+    <t>1982.12 ms</t>
+  </si>
+  <si>
+    <t>SmolLM3-3B-GGUF</t>
+  </si>
+  <si>
+    <t xml:space="preserve">3B </t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.9 GB</t>
+  </si>
+  <si>
+    <t>6406.44 ms</t>
+  </si>
+  <si>
+    <t>hf.co/openbmb/MiniCPM5-2B-GGUF:latest</t>
+  </si>
+  <si>
+    <t>6045.34 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> granite4:350m</t>
+  </si>
+  <si>
+    <t xml:space="preserve">350m </t>
+  </si>
+  <si>
+    <t>788.10 ms</t>
+  </si>
+  <si>
+    <t>5034.79 ms</t>
+  </si>
+  <si>
+    <t>Llama 3.2 1B</t>
+  </si>
+  <si>
+    <t>3592.43 ms</t>
+  </si>
+  <si>
+    <t>Falcon3-3B-Instruct</t>
+  </si>
+  <si>
+    <t>2gb</t>
+  </si>
+  <si>
+    <t>1289.53 ms</t>
+  </si>
+  <si>
+    <t>phi3:mini</t>
+  </si>
+  <si>
+    <t>MICROSOFT</t>
+  </si>
+  <si>
+    <t>4697.72 ms</t>
+  </si>
+  <si>
+    <t>granite3.3:2b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2bb </t>
+  </si>
+  <si>
+    <t>1.5GB</t>
+  </si>
+  <si>
+    <t>5131.50 ms</t>
+  </si>
+  <si>
+    <t>codegemma:2b</t>
+  </si>
+  <si>
+    <t>6207.82 ms</t>
+  </si>
+  <si>
+    <t>sailor2:1b</t>
+  </si>
+  <si>
+    <t xml:space="preserve">738MB </t>
+  </si>
+  <si>
+    <t>Sea AI Lab</t>
+  </si>
+  <si>
+    <t>7566.49 ms</t>
+  </si>
+  <si>
+    <t>reader-lm:1.5b</t>
+  </si>
+  <si>
+    <t>836.89 ms</t>
+  </si>
+  <si>
+    <t>wizardlm2</t>
+  </si>
+  <si>
+    <t>4.7 GB</t>
+  </si>
+  <si>
+    <t>WizardLM community</t>
+  </si>
+  <si>
+    <t>25546.33 ms</t>
+  </si>
+  <si>
+    <t>WizardLM-2 7B</t>
+  </si>
+  <si>
+    <t>2.7B</t>
+  </si>
+  <si>
+    <t>4.1B</t>
+  </si>
+  <si>
+    <t>3878.85 ms</t>
   </si>
 </sst>
 </file>
@@ -2726,7 +2861,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V254"/>
+  <dimension ref="A1:V263"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -15244,7 +15379,9 @@
       <c r="E243" s="2" t="s">
         <v>582</v>
       </c>
-      <c r="F243" s="2"/>
+      <c r="F243" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G243" s="13"/>
       <c r="H243" s="24"/>
       <c r="I243" s="24"/>
@@ -15279,13 +15416,25 @@
       </c>
     </row>
     <row r="244" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A244" s="13"/>
-      <c r="B244" s="10"/>
-      <c r="C244" s="12"/>
-      <c r="D244" s="2"/>
-      <c r="E244" s="2"/>
-      <c r="F244" s="2"/>
-      <c r="G244" s="13"/>
+      <c r="A244" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B244" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C244" t="s">
+        <v>584</v>
+      </c>
+      <c r="D244" s="2" t="s">
+        <v>86</v>
+      </c>
+      <c r="E244" s="2" t="s">
+        <v>585</v>
+      </c>
+      <c r="F244" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G244" s="23"/>
       <c r="H244" s="24"/>
       <c r="I244" s="24"/>
       <c r="J244" s="13"/>
@@ -15293,22 +15442,50 @@
       <c r="L244" s="13"/>
       <c r="M244" s="24"/>
       <c r="N244" s="13"/>
-      <c r="O244" s="10"/>
-      <c r="P244" s="10"/>
-      <c r="Q244" s="10"/>
-      <c r="R244" s="10"/>
-      <c r="S244" s="10"/>
-      <c r="T244" s="10"/>
-      <c r="U244" s="10"/>
-      <c r="V244" s="6"/>
+      <c r="O244">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="P244">
+        <v>0.47699999999999998</v>
+      </c>
+      <c r="Q244" t="s">
+        <v>586</v>
+      </c>
+      <c r="R244">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="S244">
+        <v>0.60399999999999998</v>
+      </c>
+      <c r="T244">
+        <v>0.97</v>
+      </c>
+      <c r="U244">
+        <v>0.752</v>
+      </c>
+      <c r="V244">
+        <v>0.503</v>
+      </c>
     </row>
     <row r="245" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A245" s="13"/>
-      <c r="B245" s="10"/>
-      <c r="C245" s="12"/>
-      <c r="D245" s="2"/>
-      <c r="E245" s="2"/>
-      <c r="F245" s="2"/>
+      <c r="A245" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B245" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C245" s="12" t="s">
+        <v>587</v>
+      </c>
+      <c r="D245" s="2" t="s">
+        <v>588</v>
+      </c>
+      <c r="E245" s="2" t="s">
+        <v>589</v>
+      </c>
+      <c r="F245" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G245" s="13"/>
       <c r="H245" s="24"/>
       <c r="I245" s="24"/>
@@ -15317,22 +15494,50 @@
       <c r="L245" s="13"/>
       <c r="M245" s="24"/>
       <c r="N245" s="13"/>
-      <c r="O245" s="10"/>
-      <c r="P245" s="10"/>
-      <c r="Q245" s="10"/>
-      <c r="R245" s="10"/>
-      <c r="S245" s="10"/>
-      <c r="T245" s="10"/>
-      <c r="U245" s="10"/>
-      <c r="V245" s="6"/>
+      <c r="O245">
+        <v>0.75900000000000001</v>
+      </c>
+      <c r="P245">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="Q245" t="s">
+        <v>590</v>
+      </c>
+      <c r="R245">
+        <v>0.67700000000000005</v>
+      </c>
+      <c r="S245">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="T245">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="U245">
+        <v>0.86499999999999999</v>
+      </c>
+      <c r="V245">
+        <v>0.60399999999999998</v>
+      </c>
     </row>
     <row r="246" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A246" s="13"/>
-      <c r="B246" s="10"/>
-      <c r="C246" s="12"/>
-      <c r="D246" s="2"/>
-      <c r="E246" s="2"/>
-      <c r="F246" s="2"/>
+      <c r="A246" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B246" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C246" s="12" t="s">
+        <v>591</v>
+      </c>
+      <c r="D246" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E246" s="2" t="s">
+        <v>593</v>
+      </c>
+      <c r="F246" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G246" s="13"/>
       <c r="H246" s="24"/>
       <c r="I246" s="24"/>
@@ -15340,23 +15545,51 @@
       <c r="K246" s="13"/>
       <c r="L246" s="13"/>
       <c r="M246" s="24"/>
-      <c r="N246" s="13"/>
-      <c r="O246" s="10"/>
-      <c r="P246" s="10"/>
-      <c r="Q246" s="10"/>
-      <c r="R246" s="10"/>
-      <c r="S246" s="10"/>
-      <c r="T246" s="10"/>
-      <c r="U246" s="10"/>
-      <c r="V246" s="6"/>
+      <c r="N246" s="23"/>
+      <c r="O246">
+        <v>0.76700000000000002</v>
+      </c>
+      <c r="P246">
+        <v>0.59699999999999998</v>
+      </c>
+      <c r="Q246" t="s">
+        <v>594</v>
+      </c>
+      <c r="R246">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="S246">
+        <v>0.56100000000000005</v>
+      </c>
+      <c r="T246">
+        <v>1</v>
+      </c>
+      <c r="U246">
+        <v>0.84399999999999997</v>
+      </c>
+      <c r="V246">
+        <v>0.60199999999999998</v>
+      </c>
     </row>
     <row r="247" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A247" s="13"/>
-      <c r="B247" s="10"/>
-      <c r="C247" s="12"/>
-      <c r="D247" s="2"/>
-      <c r="E247" s="2"/>
-      <c r="F247" s="2"/>
+      <c r="A247" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B247" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C247" s="12" t="s">
+        <v>595</v>
+      </c>
+      <c r="D247" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E247" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F247" s="2" t="s">
+        <v>178</v>
+      </c>
       <c r="G247" s="13"/>
       <c r="H247" s="24"/>
       <c r="I247" s="24"/>
@@ -15364,23 +15597,51 @@
       <c r="K247" s="13"/>
       <c r="L247" s="13"/>
       <c r="M247" s="24"/>
-      <c r="N247" s="13"/>
-      <c r="O247" s="10"/>
-      <c r="P247" s="10"/>
-      <c r="Q247" s="10"/>
-      <c r="R247" s="10"/>
-      <c r="S247" s="10"/>
-      <c r="T247" s="10"/>
-      <c r="U247" s="10"/>
-      <c r="V247" s="6"/>
+      <c r="N247" s="23"/>
+      <c r="O247">
+        <v>0.76100000000000001</v>
+      </c>
+      <c r="P247">
+        <v>0.64</v>
+      </c>
+      <c r="Q247" t="s">
+        <v>596</v>
+      </c>
+      <c r="R247">
+        <v>0.71199999999999997</v>
+      </c>
+      <c r="S247">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="T247">
+        <v>1</v>
+      </c>
+      <c r="U247">
+        <v>0.75700000000000001</v>
+      </c>
+      <c r="V247">
+        <v>0.59899999999999998</v>
+      </c>
     </row>
     <row r="248" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A248" s="13"/>
-      <c r="B248" s="10"/>
-      <c r="C248" s="12"/>
-      <c r="D248" s="2"/>
-      <c r="E248" s="2"/>
-      <c r="F248" s="2"/>
+      <c r="A248" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B248" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C248" s="12" t="s">
+        <v>597</v>
+      </c>
+      <c r="D248" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E248" s="2" t="s">
+        <v>127</v>
+      </c>
+      <c r="F248" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G248" s="13"/>
       <c r="H248" s="24"/>
       <c r="I248" s="24"/>
@@ -15388,23 +15649,51 @@
       <c r="K248" s="13"/>
       <c r="L248" s="13"/>
       <c r="M248" s="24"/>
-      <c r="N248" s="13"/>
-      <c r="O248" s="10"/>
-      <c r="P248" s="10"/>
-      <c r="Q248" s="10"/>
-      <c r="R248" s="10"/>
-      <c r="S248" s="10"/>
-      <c r="T248" s="10"/>
-      <c r="U248" s="10"/>
-      <c r="V248" s="6"/>
+      <c r="N248" s="23"/>
+      <c r="O248">
+        <v>0.59399999999999997</v>
+      </c>
+      <c r="P248">
+        <v>0.67800000000000005</v>
+      </c>
+      <c r="Q248" t="s">
+        <v>599</v>
+      </c>
+      <c r="R248">
+        <v>0.74199999999999999</v>
+      </c>
+      <c r="S248">
+        <v>0.53400000000000003</v>
+      </c>
+      <c r="T248">
+        <v>1</v>
+      </c>
+      <c r="U248">
+        <v>0.89900000000000002</v>
+      </c>
+      <c r="V248">
+        <v>0.61099999999999999</v>
+      </c>
     </row>
     <row r="249" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A249" s="13"/>
-      <c r="B249" s="10"/>
-      <c r="C249" s="12"/>
-      <c r="D249" s="2"/>
-      <c r="E249" s="2"/>
-      <c r="F249" s="2"/>
+      <c r="A249" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B249" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C249" s="12" t="s">
+        <v>534</v>
+      </c>
+      <c r="D249" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E249" s="2" t="s">
+        <v>535</v>
+      </c>
+      <c r="F249" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G249" s="13"/>
       <c r="H249" s="24"/>
       <c r="I249" s="24"/>
@@ -15412,23 +15701,51 @@
       <c r="K249" s="13"/>
       <c r="L249" s="13"/>
       <c r="M249" s="24"/>
-      <c r="N249" s="13"/>
-      <c r="O249" s="10"/>
-      <c r="P249" s="10"/>
-      <c r="Q249" s="10"/>
-      <c r="R249" s="10"/>
-      <c r="S249" s="10"/>
-      <c r="T249" s="10"/>
-      <c r="U249" s="10"/>
-      <c r="V249" s="6"/>
+      <c r="N249" s="23"/>
+      <c r="O249">
+        <v>0.76800000000000002</v>
+      </c>
+      <c r="P249">
+        <v>0.64500000000000002</v>
+      </c>
+      <c r="Q249" t="s">
+        <v>600</v>
+      </c>
+      <c r="R249">
+        <v>0.71699999999999997</v>
+      </c>
+      <c r="S249">
+        <v>0.54200000000000004</v>
+      </c>
+      <c r="T249">
+        <v>1</v>
+      </c>
+      <c r="U249">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="V249">
+        <v>0.61899999999999999</v>
+      </c>
     </row>
     <row r="250" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A250" s="13"/>
-      <c r="B250" s="10"/>
-      <c r="C250" s="12"/>
-      <c r="D250" s="2"/>
-      <c r="E250" s="2"/>
-      <c r="F250" s="2"/>
+      <c r="A250" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B250" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C250" t="s">
+        <v>601</v>
+      </c>
+      <c r="D250" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E250" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="F250" s="2" t="s">
+        <v>43</v>
+      </c>
       <c r="G250" s="13"/>
       <c r="H250" s="24"/>
       <c r="I250" s="24"/>
@@ -15436,23 +15753,51 @@
       <c r="K250" s="13"/>
       <c r="L250" s="13"/>
       <c r="M250" s="24"/>
-      <c r="N250" s="13"/>
-      <c r="O250" s="10"/>
-      <c r="P250" s="10"/>
-      <c r="Q250" s="10"/>
-      <c r="R250" s="10"/>
-      <c r="S250" s="10"/>
-      <c r="T250" s="10"/>
-      <c r="U250" s="10"/>
-      <c r="V250" s="6"/>
+      <c r="N250" s="23"/>
+      <c r="O250">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="P250">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="Q250" t="s">
+        <v>602</v>
+      </c>
+      <c r="R250">
+        <v>0.69499999999999995</v>
+      </c>
+      <c r="S250">
+        <v>0.55300000000000005</v>
+      </c>
+      <c r="T250">
+        <v>1</v>
+      </c>
+      <c r="U250">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="V250">
+        <v>0.58899999999999997</v>
+      </c>
     </row>
     <row r="251" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A251" s="13"/>
-      <c r="B251" s="10"/>
-      <c r="C251" s="12"/>
-      <c r="D251" s="2"/>
-      <c r="E251" s="2"/>
-      <c r="F251" s="2"/>
+      <c r="A251" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B251" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C251" t="s">
+        <v>603</v>
+      </c>
+      <c r="D251" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E251" t="s">
+        <v>604</v>
+      </c>
+      <c r="F251" s="2" t="s">
+        <v>142</v>
+      </c>
       <c r="G251" s="13"/>
       <c r="H251" s="24"/>
       <c r="I251" s="24"/>
@@ -15460,23 +15805,51 @@
       <c r="K251" s="13"/>
       <c r="L251" s="13"/>
       <c r="M251" s="24"/>
-      <c r="N251" s="13"/>
-      <c r="O251" s="10"/>
-      <c r="P251" s="10"/>
-      <c r="Q251" s="10"/>
-      <c r="R251" s="10"/>
-      <c r="S251" s="10"/>
-      <c r="T251" s="10"/>
-      <c r="U251" s="10"/>
-      <c r="V251" s="6"/>
+      <c r="N251" s="23"/>
+      <c r="O251">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="P251">
+        <v>9.7000000000000003E-2</v>
+      </c>
+      <c r="Q251" t="s">
+        <v>605</v>
+      </c>
+      <c r="R251">
+        <v>0.11700000000000001</v>
+      </c>
+      <c r="S251">
+        <v>0.6</v>
+      </c>
+      <c r="T251">
+        <v>1</v>
+      </c>
+      <c r="U251">
+        <v>0.03</v>
+      </c>
+      <c r="V251">
+        <v>0.255</v>
+      </c>
     </row>
     <row r="252" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A252" s="13"/>
-      <c r="B252" s="10"/>
-      <c r="C252" s="12"/>
-      <c r="D252" s="2"/>
-      <c r="E252" s="2"/>
-      <c r="F252" s="2"/>
+      <c r="A252" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B252" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C252" s="12" t="s">
+        <v>606</v>
+      </c>
+      <c r="D252" t="s">
+        <v>464</v>
+      </c>
+      <c r="E252" t="s">
+        <v>49</v>
+      </c>
+      <c r="F252" s="2" t="s">
+        <v>607</v>
+      </c>
       <c r="G252" s="13"/>
       <c r="H252" s="24"/>
       <c r="I252" s="24"/>
@@ -15484,23 +15857,51 @@
       <c r="K252" s="13"/>
       <c r="L252" s="13"/>
       <c r="M252" s="24"/>
-      <c r="N252" s="13"/>
-      <c r="O252" s="10"/>
-      <c r="P252" s="10"/>
-      <c r="Q252" s="10"/>
-      <c r="R252" s="10"/>
-      <c r="S252" s="10"/>
-      <c r="T252" s="10"/>
-      <c r="U252" s="10"/>
-      <c r="V252" s="6"/>
+      <c r="N252" s="23"/>
+      <c r="O252">
+        <v>0.77200000000000002</v>
+      </c>
+      <c r="P252">
+        <v>0.66200000000000003</v>
+      </c>
+      <c r="Q252" t="s">
+        <v>608</v>
+      </c>
+      <c r="R252">
+        <v>0.72899999999999998</v>
+      </c>
+      <c r="S252">
+        <v>0.54</v>
+      </c>
+      <c r="T252">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="U252">
+        <v>0.81699999999999995</v>
+      </c>
+      <c r="V252">
+        <v>0.61199999999999999</v>
+      </c>
     </row>
     <row r="253" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A253" s="13"/>
-      <c r="B253" s="10"/>
-      <c r="C253" s="12"/>
-      <c r="D253" s="2"/>
-      <c r="E253" s="2"/>
-      <c r="F253" s="2"/>
+      <c r="A253" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B253" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C253" s="12" t="s">
+        <v>609</v>
+      </c>
+      <c r="D253" s="2" t="s">
+        <v>610</v>
+      </c>
+      <c r="E253" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F253" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G253" s="13"/>
       <c r="H253" s="24"/>
       <c r="I253" s="24"/>
@@ -15508,23 +15909,51 @@
       <c r="K253" s="13"/>
       <c r="L253" s="13"/>
       <c r="M253" s="24"/>
-      <c r="N253" s="13"/>
-      <c r="O253" s="10"/>
-      <c r="P253" s="10"/>
-      <c r="Q253" s="10"/>
-      <c r="R253" s="10"/>
-      <c r="S253" s="10"/>
-      <c r="T253" s="10"/>
-      <c r="U253" s="10"/>
-      <c r="V253" s="6"/>
+      <c r="N253" s="23"/>
+      <c r="O253">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="P253">
+        <v>0.64300000000000002</v>
+      </c>
+      <c r="Q253" t="s">
+        <v>612</v>
+      </c>
+      <c r="R253">
+        <v>0.71399999999999997</v>
+      </c>
+      <c r="S253">
+        <v>0.54600000000000004</v>
+      </c>
+      <c r="T253">
+        <v>1</v>
+      </c>
+      <c r="U253">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="V253">
+        <v>0.60899999999999999</v>
+      </c>
     </row>
     <row r="254" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A254" s="13"/>
-      <c r="B254" s="10"/>
-      <c r="C254" s="12"/>
-      <c r="D254" s="2"/>
-      <c r="E254" s="2"/>
-      <c r="F254" s="2"/>
+      <c r="A254" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B254" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C254" t="s">
+        <v>613</v>
+      </c>
+      <c r="D254" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E254" t="s">
+        <v>116</v>
+      </c>
+      <c r="F254" t="s">
+        <v>74</v>
+      </c>
       <c r="G254" s="13"/>
       <c r="H254" s="24"/>
       <c r="I254" s="24"/>
@@ -15532,15 +15961,359 @@
       <c r="K254" s="13"/>
       <c r="L254" s="13"/>
       <c r="M254" s="24"/>
-      <c r="N254" s="13"/>
-      <c r="O254" s="10"/>
-      <c r="P254" s="10"/>
-      <c r="Q254" s="10"/>
-      <c r="R254" s="10"/>
-      <c r="S254" s="10"/>
-      <c r="T254" s="10"/>
-      <c r="U254" s="10"/>
-      <c r="V254" s="6"/>
+      <c r="N254" s="23"/>
+      <c r="O254">
+        <v>0.33500000000000002</v>
+      </c>
+      <c r="P254">
+        <v>0.35</v>
+      </c>
+      <c r="Q254" t="s">
+        <v>614</v>
+      </c>
+      <c r="R254">
+        <v>0.48</v>
+      </c>
+      <c r="S254">
+        <v>0.629</v>
+      </c>
+      <c r="T254">
+        <v>1</v>
+      </c>
+      <c r="U254">
+        <v>0.371</v>
+      </c>
+      <c r="V254">
+        <v>0.38200000000000001</v>
+      </c>
+    </row>
+    <row r="255" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A255" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B255" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C255" s="12" t="s">
+        <v>615</v>
+      </c>
+      <c r="D255" t="s">
+        <v>409</v>
+      </c>
+      <c r="E255" s="2" t="s">
+        <v>616</v>
+      </c>
+      <c r="F255" t="s">
+        <v>617</v>
+      </c>
+      <c r="G255" s="23"/>
+      <c r="H255" s="24"/>
+      <c r="I255" s="24"/>
+      <c r="J255" s="13"/>
+      <c r="K255" s="13"/>
+      <c r="L255" s="13"/>
+      <c r="M255" s="24"/>
+      <c r="N255" s="24"/>
+      <c r="O255">
+        <v>0.44</v>
+      </c>
+      <c r="P255">
+        <v>0.41799999999999998</v>
+      </c>
+      <c r="Q255" t="s">
+        <v>618</v>
+      </c>
+      <c r="R255">
+        <v>0.51400000000000001</v>
+      </c>
+      <c r="S255">
+        <v>0.628</v>
+      </c>
+      <c r="T255">
+        <v>0.89400000000000002</v>
+      </c>
+      <c r="U255">
+        <v>0.753</v>
+      </c>
+      <c r="V255">
+        <v>0.45300000000000001</v>
+      </c>
+    </row>
+    <row r="256" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A256" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B256" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C256" s="12" t="s">
+        <v>619</v>
+      </c>
+      <c r="D256" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E256" s="2" t="s">
+        <v>611</v>
+      </c>
+      <c r="F256" t="s">
+        <v>69</v>
+      </c>
+      <c r="G256" s="13"/>
+      <c r="H256" s="23"/>
+      <c r="I256" s="24"/>
+      <c r="J256" s="13"/>
+      <c r="K256" s="13"/>
+      <c r="L256" s="13"/>
+      <c r="M256" s="24"/>
+      <c r="N256" s="13"/>
+      <c r="O256">
+        <v>0.19800000000000001</v>
+      </c>
+      <c r="P256">
+        <v>0.20699999999999999</v>
+      </c>
+      <c r="Q256" t="s">
+        <v>620</v>
+      </c>
+      <c r="R256">
+        <v>0.219</v>
+      </c>
+      <c r="S256">
+        <v>0.13200000000000001</v>
+      </c>
+      <c r="T256">
+        <v>0.187</v>
+      </c>
+      <c r="U256">
+        <v>0.224</v>
+      </c>
+      <c r="V256" s="6">
+        <v>0.17599999999999999</v>
+      </c>
+    </row>
+    <row r="257" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A257" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B257" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C257" s="12" t="s">
+        <v>621</v>
+      </c>
+      <c r="D257" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E257" s="2" t="s">
+        <v>622</v>
+      </c>
+      <c r="F257" t="s">
+        <v>623</v>
+      </c>
+      <c r="G257" s="13"/>
+      <c r="H257" s="23"/>
+      <c r="I257" s="24"/>
+      <c r="J257" s="13"/>
+      <c r="K257" s="13"/>
+      <c r="L257" s="13"/>
+      <c r="M257" s="24"/>
+      <c r="N257" s="13"/>
+      <c r="O257">
+        <v>0.85199999999999998</v>
+      </c>
+      <c r="P257">
+        <v>0.48399999999999999</v>
+      </c>
+      <c r="Q257" t="s">
+        <v>624</v>
+      </c>
+      <c r="R257">
+        <v>0.58699999999999997</v>
+      </c>
+      <c r="S257">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="T257">
+        <v>1</v>
+      </c>
+      <c r="U257">
+        <v>0.93</v>
+      </c>
+      <c r="V257">
+        <v>0.59699999999999998</v>
+      </c>
+    </row>
+    <row r="258" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A258" s="13">
+        <v>46323</v>
+      </c>
+      <c r="B258" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C258" s="12" t="s">
+        <v>625</v>
+      </c>
+      <c r="D258" s="2" t="s">
+        <v>626</v>
+      </c>
+      <c r="E258" s="2" t="s">
+        <v>627</v>
+      </c>
+      <c r="F258" t="s">
+        <v>623</v>
+      </c>
+      <c r="G258" s="13"/>
+      <c r="H258" s="24"/>
+      <c r="I258" s="24"/>
+      <c r="J258" s="13"/>
+      <c r="K258" s="23"/>
+      <c r="L258" s="13"/>
+      <c r="M258" s="24"/>
+      <c r="N258" s="13"/>
+      <c r="O258">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="P258">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="Q258" t="s">
+        <v>628</v>
+      </c>
+      <c r="R258">
+        <v>0.68300000000000005</v>
+      </c>
+      <c r="S258">
+        <v>0.55700000000000005</v>
+      </c>
+      <c r="T258">
+        <v>0.80400000000000005</v>
+      </c>
+      <c r="U258">
+        <v>0.85899999999999999</v>
+      </c>
+      <c r="V258">
+        <v>0.57299999999999995</v>
+      </c>
+    </row>
+    <row r="259" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A259" s="13"/>
+      <c r="B259" s="10"/>
+      <c r="C259" s="12"/>
+      <c r="D259" s="2"/>
+      <c r="E259" s="2"/>
+      <c r="F259" s="2"/>
+      <c r="G259" s="13"/>
+      <c r="H259" s="24"/>
+      <c r="I259" s="24"/>
+      <c r="J259" s="13"/>
+      <c r="K259" s="13"/>
+      <c r="L259" s="13"/>
+      <c r="M259" s="24"/>
+      <c r="N259" s="13"/>
+      <c r="O259" s="10"/>
+      <c r="P259" s="10"/>
+      <c r="Q259" s="10"/>
+      <c r="R259" s="10"/>
+      <c r="S259" s="10"/>
+      <c r="T259" s="10"/>
+      <c r="U259" s="10"/>
+      <c r="V259" s="6"/>
+    </row>
+    <row r="260" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A260" s="13"/>
+      <c r="B260" s="10"/>
+      <c r="C260" s="12"/>
+      <c r="D260" s="2"/>
+      <c r="E260" s="2"/>
+      <c r="F260" s="2"/>
+      <c r="G260" s="13"/>
+      <c r="H260" s="24"/>
+      <c r="I260" s="24"/>
+      <c r="J260" s="13"/>
+      <c r="K260" s="13"/>
+      <c r="L260" s="13"/>
+      <c r="M260" s="24"/>
+      <c r="N260" s="13"/>
+      <c r="O260" s="10"/>
+      <c r="P260" s="10"/>
+      <c r="Q260" s="10"/>
+      <c r="R260" s="10"/>
+      <c r="S260" s="10"/>
+      <c r="T260" s="10"/>
+      <c r="U260" s="10"/>
+      <c r="V260" s="6"/>
+    </row>
+    <row r="261" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A261" s="13"/>
+      <c r="B261" s="10"/>
+      <c r="C261" s="12"/>
+      <c r="D261" s="2"/>
+      <c r="E261" s="2"/>
+      <c r="F261" s="2"/>
+      <c r="G261" s="13"/>
+      <c r="H261" s="24"/>
+      <c r="I261" s="24"/>
+      <c r="J261" s="13"/>
+      <c r="K261" s="13"/>
+      <c r="L261" s="13"/>
+      <c r="M261" s="24"/>
+      <c r="N261" s="13"/>
+      <c r="O261" s="10"/>
+      <c r="P261" s="10"/>
+      <c r="Q261" s="10"/>
+      <c r="R261" s="10"/>
+      <c r="S261" s="10"/>
+      <c r="T261" s="10"/>
+      <c r="U261" s="10"/>
+      <c r="V261" s="6"/>
+    </row>
+    <row r="262" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A262" s="13"/>
+      <c r="B262" s="10"/>
+      <c r="C262" s="12"/>
+      <c r="D262" s="2"/>
+      <c r="E262" s="2"/>
+      <c r="F262" s="2"/>
+      <c r="G262" s="13"/>
+      <c r="H262" s="24"/>
+      <c r="I262" s="24"/>
+      <c r="J262" s="13"/>
+      <c r="K262" s="13"/>
+      <c r="L262" s="13"/>
+      <c r="M262" s="24"/>
+      <c r="N262" s="13"/>
+      <c r="O262" s="10"/>
+      <c r="P262" s="10"/>
+      <c r="Q262" s="10"/>
+      <c r="R262" s="10"/>
+      <c r="S262" s="10"/>
+      <c r="T262" s="10"/>
+      <c r="U262" s="10"/>
+      <c r="V262" s="6"/>
+    </row>
+    <row r="263" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A263" s="13"/>
+      <c r="B263" s="10"/>
+      <c r="C263" s="12"/>
+      <c r="D263" s="2"/>
+      <c r="E263" s="2"/>
+      <c r="F263" s="2"/>
+      <c r="G263" s="13"/>
+      <c r="H263" s="24"/>
+      <c r="I263" s="24"/>
+      <c r="J263" s="13"/>
+      <c r="K263" s="13"/>
+      <c r="L263" s="13"/>
+      <c r="M263" s="24"/>
+      <c r="N263" s="13"/>
+      <c r="O263" s="10"/>
+      <c r="P263" s="10"/>
+      <c r="Q263" s="10"/>
+      <c r="R263" s="10"/>
+      <c r="S263" s="10"/>
+      <c r="T263" s="10"/>
+      <c r="U263" s="10"/>
+      <c r="V263" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4393" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{E66A95E2-7844-4863-8408-10DE7D112023}"/>
+  <xr:revisionPtr revIDLastSave="4519" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA516A21-4019-406F-8FD9-92DBD335C7B6}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="629">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="659">
   <si>
     <t>Date</t>
   </si>
@@ -1886,9 +1886,6 @@
     <t>granite3.3:2b</t>
   </si>
   <si>
-    <t xml:space="preserve">2bb </t>
-  </si>
-  <si>
     <t>1.5GB</t>
   </si>
   <si>
@@ -1941,6 +1938,99 @@
   </si>
   <si>
     <t>3878.85 ms</t>
+  </si>
+  <si>
+    <t>Dolphin 3.0 Llama 3.2 1B</t>
+  </si>
+  <si>
+    <t>~1.3 GB</t>
+  </si>
+  <si>
+    <t>3441.72 ms</t>
+  </si>
+  <si>
+    <t>ShieldGemma 2B</t>
+  </si>
+  <si>
+    <t>668.54 ms</t>
+  </si>
+  <si>
+    <t>smollm2:135m</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 270 MB</t>
+  </si>
+  <si>
+    <t>945.32 ms</t>
+  </si>
+  <si>
+    <t>3712.63 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 708 MB</t>
+  </si>
+  <si>
+    <t>657.76 ms</t>
+  </si>
+  <si>
+    <t>sailor2</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.1 GB </t>
+  </si>
+  <si>
+    <t>5919.71 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> gemma2</t>
+  </si>
+  <si>
+    <t>8285.18 ms</t>
+  </si>
+  <si>
+    <t>1793.78 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> falcon3</t>
+  </si>
+  <si>
+    <t>6606.36 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> qwen2.5-coder</t>
+  </si>
+  <si>
+    <t>1.9 GB</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Alibaba Cloud </t>
+  </si>
+  <si>
+    <t>4389.82 ms</t>
+  </si>
+  <si>
+    <t>cogito</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 2.2 GB</t>
+  </si>
+  <si>
+    <t>Deep Cogito</t>
+  </si>
+  <si>
+    <t>4372.07 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> entity12208/editorai:v2</t>
+  </si>
+  <si>
+    <t>941 MB</t>
+  </si>
+  <si>
+    <t>Editor AI</t>
+  </si>
+  <si>
+    <t>574.08 ms</t>
   </si>
 </sst>
 </file>
@@ -2861,7 +2951,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V263"/>
+  <dimension ref="A1:V274"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -15894,10 +15984,10 @@
         <v>609</v>
       </c>
       <c r="D253" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E253" s="2" t="s">
         <v>610</v>
-      </c>
-      <c r="E253" s="2" t="s">
-        <v>611</v>
       </c>
       <c r="F253" s="2" t="s">
         <v>83</v>
@@ -15917,7 +16007,7 @@
         <v>0.64300000000000002</v>
       </c>
       <c r="Q253" t="s">
-        <v>612</v>
+        <v>611</v>
       </c>
       <c r="R253">
         <v>0.71399999999999997</v>
@@ -15943,7 +16033,7 @@
         <v>398</v>
       </c>
       <c r="C254" t="s">
-        <v>613</v>
+        <v>612</v>
       </c>
       <c r="D254" s="2" t="s">
         <v>244</v>
@@ -15969,7 +16059,7 @@
         <v>0.35</v>
       </c>
       <c r="Q254" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="R254">
         <v>0.48</v>
@@ -15995,16 +16085,16 @@
         <v>393</v>
       </c>
       <c r="C255" s="12" t="s">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="D255" t="s">
         <v>409</v>
       </c>
       <c r="E255" s="2" t="s">
+        <v>615</v>
+      </c>
+      <c r="F255" t="s">
         <v>616</v>
-      </c>
-      <c r="F255" t="s">
-        <v>617</v>
       </c>
       <c r="G255" s="23"/>
       <c r="H255" s="24"/>
@@ -16021,7 +16111,7 @@
         <v>0.41799999999999998</v>
       </c>
       <c r="Q255" t="s">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="R255">
         <v>0.51400000000000001</v>
@@ -16047,13 +16137,13 @@
         <v>398</v>
       </c>
       <c r="C256" s="12" t="s">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D256" s="2" t="s">
         <v>34</v>
       </c>
       <c r="E256" s="2" t="s">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="F256" t="s">
         <v>69</v>
@@ -16073,7 +16163,7 @@
         <v>0.20699999999999999</v>
       </c>
       <c r="Q256" t="s">
-        <v>620</v>
+        <v>619</v>
       </c>
       <c r="R256">
         <v>0.219</v>
@@ -16099,16 +16189,16 @@
         <v>393</v>
       </c>
       <c r="C257" s="12" t="s">
-        <v>621</v>
+        <v>620</v>
       </c>
       <c r="D257" s="2" t="s">
         <v>244</v>
       </c>
       <c r="E257" s="2" t="s">
+        <v>621</v>
+      </c>
+      <c r="F257" t="s">
         <v>622</v>
-      </c>
-      <c r="F257" t="s">
-        <v>623</v>
       </c>
       <c r="G257" s="13"/>
       <c r="H257" s="23"/>
@@ -16125,7 +16215,7 @@
         <v>0.48399999999999999</v>
       </c>
       <c r="Q257" t="s">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="R257">
         <v>0.58699999999999997</v>
@@ -16151,16 +16241,16 @@
         <v>398</v>
       </c>
       <c r="C258" s="12" t="s">
+        <v>624</v>
+      </c>
+      <c r="D258" s="2" t="s">
         <v>625</v>
       </c>
-      <c r="D258" s="2" t="s">
+      <c r="E258" s="2" t="s">
         <v>626</v>
       </c>
-      <c r="E258" s="2" t="s">
-        <v>627</v>
-      </c>
       <c r="F258" t="s">
-        <v>623</v>
+        <v>622</v>
       </c>
       <c r="G258" s="13"/>
       <c r="H258" s="24"/>
@@ -16177,7 +16267,7 @@
         <v>0.60299999999999998</v>
       </c>
       <c r="Q258" t="s">
-        <v>628</v>
+        <v>627</v>
       </c>
       <c r="R258">
         <v>0.68300000000000005</v>
@@ -16196,124 +16286,723 @@
       </c>
     </row>
     <row r="259" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A259" s="13"/>
-      <c r="B259" s="10"/>
-      <c r="C259" s="12"/>
-      <c r="D259" s="2"/>
-      <c r="E259" s="2"/>
-      <c r="F259" s="2"/>
+      <c r="A259" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B259" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C259" t="s">
+        <v>628</v>
+      </c>
+      <c r="D259" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E259" s="2" t="s">
+        <v>629</v>
+      </c>
+      <c r="F259" s="2" t="s">
+        <v>354</v>
+      </c>
       <c r="G259" s="13"/>
       <c r="H259" s="24"/>
       <c r="I259" s="24"/>
       <c r="J259" s="13"/>
       <c r="K259" s="13"/>
-      <c r="L259" s="13"/>
+      <c r="L259" s="23"/>
       <c r="M259" s="24"/>
       <c r="N259" s="13"/>
-      <c r="O259" s="10"/>
-      <c r="P259" s="10"/>
-      <c r="Q259" s="10"/>
-      <c r="R259" s="10"/>
-      <c r="S259" s="10"/>
-      <c r="T259" s="10"/>
-      <c r="U259" s="10"/>
-      <c r="V259" s="6"/>
+      <c r="O259">
+        <v>0.66400000000000003</v>
+      </c>
+      <c r="P259">
+        <v>0.6</v>
+      </c>
+      <c r="Q259" t="s">
+        <v>630</v>
+      </c>
+      <c r="R259">
+        <v>0.68</v>
+      </c>
+      <c r="S259">
+        <v>0.55800000000000005</v>
+      </c>
+      <c r="T259">
+        <v>0.94</v>
+      </c>
+      <c r="U259">
+        <v>0.85299999999999998</v>
+      </c>
+      <c r="V259">
+        <v>0.57699999999999996</v>
+      </c>
     </row>
     <row r="260" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A260" s="13"/>
-      <c r="B260" s="10"/>
-      <c r="C260" s="12"/>
-      <c r="D260" s="2"/>
-      <c r="E260" s="2"/>
-      <c r="F260" s="2"/>
+      <c r="A260" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B260" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C260" t="s">
+        <v>631</v>
+      </c>
+      <c r="D260" s="2" t="s">
+        <v>477</v>
+      </c>
+      <c r="E260" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="F260" s="2" t="s">
+        <v>74</v>
+      </c>
       <c r="G260" s="13"/>
-      <c r="H260" s="24"/>
+      <c r="H260" s="23"/>
       <c r="I260" s="24"/>
       <c r="J260" s="13"/>
       <c r="K260" s="13"/>
       <c r="L260" s="13"/>
       <c r="M260" s="24"/>
       <c r="N260" s="13"/>
-      <c r="O260" s="10"/>
-      <c r="P260" s="10"/>
-      <c r="Q260" s="10"/>
-      <c r="R260" s="10"/>
-      <c r="S260" s="10"/>
-      <c r="T260" s="10"/>
-      <c r="U260" s="10"/>
-      <c r="V260" s="6"/>
+      <c r="O260">
+        <v>0</v>
+      </c>
+      <c r="P260">
+        <v>7.0999999999999994E-2</v>
+      </c>
+      <c r="Q260" t="s">
+        <v>632</v>
+      </c>
+      <c r="R260">
+        <v>0.25700000000000001</v>
+      </c>
+      <c r="S260">
+        <v>0.57499999999999996</v>
+      </c>
+      <c r="T260">
+        <v>1</v>
+      </c>
+      <c r="U260">
+        <v>1</v>
+      </c>
+      <c r="V260">
+        <v>0.41</v>
+      </c>
     </row>
     <row r="261" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A261" s="13"/>
-      <c r="B261" s="10"/>
-      <c r="C261" s="12"/>
-      <c r="D261" s="2"/>
-      <c r="E261" s="2"/>
-      <c r="F261" s="2"/>
+      <c r="A261" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B261" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C261" s="12" t="s">
+        <v>633</v>
+      </c>
+      <c r="D261" s="2" t="s">
+        <v>312</v>
+      </c>
+      <c r="E261" s="2" t="s">
+        <v>634</v>
+      </c>
+      <c r="F261" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G261" s="13"/>
       <c r="H261" s="24"/>
       <c r="I261" s="24"/>
       <c r="J261" s="13"/>
       <c r="K261" s="13"/>
       <c r="L261" s="13"/>
-      <c r="M261" s="24"/>
+      <c r="M261" s="23"/>
       <c r="N261" s="13"/>
-      <c r="O261" s="10"/>
-      <c r="P261" s="10"/>
-      <c r="Q261" s="10"/>
-      <c r="R261" s="10"/>
-      <c r="S261" s="10"/>
-      <c r="T261" s="10"/>
-      <c r="U261" s="10"/>
-      <c r="V261" s="6"/>
+      <c r="O261">
+        <v>0.69299999999999995</v>
+      </c>
+      <c r="P261">
+        <v>0.33600000000000002</v>
+      </c>
+      <c r="Q261" t="s">
+        <v>635</v>
+      </c>
+      <c r="R261">
+        <v>0.36899999999999999</v>
+      </c>
+      <c r="S261">
+        <v>0.64900000000000002</v>
+      </c>
+      <c r="T261">
+        <v>1</v>
+      </c>
+      <c r="U261">
+        <v>0.73799999999999999</v>
+      </c>
+      <c r="V261">
+        <v>0.49399999999999999</v>
+      </c>
     </row>
     <row r="262" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A262" s="13"/>
-      <c r="B262" s="10"/>
-      <c r="C262" s="12"/>
-      <c r="D262" s="2"/>
-      <c r="E262" s="2"/>
-      <c r="F262" s="2"/>
+      <c r="A262" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B262" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C262" s="12" t="s">
+        <v>138</v>
+      </c>
+      <c r="D262" s="2" t="s">
+        <v>409</v>
+      </c>
+      <c r="E262" s="2" t="s">
+        <v>139</v>
+      </c>
+      <c r="F262" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G262" s="13"/>
       <c r="H262" s="24"/>
       <c r="I262" s="24"/>
-      <c r="J262" s="13"/>
+      <c r="J262" s="23"/>
       <c r="K262" s="13"/>
       <c r="L262" s="13"/>
       <c r="M262" s="24"/>
       <c r="N262" s="13"/>
-      <c r="O262" s="10"/>
-      <c r="P262" s="10"/>
-      <c r="Q262" s="10"/>
-      <c r="R262" s="10"/>
-      <c r="S262" s="10"/>
-      <c r="T262" s="10"/>
-      <c r="U262" s="10"/>
-      <c r="V262" s="6"/>
+      <c r="O262">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="P262">
+        <v>0.65600000000000003</v>
+      </c>
+      <c r="Q262" t="s">
+        <v>636</v>
+      </c>
+      <c r="R262">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="S262">
+        <v>0.53700000000000003</v>
+      </c>
+      <c r="T262">
+        <v>0.873</v>
+      </c>
+      <c r="U262">
+        <v>0.86599999999999999</v>
+      </c>
+      <c r="V262">
+        <v>0.59699999999999998</v>
+      </c>
     </row>
     <row r="263" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A263" s="13"/>
-      <c r="B263" s="10"/>
-      <c r="C263" s="12"/>
-      <c r="D263" s="2"/>
-      <c r="E263" s="2"/>
-      <c r="F263" s="2"/>
+      <c r="A263" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B263" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C263" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="D263" s="2" t="s">
+        <v>598</v>
+      </c>
+      <c r="E263" s="2" t="s">
+        <v>637</v>
+      </c>
+      <c r="F263" s="2" t="s">
+        <v>83</v>
+      </c>
       <c r="G263" s="13"/>
       <c r="H263" s="24"/>
       <c r="I263" s="24"/>
       <c r="J263" s="13"/>
-      <c r="K263" s="13"/>
+      <c r="K263" s="23"/>
       <c r="L263" s="13"/>
       <c r="M263" s="24"/>
       <c r="N263" s="13"/>
-      <c r="O263" s="10"/>
-      <c r="P263" s="10"/>
-      <c r="Q263" s="10"/>
-      <c r="R263" s="10"/>
-      <c r="S263" s="10"/>
-      <c r="T263" s="10"/>
-      <c r="U263" s="10"/>
-      <c r="V263" s="6"/>
+      <c r="O263">
+        <v>0.71299999999999997</v>
+      </c>
+      <c r="P263">
+        <v>0.52400000000000002</v>
+      </c>
+      <c r="Q263" t="s">
+        <v>638</v>
+      </c>
+      <c r="R263">
+        <v>0.61899999999999999</v>
+      </c>
+      <c r="S263">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="T263">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U263">
+        <v>0.63600000000000001</v>
+      </c>
+      <c r="V263">
+        <v>0.53900000000000003</v>
+      </c>
+    </row>
+    <row r="264" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A264" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B264" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C264" s="12" t="s">
+        <v>639</v>
+      </c>
+      <c r="D264" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E264" s="2" t="s">
+        <v>640</v>
+      </c>
+      <c r="F264" t="s">
+        <v>616</v>
+      </c>
+      <c r="G264" s="13"/>
+      <c r="H264" s="24"/>
+      <c r="I264" s="24"/>
+      <c r="J264" s="13"/>
+      <c r="K264" s="13"/>
+      <c r="L264" s="13"/>
+      <c r="M264" s="24"/>
+      <c r="N264" s="23"/>
+      <c r="O264">
+        <v>0.66700000000000004</v>
+      </c>
+      <c r="P264">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="Q264" t="s">
+        <v>641</v>
+      </c>
+      <c r="R264">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="S264">
+        <v>0.57299999999999995</v>
+      </c>
+      <c r="T264">
+        <v>0.96199999999999997</v>
+      </c>
+      <c r="U264">
+        <v>0.77500000000000002</v>
+      </c>
+      <c r="V264">
+        <v>0.55800000000000005</v>
+      </c>
+    </row>
+    <row r="265" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A265" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B265" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C265" s="12" t="s">
+        <v>642</v>
+      </c>
+      <c r="D265" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E265" s="2" t="s">
+        <v>116</v>
+      </c>
+      <c r="F265" s="2" t="s">
+        <v>74</v>
+      </c>
+      <c r="G265" s="13"/>
+      <c r="H265" s="24"/>
+      <c r="I265" s="24"/>
+      <c r="J265" s="13"/>
+      <c r="K265" s="13"/>
+      <c r="L265" s="13"/>
+      <c r="M265" s="24"/>
+      <c r="N265" s="23"/>
+      <c r="O265">
+        <v>0.622</v>
+      </c>
+      <c r="P265">
+        <v>0.503</v>
+      </c>
+      <c r="Q265" t="s">
+        <v>643</v>
+      </c>
+      <c r="R265">
+        <v>0.58299999999999996</v>
+      </c>
+      <c r="S265">
+        <v>0.60199999999999998</v>
+      </c>
+      <c r="T265">
+        <v>0.93200000000000005</v>
+      </c>
+      <c r="U265">
+        <v>0.878</v>
+      </c>
+      <c r="V265">
+        <v>0.53700000000000003</v>
+      </c>
+    </row>
+    <row r="266" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A266" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B266" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C266" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="D266" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E266" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="F266" t="s">
+        <v>194</v>
+      </c>
+      <c r="G266" s="13"/>
+      <c r="H266" s="24"/>
+      <c r="I266" s="24"/>
+      <c r="J266" s="23"/>
+      <c r="K266" s="13"/>
+      <c r="L266" s="13"/>
+      <c r="M266" s="24"/>
+      <c r="N266" s="13"/>
+      <c r="O266">
+        <v>0.40100000000000002</v>
+      </c>
+      <c r="P266">
+        <v>0.47499999999999998</v>
+      </c>
+      <c r="Q266" t="s">
+        <v>644</v>
+      </c>
+      <c r="R266">
+        <v>0.57999999999999996</v>
+      </c>
+      <c r="S266">
+        <v>0.60299999999999998</v>
+      </c>
+      <c r="T266">
+        <v>1</v>
+      </c>
+      <c r="U266">
+        <v>0.68500000000000005</v>
+      </c>
+      <c r="V266">
+        <v>0.47699999999999998</v>
+      </c>
+    </row>
+    <row r="267" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A267" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B267" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C267" s="12" t="s">
+        <v>645</v>
+      </c>
+      <c r="D267" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E267" s="2" t="s">
+        <v>501</v>
+      </c>
+      <c r="F267" t="s">
+        <v>552</v>
+      </c>
+      <c r="G267" s="13"/>
+      <c r="H267" s="23"/>
+      <c r="I267" s="24"/>
+      <c r="J267" s="13"/>
+      <c r="K267" s="13"/>
+      <c r="L267" s="13"/>
+      <c r="M267" s="24"/>
+      <c r="N267" s="13"/>
+      <c r="O267">
+        <v>0.74399999999999999</v>
+      </c>
+      <c r="P267">
+        <v>0.64800000000000002</v>
+      </c>
+      <c r="Q267" t="s">
+        <v>646</v>
+      </c>
+      <c r="R267">
+        <v>0.71899999999999997</v>
+      </c>
+      <c r="S267">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="T267">
+        <v>0.74</v>
+      </c>
+      <c r="U267">
+        <v>0.81299999999999994</v>
+      </c>
+      <c r="V267">
+        <v>0.56799999999999995</v>
+      </c>
+    </row>
+    <row r="268" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A268" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B268" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C268" s="12" t="s">
+        <v>647</v>
+      </c>
+      <c r="D268" s="2" t="s">
+        <v>558</v>
+      </c>
+      <c r="E268" t="s">
+        <v>648</v>
+      </c>
+      <c r="F268" s="2" t="s">
+        <v>649</v>
+      </c>
+      <c r="G268" s="13"/>
+      <c r="H268" s="24"/>
+      <c r="I268" s="23"/>
+      <c r="J268" s="13"/>
+      <c r="K268" s="13"/>
+      <c r="L268" s="13"/>
+      <c r="M268" s="24"/>
+      <c r="N268" s="13"/>
+      <c r="O268">
+        <v>0.52300000000000002</v>
+      </c>
+      <c r="P268">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="Q268" t="s">
+        <v>650</v>
+      </c>
+      <c r="R268">
+        <v>0.66300000000000003</v>
+      </c>
+      <c r="S268">
+        <v>0.56599999999999995</v>
+      </c>
+      <c r="T268">
+        <v>1</v>
+      </c>
+      <c r="U268">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="V268">
+        <v>0.55200000000000005</v>
+      </c>
+    </row>
+    <row r="269" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A269" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B269" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C269" s="12" t="s">
+        <v>651</v>
+      </c>
+      <c r="D269" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E269" s="2" t="s">
+        <v>652</v>
+      </c>
+      <c r="F269" t="s">
+        <v>653</v>
+      </c>
+      <c r="G269" s="13"/>
+      <c r="H269" s="24"/>
+      <c r="I269" s="24"/>
+      <c r="J269" s="13"/>
+      <c r="K269" s="13"/>
+      <c r="L269" s="13"/>
+      <c r="M269" s="24"/>
+      <c r="N269" s="23"/>
+      <c r="O269">
+        <v>0.71799999999999997</v>
+      </c>
+      <c r="P269">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="Q269" t="s">
+        <v>654</v>
+      </c>
+      <c r="R269">
+        <v>0.72299999999999998</v>
+      </c>
+      <c r="S269">
+        <v>0.54100000000000004</v>
+      </c>
+      <c r="T269">
+        <v>1</v>
+      </c>
+      <c r="U269">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="V269">
+        <v>0.60799999999999998</v>
+      </c>
+    </row>
+    <row r="270" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A270" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B270" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C270" s="12" t="s">
+        <v>655</v>
+      </c>
+      <c r="D270" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E270" t="s">
+        <v>656</v>
+      </c>
+      <c r="F270" s="2" t="s">
+        <v>657</v>
+      </c>
+      <c r="G270" s="13"/>
+      <c r="H270" s="24"/>
+      <c r="I270" s="23"/>
+      <c r="J270" s="13"/>
+      <c r="K270" s="13"/>
+      <c r="L270" s="13"/>
+      <c r="M270" s="24"/>
+      <c r="N270" s="13"/>
+      <c r="O270">
+        <v>0.36399999999999999</v>
+      </c>
+      <c r="P270">
+        <v>0.39700000000000002</v>
+      </c>
+      <c r="Q270" t="s">
+        <v>658</v>
+      </c>
+      <c r="R270">
+        <v>0.51800000000000002</v>
+      </c>
+      <c r="S270">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="T270">
+        <v>1</v>
+      </c>
+      <c r="U270">
+        <v>0.58899999999999997</v>
+      </c>
+      <c r="V270">
+        <v>0.46700000000000003</v>
+      </c>
+    </row>
+    <row r="271" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A271" s="13"/>
+      <c r="B271" s="10"/>
+      <c r="C271" s="12"/>
+      <c r="D271" s="2"/>
+      <c r="E271" s="2"/>
+      <c r="G271" s="13"/>
+      <c r="H271" s="24"/>
+      <c r="I271" s="24"/>
+      <c r="J271" s="13"/>
+      <c r="K271" s="13"/>
+      <c r="L271" s="13"/>
+      <c r="M271" s="24"/>
+      <c r="N271" s="13"/>
+      <c r="O271" s="10"/>
+      <c r="P271" s="10"/>
+      <c r="Q271" s="10"/>
+      <c r="R271" s="10"/>
+      <c r="S271" s="10"/>
+      <c r="T271" s="10"/>
+      <c r="U271" s="10"/>
+      <c r="V271" s="6"/>
+    </row>
+    <row r="272" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A272" s="13"/>
+      <c r="B272" s="10"/>
+      <c r="C272" s="12"/>
+      <c r="D272" s="2"/>
+      <c r="E272" s="2"/>
+      <c r="F272" s="2"/>
+      <c r="G272" s="13"/>
+      <c r="H272" s="24"/>
+      <c r="I272" s="24"/>
+      <c r="J272" s="13"/>
+      <c r="K272" s="13"/>
+      <c r="L272" s="13"/>
+      <c r="M272" s="24"/>
+      <c r="N272" s="13"/>
+      <c r="O272" s="10"/>
+      <c r="P272" s="10"/>
+      <c r="Q272" s="10"/>
+      <c r="R272" s="10"/>
+      <c r="S272" s="10"/>
+      <c r="T272" s="10"/>
+      <c r="U272" s="10"/>
+      <c r="V272" s="6"/>
+    </row>
+    <row r="273" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A273" s="13"/>
+      <c r="B273" s="10"/>
+      <c r="C273" s="12"/>
+      <c r="D273" s="2"/>
+      <c r="E273" s="2"/>
+      <c r="F273" s="2"/>
+      <c r="G273" s="13"/>
+      <c r="H273" s="24"/>
+      <c r="I273" s="24"/>
+      <c r="J273" s="13"/>
+      <c r="K273" s="13"/>
+      <c r="L273" s="13"/>
+      <c r="M273" s="24"/>
+      <c r="N273" s="13"/>
+      <c r="O273" s="10"/>
+      <c r="P273" s="10"/>
+      <c r="Q273" s="10"/>
+      <c r="R273" s="10"/>
+      <c r="S273" s="10"/>
+      <c r="T273" s="10"/>
+      <c r="U273" s="10"/>
+      <c r="V273" s="6"/>
+    </row>
+    <row r="274" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A274" s="13"/>
+      <c r="B274" s="10"/>
+      <c r="C274" s="12"/>
+      <c r="D274" s="2"/>
+      <c r="E274" s="2"/>
+      <c r="F274" s="2"/>
+      <c r="G274" s="13"/>
+      <c r="H274" s="24"/>
+      <c r="I274" s="24"/>
+      <c r="J274" s="13"/>
+      <c r="K274" s="13"/>
+      <c r="L274" s="13"/>
+      <c r="M274" s="24"/>
+      <c r="N274" s="13"/>
+      <c r="O274" s="10"/>
+      <c r="P274" s="10"/>
+      <c r="Q274" s="10"/>
+      <c r="R274" s="10"/>
+      <c r="S274" s="10"/>
+      <c r="T274" s="10"/>
+      <c r="U274" s="10"/>
+      <c r="V274" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4519" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DA516A21-4019-406F-8FD9-92DBD335C7B6}"/>
+  <xr:revisionPtr revIDLastSave="4551" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25252688-7057-4D7B-839D-20A3D7DE6668}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1606" uniqueCount="659">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="671">
   <si>
     <t>Date</t>
   </si>
@@ -2031,6 +2031,42 @@
   </si>
   <si>
     <t>574.08 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> granite4</t>
+  </si>
+  <si>
+    <t>1253.90 ms</t>
+  </si>
+  <si>
+    <t>qwen2-math:1.5b-instruct-q5_1</t>
+  </si>
+  <si>
+    <t>Qwen Team (Alibaba)</t>
+  </si>
+  <si>
+    <t>4340.22 ms</t>
+  </si>
+  <si>
+    <t>LiquidAI</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 1.2 GB</t>
+  </si>
+  <si>
+    <t>1805.72 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> qwen2.5:1.5b-instruct-q5_1</t>
+  </si>
+  <si>
+    <t>5b</t>
+  </si>
+  <si>
+    <t>1.2 GB</t>
+  </si>
+  <si>
+    <t>4366.12 ms</t>
   </si>
 </sst>
 </file>
@@ -2951,7 +2987,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V274"/>
+  <dimension ref="A1:V276"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -16910,35 +16946,73 @@
       </c>
     </row>
     <row r="271" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A271" s="13"/>
-      <c r="B271" s="10"/>
-      <c r="C271" s="12"/>
-      <c r="D271" s="2"/>
-      <c r="E271" s="2"/>
+      <c r="A271" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B271" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C271" s="12" t="s">
+        <v>659</v>
+      </c>
+      <c r="D271" s="2" t="s">
+        <v>592</v>
+      </c>
+      <c r="E271" t="s">
+        <v>217</v>
+      </c>
       <c r="G271" s="13"/>
       <c r="H271" s="24"/>
       <c r="I271" s="24"/>
-      <c r="J271" s="13"/>
+      <c r="J271" s="23"/>
       <c r="K271" s="13"/>
       <c r="L271" s="13"/>
       <c r="M271" s="24"/>
       <c r="N271" s="13"/>
-      <c r="O271" s="10"/>
-      <c r="P271" s="10"/>
-      <c r="Q271" s="10"/>
-      <c r="R271" s="10"/>
-      <c r="S271" s="10"/>
-      <c r="T271" s="10"/>
-      <c r="U271" s="10"/>
-      <c r="V271" s="6"/>
+      <c r="O271">
+        <v>0.59199999999999997</v>
+      </c>
+      <c r="P271">
+        <v>0.51700000000000002</v>
+      </c>
+      <c r="Q271" t="s">
+        <v>660</v>
+      </c>
+      <c r="R271">
+        <v>0.61399999999999999</v>
+      </c>
+      <c r="S271">
+        <v>0.58199999999999996</v>
+      </c>
+      <c r="T271">
+        <v>1</v>
+      </c>
+      <c r="U271">
+        <v>0.83699999999999997</v>
+      </c>
+      <c r="V271">
+        <v>0.55500000000000005</v>
+      </c>
     </row>
     <row r="272" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A272" s="13"/>
-      <c r="B272" s="10"/>
-      <c r="C272" s="12"/>
-      <c r="D272" s="2"/>
-      <c r="E272" s="2"/>
-      <c r="F272" s="2"/>
+      <c r="A272" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B272" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C272" s="12" t="s">
+        <v>661</v>
+      </c>
+      <c r="D272" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="E272" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="F272" t="s">
+        <v>662</v>
+      </c>
       <c r="G272" s="13"/>
       <c r="H272" s="24"/>
       <c r="I272" s="24"/>
@@ -16946,63 +17020,183 @@
       <c r="K272" s="13"/>
       <c r="L272" s="13"/>
       <c r="M272" s="24"/>
-      <c r="N272" s="13"/>
-      <c r="O272" s="10"/>
-      <c r="P272" s="10"/>
-      <c r="Q272" s="10"/>
-      <c r="R272" s="10"/>
-      <c r="S272" s="10"/>
-      <c r="T272" s="10"/>
-      <c r="U272" s="10"/>
-      <c r="V272" s="6"/>
+      <c r="N272" s="23"/>
+      <c r="O272">
+        <v>0.76300000000000001</v>
+      </c>
+      <c r="P272">
+        <v>0.58799999999999997</v>
+      </c>
+      <c r="Q272" t="s">
+        <v>663</v>
+      </c>
+      <c r="R272">
+        <v>0.67100000000000004</v>
+      </c>
+      <c r="S272">
+        <v>0.56699999999999995</v>
+      </c>
+      <c r="T272">
+        <v>1</v>
+      </c>
+      <c r="U272">
+        <v>0.82299999999999995</v>
+      </c>
+      <c r="V272">
+        <v>0.59699999999999998</v>
+      </c>
     </row>
     <row r="273" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A273" s="13"/>
-      <c r="B273" s="10"/>
-      <c r="C273" s="12"/>
-      <c r="D273" s="2"/>
-      <c r="E273" s="2"/>
-      <c r="F273" s="2"/>
+      <c r="A273" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B273" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C273" s="12" t="s">
+        <v>664</v>
+      </c>
+      <c r="D273" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E273" s="2" t="s">
+        <v>665</v>
+      </c>
+      <c r="F273" t="s">
+        <v>79</v>
+      </c>
       <c r="G273" s="13"/>
       <c r="H273" s="24"/>
-      <c r="I273" s="24"/>
+      <c r="I273" s="23"/>
       <c r="J273" s="13"/>
       <c r="K273" s="13"/>
       <c r="L273" s="13"/>
       <c r="M273" s="24"/>
       <c r="N273" s="13"/>
-      <c r="O273" s="10"/>
-      <c r="P273" s="10"/>
-      <c r="Q273" s="10"/>
-      <c r="R273" s="10"/>
-      <c r="S273" s="10"/>
-      <c r="T273" s="10"/>
-      <c r="U273" s="10"/>
-      <c r="V273" s="6"/>
+      <c r="O273">
+        <v>0.73</v>
+      </c>
+      <c r="P273">
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="Q273" t="s">
+        <v>666</v>
+      </c>
+      <c r="R273">
+        <v>0.71099999999999997</v>
+      </c>
+      <c r="S273">
+        <v>0.498</v>
+      </c>
+      <c r="T273">
+        <v>1</v>
+      </c>
+      <c r="U273">
+        <v>0.94399999999999995</v>
+      </c>
+      <c r="V273">
+        <v>0.64800000000000002</v>
+      </c>
     </row>
     <row r="274" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A274" s="13"/>
-      <c r="B274" s="10"/>
-      <c r="C274" s="12"/>
-      <c r="D274" s="2"/>
-      <c r="E274" s="2"/>
-      <c r="F274" s="2"/>
+      <c r="A274" s="13">
+        <v>46324</v>
+      </c>
+      <c r="B274" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C274" s="12" t="s">
+        <v>667</v>
+      </c>
+      <c r="D274" s="2" t="s">
+        <v>668</v>
+      </c>
+      <c r="E274" s="2" t="s">
+        <v>669</v>
+      </c>
+      <c r="F274" t="s">
+        <v>406</v>
+      </c>
       <c r="G274" s="13"/>
-      <c r="H274" s="24"/>
+      <c r="H274" s="23"/>
       <c r="I274" s="24"/>
       <c r="J274" s="13"/>
       <c r="K274" s="13"/>
       <c r="L274" s="13"/>
       <c r="M274" s="24"/>
       <c r="N274" s="13"/>
-      <c r="O274" s="10"/>
-      <c r="P274" s="10"/>
-      <c r="Q274" s="10"/>
-      <c r="R274" s="10"/>
-      <c r="S274" s="10"/>
-      <c r="T274" s="10"/>
-      <c r="U274" s="10"/>
-      <c r="V274" s="6"/>
+      <c r="O274">
+        <v>0.73199999999999998</v>
+      </c>
+      <c r="P274">
+        <v>0.65700000000000003</v>
+      </c>
+      <c r="Q274" t="s">
+        <v>670</v>
+      </c>
+      <c r="R274">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="S274">
+        <v>0.53800000000000003</v>
+      </c>
+      <c r="T274">
+        <v>0.78</v>
+      </c>
+      <c r="U274">
+        <v>0.86299999999999999</v>
+      </c>
+      <c r="V274">
+        <v>0.58299999999999996</v>
+      </c>
+    </row>
+    <row r="275" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A275" s="13"/>
+      <c r="B275" s="10"/>
+      <c r="C275" s="12"/>
+      <c r="D275" s="2"/>
+      <c r="E275" s="2"/>
+      <c r="F275" s="2"/>
+      <c r="G275" s="13"/>
+      <c r="H275" s="24"/>
+      <c r="I275" s="24"/>
+      <c r="J275" s="13"/>
+      <c r="K275" s="13"/>
+      <c r="L275" s="13"/>
+      <c r="M275" s="24"/>
+      <c r="N275" s="13"/>
+      <c r="O275" s="10"/>
+      <c r="P275" s="10"/>
+      <c r="Q275" s="10"/>
+      <c r="R275" s="10"/>
+      <c r="S275" s="10"/>
+      <c r="T275" s="10"/>
+      <c r="U275" s="10"/>
+      <c r="V275" s="6"/>
+    </row>
+    <row r="276" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A276" s="13"/>
+      <c r="B276" s="10"/>
+      <c r="C276" s="12"/>
+      <c r="D276" s="2"/>
+      <c r="E276" s="2"/>
+      <c r="F276" s="2"/>
+      <c r="G276" s="13"/>
+      <c r="H276" s="24"/>
+      <c r="I276" s="24"/>
+      <c r="J276" s="13"/>
+      <c r="K276" s="13"/>
+      <c r="L276" s="13"/>
+      <c r="M276" s="24"/>
+      <c r="N276" s="13"/>
+      <c r="O276" s="10"/>
+      <c r="P276" s="10"/>
+      <c r="Q276" s="10"/>
+      <c r="R276" s="10"/>
+      <c r="S276" s="10"/>
+      <c r="T276" s="10"/>
+      <c r="U276" s="10"/>
+      <c r="V276" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30619"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30621"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4551" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{25252688-7057-4D7B-839D-20A3D7DE6668}"/>
+  <xr:revisionPtr revIDLastSave="4634" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A456466-3883-4ED7-9DA2-CE3E8082B723}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1629" uniqueCount="671">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1672" uniqueCount="693">
   <si>
     <t>Date</t>
   </si>
@@ -2067,6 +2067,72 @@
   </si>
   <si>
     <t>4366.12 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> MeetSolanki/MeetAISmall</t>
+  </si>
+  <si>
+    <t>0.7b</t>
+  </si>
+  <si>
+    <t>523 MB</t>
+  </si>
+  <si>
+    <t>1838.74 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> tulu3</t>
+  </si>
+  <si>
+    <t>8b</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 4.9 GB</t>
+  </si>
+  <si>
+    <t>16814.81 ms</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> hf.co/mradermacher/Yi-Coder-1.5B-Chat-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 963 MB</t>
+  </si>
+  <si>
+    <t>2509.01 ms</t>
+  </si>
+  <si>
+    <t>granite-3.3-2b-instruct-GGUF:Q4_K_M</t>
+  </si>
+  <si>
+    <t>6488.13 ms</t>
+  </si>
+  <si>
+    <t>MeetSolanki/MeetAISmall</t>
+  </si>
+  <si>
+    <t>241 MB</t>
+  </si>
+  <si>
+    <t>2193.75 ms</t>
+  </si>
+  <si>
+    <t>GRAFT-1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 971 MB</t>
+  </si>
+  <si>
+    <t>2087.55 ms</t>
+  </si>
+  <si>
+    <t>Granite 4.0 H-1B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">901 MB  </t>
+  </si>
+  <si>
+    <t>6533.02 ms</t>
   </si>
 </sst>
 </file>
@@ -2987,7 +3053,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A897CD1C-0E15-574E-9F3A-4CBFEDFF084C}">
-  <dimension ref="A1:V276"/>
+  <dimension ref="A1:V284"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" customHeight="1"/>
   <cols>
     <col min="2" max="2" width="10.375" customWidth="1"/>
@@ -16961,6 +17027,9 @@
       <c r="E271" t="s">
         <v>217</v>
       </c>
+      <c r="F271" t="s">
+        <v>69</v>
+      </c>
       <c r="G271" s="13"/>
       <c r="H271" s="24"/>
       <c r="I271" s="24"/>
@@ -17151,52 +17220,440 @@
       </c>
     </row>
     <row r="275" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A275" s="13"/>
-      <c r="B275" s="10"/>
-      <c r="C275" s="12"/>
-      <c r="D275" s="2"/>
-      <c r="E275" s="2"/>
-      <c r="F275" s="2"/>
+      <c r="A275" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B275" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C275" s="12" t="s">
+        <v>671</v>
+      </c>
+      <c r="D275" s="2" t="s">
+        <v>672</v>
+      </c>
+      <c r="E275" t="s">
+        <v>673</v>
+      </c>
+      <c r="F275" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G275" s="13"/>
       <c r="H275" s="24"/>
       <c r="I275" s="24"/>
       <c r="J275" s="13"/>
-      <c r="K275" s="13"/>
+      <c r="K275" s="23"/>
       <c r="L275" s="13"/>
       <c r="M275" s="24"/>
       <c r="N275" s="13"/>
-      <c r="O275" s="10"/>
-      <c r="P275" s="10"/>
-      <c r="Q275" s="10"/>
-      <c r="R275" s="10"/>
-      <c r="S275" s="10"/>
-      <c r="T275" s="10"/>
-      <c r="U275" s="10"/>
-      <c r="V275" s="6"/>
+      <c r="O275">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="P275">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="Q275" t="s">
+        <v>674</v>
+      </c>
+      <c r="R275">
+        <v>0.64</v>
+      </c>
+      <c r="S275">
+        <v>0.57799999999999996</v>
+      </c>
+      <c r="T275">
+        <v>1</v>
+      </c>
+      <c r="U275">
+        <v>0.89200000000000002</v>
+      </c>
+      <c r="V275">
+        <v>0.56200000000000006</v>
+      </c>
     </row>
     <row r="276" spans="1:22" ht="15.75" customHeight="1">
-      <c r="A276" s="13"/>
-      <c r="B276" s="10"/>
-      <c r="C276" s="12"/>
-      <c r="D276" s="2"/>
-      <c r="E276" s="2"/>
-      <c r="F276" s="2"/>
+      <c r="A276" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B276" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C276" s="12" t="s">
+        <v>675</v>
+      </c>
+      <c r="D276" s="2" t="s">
+        <v>676</v>
+      </c>
+      <c r="E276" s="2" t="s">
+        <v>677</v>
+      </c>
+      <c r="F276" s="2" t="s">
+        <v>69</v>
+      </c>
       <c r="G276" s="13"/>
       <c r="H276" s="24"/>
       <c r="I276" s="24"/>
       <c r="J276" s="13"/>
       <c r="K276" s="13"/>
-      <c r="L276" s="13"/>
+      <c r="L276" s="23"/>
       <c r="M276" s="24"/>
       <c r="N276" s="13"/>
-      <c r="O276" s="10"/>
-      <c r="P276" s="10"/>
-      <c r="Q276" s="10"/>
-      <c r="R276" s="10"/>
-      <c r="S276" s="10"/>
-      <c r="T276" s="10"/>
-      <c r="U276" s="10"/>
-      <c r="V276" s="6"/>
+      <c r="O276">
+        <v>0.72499999999999998</v>
+      </c>
+      <c r="P276">
+        <v>0.60499999999999998</v>
+      </c>
+      <c r="Q276" t="s">
+        <v>678</v>
+      </c>
+      <c r="R276">
+        <v>0.68400000000000005</v>
+      </c>
+      <c r="S276">
+        <v>0.56999999999999995</v>
+      </c>
+      <c r="T276">
+        <v>0.94</v>
+      </c>
+      <c r="U276">
+        <v>0.84799999999999998</v>
+      </c>
+      <c r="V276">
+        <v>0.58499999999999996</v>
+      </c>
+    </row>
+    <row r="277" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A277" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B277" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C277" s="12" t="s">
+        <v>679</v>
+      </c>
+      <c r="D277" s="2" t="s">
+        <v>481</v>
+      </c>
+      <c r="E277" s="2" t="s">
+        <v>680</v>
+      </c>
+      <c r="F277" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G277" s="13"/>
+      <c r="H277" s="24"/>
+      <c r="I277" s="23"/>
+      <c r="J277" s="13"/>
+      <c r="K277" s="13"/>
+      <c r="L277" s="13"/>
+      <c r="M277" s="24"/>
+      <c r="N277" s="13"/>
+      <c r="O277">
+        <v>0.73499999999999999</v>
+      </c>
+      <c r="P277">
+        <v>0.65</v>
+      </c>
+      <c r="Q277" t="s">
+        <v>681</v>
+      </c>
+      <c r="R277">
+        <v>0.72</v>
+      </c>
+      <c r="S277">
+        <v>0.53900000000000003</v>
+      </c>
+      <c r="T277">
+        <v>0.96299999999999997</v>
+      </c>
+      <c r="U277">
+        <v>0.86099999999999999</v>
+      </c>
+      <c r="V277">
+        <v>0.61199999999999999</v>
+      </c>
+    </row>
+    <row r="278" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A278" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B278" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C278" s="12" t="s">
+        <v>682</v>
+      </c>
+      <c r="D278" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="E278" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="F278" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G278" s="13"/>
+      <c r="H278" s="24"/>
+      <c r="I278" s="24"/>
+      <c r="J278" s="13"/>
+      <c r="K278" s="13"/>
+      <c r="L278" s="23"/>
+      <c r="M278" s="24"/>
+      <c r="N278" s="13"/>
+      <c r="O278">
+        <v>0.79800000000000004</v>
+      </c>
+      <c r="P278">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="Q278" t="s">
+        <v>683</v>
+      </c>
+      <c r="R278">
+        <v>0.70899999999999996</v>
+      </c>
+      <c r="S278">
+        <v>0.54800000000000004</v>
+      </c>
+      <c r="T278">
+        <v>0.872</v>
+      </c>
+      <c r="U278">
+        <v>0.86</v>
+      </c>
+      <c r="V278">
+        <v>0.60199999999999998</v>
+      </c>
+    </row>
+    <row r="279" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A279" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B279" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C279" t="s">
+        <v>684</v>
+      </c>
+      <c r="D279" t="s">
+        <v>578</v>
+      </c>
+      <c r="E279" t="s">
+        <v>685</v>
+      </c>
+      <c r="F279" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="G279" s="13"/>
+      <c r="H279" s="24"/>
+      <c r="I279" s="24"/>
+      <c r="J279" s="13"/>
+      <c r="K279" s="13"/>
+      <c r="L279" s="13"/>
+      <c r="M279" s="24"/>
+      <c r="N279" s="23"/>
+      <c r="O279">
+        <v>0.73</v>
+      </c>
+      <c r="P279">
+        <v>0.56799999999999995</v>
+      </c>
+      <c r="Q279" t="s">
+        <v>686</v>
+      </c>
+      <c r="R279">
+        <v>0.65400000000000003</v>
+      </c>
+      <c r="S279">
+        <v>0.57899999999999996</v>
+      </c>
+      <c r="T279">
+        <v>0.90500000000000003</v>
+      </c>
+      <c r="U279">
+        <v>0.85799999999999998</v>
+      </c>
+      <c r="V279">
+        <v>0.57899999999999996</v>
+      </c>
+    </row>
+    <row r="280" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A280" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B280" s="10" t="s">
+        <v>398</v>
+      </c>
+      <c r="C280" s="12" t="s">
+        <v>687</v>
+      </c>
+      <c r="D280" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E280" s="2" t="s">
+        <v>688</v>
+      </c>
+      <c r="F280" s="2" t="s">
+        <v>69</v>
+      </c>
+      <c r="G280" s="24"/>
+      <c r="H280" s="23"/>
+      <c r="I280" s="24"/>
+      <c r="J280" s="13"/>
+      <c r="K280" s="13"/>
+      <c r="L280" s="13"/>
+      <c r="M280" s="24"/>
+      <c r="N280" s="13"/>
+      <c r="O280">
+        <v>0.626</v>
+      </c>
+      <c r="P280">
+        <v>0.65800000000000003</v>
+      </c>
+      <c r="Q280" t="s">
+        <v>689</v>
+      </c>
+      <c r="R280">
+        <v>0.72699999999999998</v>
+      </c>
+      <c r="S280">
+        <v>0.54</v>
+      </c>
+      <c r="T280">
+        <v>0.74</v>
+      </c>
+      <c r="U280">
+        <v>0.88800000000000001</v>
+      </c>
+      <c r="V280">
+        <v>0.56399999999999995</v>
+      </c>
+    </row>
+    <row r="281" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A281" s="13">
+        <v>46325</v>
+      </c>
+      <c r="B281" s="10" t="s">
+        <v>393</v>
+      </c>
+      <c r="C281" t="s">
+        <v>690</v>
+      </c>
+      <c r="D281" s="2" t="s">
+        <v>376</v>
+      </c>
+      <c r="E281" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="F281" s="2" t="s">
+        <v>83</v>
+      </c>
+      <c r="G281" s="13"/>
+      <c r="H281" s="24"/>
+      <c r="I281" s="24"/>
+      <c r="J281" s="13"/>
+      <c r="K281" s="13"/>
+      <c r="L281" s="23"/>
+      <c r="M281" s="24"/>
+      <c r="N281" s="13"/>
+      <c r="O281">
+        <v>0.72599999999999998</v>
+      </c>
+      <c r="P281">
+        <v>0.63800000000000001</v>
+      </c>
+      <c r="Q281" t="s">
+        <v>692</v>
+      </c>
+      <c r="R281">
+        <v>0.71</v>
+      </c>
+      <c r="S281">
+        <v>0.54900000000000004</v>
+      </c>
+      <c r="T281">
+        <v>0.91</v>
+      </c>
+      <c r="U281">
+        <v>0.83799999999999997</v>
+      </c>
+      <c r="V281">
+        <v>0.59</v>
+      </c>
+    </row>
+    <row r="282" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A282" s="13"/>
+      <c r="B282" s="10"/>
+      <c r="C282" s="12"/>
+      <c r="D282" s="2"/>
+      <c r="E282" s="2"/>
+      <c r="F282" s="2"/>
+      <c r="G282" s="13"/>
+      <c r="H282" s="24"/>
+      <c r="I282" s="24"/>
+      <c r="J282" s="13"/>
+      <c r="K282" s="13"/>
+      <c r="L282" s="13"/>
+      <c r="M282" s="24"/>
+      <c r="N282" s="13"/>
+      <c r="O282" s="10"/>
+      <c r="P282" s="10"/>
+      <c r="Q282" s="10"/>
+      <c r="R282" s="10"/>
+      <c r="S282" s="10"/>
+      <c r="T282" s="10"/>
+      <c r="U282" s="10"/>
+      <c r="V282" s="6"/>
+    </row>
+    <row r="283" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A283" s="13"/>
+      <c r="B283" s="10"/>
+      <c r="C283" s="12"/>
+      <c r="D283" s="2"/>
+      <c r="E283" s="2"/>
+      <c r="F283" s="2"/>
+      <c r="G283" s="13"/>
+      <c r="H283" s="24"/>
+      <c r="I283" s="24"/>
+      <c r="J283" s="13"/>
+      <c r="K283" s="13"/>
+      <c r="L283" s="13"/>
+      <c r="M283" s="24"/>
+      <c r="N283" s="13"/>
+      <c r="O283" s="10"/>
+      <c r="P283" s="10"/>
+      <c r="Q283" s="10"/>
+      <c r="R283" s="10"/>
+      <c r="S283" s="10"/>
+      <c r="T283" s="10"/>
+      <c r="U283" s="10"/>
+      <c r="V283" s="6"/>
+    </row>
+    <row r="284" spans="1:22" ht="15.75" customHeight="1">
+      <c r="A284" s="13"/>
+      <c r="B284" s="10"/>
+      <c r="C284" s="12"/>
+      <c r="D284" s="2"/>
+      <c r="E284" s="2"/>
+      <c r="F284" s="2"/>
+      <c r="G284" s="13"/>
+      <c r="H284" s="24"/>
+      <c r="I284" s="24"/>
+      <c r="J284" s="13"/>
+      <c r="K284" s="13"/>
+      <c r="L284" s="13"/>
+      <c r="M284" s="24"/>
+      <c r="N284" s="13"/>
+      <c r="O284" s="10"/>
+      <c r="P284" s="10"/>
+      <c r="Q284" s="10"/>
+      <c r="R284" s="10"/>
+      <c r="S284" s="10"/>
+      <c r="T284" s="10"/>
+      <c r="U284" s="10"/>
+      <c r="V284" s="6"/>
     </row>
   </sheetData>
   <mergeCells count="7">

--- a/scratch/tracker.xlsx
+++ b/scratch/tracker.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://drpinnacle-my.sharepoint.com/personal/vish_drpinnacle_com/Documents/Projects/openvals/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="4634" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9A456466-3883-4ED7-9DA2-CE3E8082B723}"/>
+  <xr:revisionPtr revIDLastSave="4636" documentId="8_{F24D4BFB-FFC1-BD42-9143-22F6B790B9D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A31ADF40-B64E-4F68-B60B-33E55C7EEC8C}"/>
   <bookViews>
     <workbookView xWindow="3960" yWindow="2780" windowWidth="28040" windowHeight="17180" xr2:uid="{BEF502B7-096A-F24C-A77D-ED0F5F38F7FE}"/>
   </bookViews>
